--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -69,7 +69,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -110,12 +110,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C62828"/>
         <bgColor rgb="00C62828"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -177,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,31 +228,19 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,16 +267,16 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 14/10/2026 10:46 | Market session: 2026-10-13 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 15/10/2026 08:42 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -771,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.5640</t>
+          <t>$0.4700</t>
         </is>
       </c>
     </row>
@@ -783,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>167 contracts</t>
+          <t>588 contracts</t>
         </is>
       </c>
     </row>
@@ -795,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.044 (very low volume (167 contracts): not meaningful)</t>
+          <t>0.016 (call-skewed volume)</t>
         </is>
       </c>
     </row>
@@ -807,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,600</t>
+          <t>52,606</t>
         </is>
       </c>
     </row>
@@ -819,7 +801,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,163</t>
+          <t>5,168</t>
         </is>
       </c>
     </row>
@@ -913,7 +895,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>397</v>
@@ -928,19 +910,19 @@
         <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>9.99</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>3.2965</v>
+        <v>0</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>19554</v>
+        <v>7615</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -955,10 +937,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7171</v>
+        <v>7172</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>1591</v>
@@ -967,22 +949,22 @@
         <v>0.222</v>
       </c>
       <c r="G17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J17" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>1.622</v>
+        <v>0.6297</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>150704</v>
+        <v>89600</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -997,10 +979,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27281</v>
+        <v>27300</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3364</v>
@@ -1009,10 +991,10 @@
         <v>0.123</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>140</v>
+        <v>444</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>0.014</v>
@@ -1021,10 +1003,10 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.4637</v>
+        <v>1.2038</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1090781</v>
+        <v>904865</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17218</v>
+        <v>17203</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>197</v>
@@ -1051,7 +1033,7 @@
         <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1063,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>1.4144</v>
+        <v>2.0133</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>650024</v>
+        <v>624383</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1081,34 +1063,34 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="G20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="I20" s="9" t="n">
-        <v>5</v>
+        <v>9.99</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>1.2668</v>
+        <v>1.2</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>33180</v>
+        <v>29612</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.5640 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.4700 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-10-16 (2 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-10-16 (1 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1272,67 +1254,67 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="n">
-        <v>1.7422</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>3.3096</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="24" t="n">
+      <c r="B7" s="17" t="n">
+        <v>4.2772</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>6.7598</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14" t="n">
         <v>232</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="25" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J7" s="26" t="n">
+      <c r="H7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M7" s="16" t="n">
+      <c r="K7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M7" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="N7" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="15" t="n">
-        <v>3.3195</v>
-      </c>
-      <c r="Q7" s="15" t="n">
-        <v>-0.167</v>
-      </c>
-      <c r="R7" s="17" t="n">
-        <v>8.223100000000001</v>
+      <c r="O7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25" t="n">
+        <v>6.8086</v>
+      </c>
+      <c r="Q7" s="25" t="n">
+        <v>-0.652</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>5.635</v>
+        <v>8.5214</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.032</v>
+        <v>0.004</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.4448</v>
+        <v>0.0847</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>0</v>
@@ -1349,31 +1331,31 @@
       <c r="I8" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M8" s="27" t="n">
+      <c r="K8" s="23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L8" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M8" s="23" t="n">
         <v>0.41</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="29" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="Q8" s="29" t="n">
-        <v>-0.971</v>
-      </c>
-      <c r="R8" s="30" t="n">
+      <c r="O8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="25" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="Q8" s="25" t="n">
+        <v>-0.998</v>
+      </c>
+      <c r="R8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1382,10 +1364,10 @@
         <v>0.5</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.1154</v>
+        <v>0.013</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1402,32 +1384,32 @@
       <c r="I9" s="16" t="n">
         <v>0.95</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="K9" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="29" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="Q9" s="29" t="n">
-        <v>-0.993</v>
-      </c>
-      <c r="R9" s="30" t="n">
-        <v>6.8975</v>
+      <c r="K9" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L9" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q9" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -1435,10 +1417,10 @@
         <v>1.2</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.0528</v>
+        <v>0.0042</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
@@ -1455,32 +1437,32 @@
       <c r="I10" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L10" s="27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M10" s="27" t="n">
+      <c r="K10" s="23" t="n">
         <v>1.35</v>
       </c>
-      <c r="N10" s="28" t="n">
+      <c r="L10" s="23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="29" t="n">
-        <v>0.0442</v>
-      </c>
-      <c r="Q10" s="29" t="n">
-        <v>-0.998</v>
-      </c>
-      <c r="R10" s="30" t="n">
-        <v>8.26</v>
+      <c r="O10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="25" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="Q10" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1488,10 +1470,10 @@
         <v>1.2</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.0307</v>
+        <v>0.0018</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1508,31 +1490,31 @@
       <c r="I11" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="J11" s="26" t="n">
+      <c r="J11" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K11" s="27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="29" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="Q11" s="29" t="n">
-        <v>-0.999</v>
-      </c>
-      <c r="R11" s="30" t="n">
+      <c r="K11" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L11" s="23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="25" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q11" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R11" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1541,10 +1523,10 @@
         <v>1.2</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.0072</v>
+        <v>0.0002</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1561,31 +1543,31 @@
       <c r="I12" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="27" t="n">
+      <c r="K12" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="L12" s="27" t="n">
+      <c r="L12" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="M12" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="29" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="Q12" s="29" t="n">
+      <c r="M12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="R12" s="30" t="n">
+      <c r="R12" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1597,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.0034</v>
+        <v>0.0001</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1614,31 +1596,31 @@
       <c r="I13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K13" s="27" t="n">
+      <c r="K13" s="23" t="n">
         <v>6.3</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L13" s="23" t="n">
         <v>7.6</v>
       </c>
-      <c r="M13" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="29" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="Q13" s="29" t="n">
+      <c r="M13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="R13" s="30" t="n">
+      <c r="R13" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1647,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (37 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (36 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1739,67 +1721,67 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="n">
-        <v>1.622</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>1.4749</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>1725</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H18" s="25" t="n">
+      <c r="B18" s="17" t="n">
+        <v>0.9446</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>1.9038</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1726</v>
+      </c>
+      <c r="G18" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" s="26" t="n">
+      <c r="H18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J18" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="16" t="n">
+      <c r="K18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="23" t="n">
         <v>0.7</v>
       </c>
-      <c r="M18" s="16" t="n">
+      <c r="M18" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="24" t="n">
         <v>871</v>
       </c>
-      <c r="O18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>1.4898</v>
-      </c>
-      <c r="Q18" s="15" t="n">
-        <v>-0.302</v>
-      </c>
-      <c r="R18" s="17" t="n">
-        <v>6.7188</v>
+      <c r="O18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25" t="n">
+        <v>1.9276</v>
+      </c>
+      <c r="Q18" s="25" t="n">
+        <v>-0.452</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>6.4666</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>1.9909</v>
+        <v>1.961</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.285</v>
+        <v>0.231</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.9688</v>
+        <v>0.9543</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>0</v>
@@ -1814,45 +1796,45 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J19" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="27" t="n">
+      <c r="K19" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L19" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M19" s="23" t="n">
         <v>0.45</v>
       </c>
-      <c r="N19" s="28" t="n">
+      <c r="N19" s="24" t="n">
         <v>358</v>
       </c>
-      <c r="O19" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="29" t="n">
-        <v>0.9902</v>
-      </c>
-      <c r="Q19" s="29" t="n">
-        <v>-0.733</v>
-      </c>
-      <c r="R19" s="30" t="n">
+      <c r="O19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="25" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="Q19" s="25" t="n">
+        <v>-0.787</v>
+      </c>
+      <c r="R19" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.1945</v>
+        <v>2.5804</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.192</v>
+        <v>0.16</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.6355</v>
+        <v>0.6339</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>0</v>
@@ -1869,43 +1851,43 @@
       <c r="I20" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J20" s="26" t="n">
+      <c r="J20" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="K20" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L20" s="27" t="n">
+      <c r="K20" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L20" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="N20" s="28" t="n">
+      <c r="N20" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="O20" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="29" t="n">
-        <v>0.6566</v>
-      </c>
-      <c r="Q20" s="29" t="n">
-        <v>-0.827</v>
-      </c>
-      <c r="R20" s="30" t="n">
+      <c r="O20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="25" t="n">
+        <v>0.6592</v>
+      </c>
+      <c r="Q20" s="25" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="R20" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>3.11</v>
+        <v>4.9072</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.152</v>
+        <v>0.128</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.4881</v>
+        <v>0.4906</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>0</v>
@@ -1920,45 +1902,45 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J21" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J21" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="27" t="n">
+      <c r="K21" s="23" t="n">
         <v>0.95</v>
       </c>
-      <c r="L21" s="27" t="n">
+      <c r="L21" s="23" t="n">
         <v>1.95</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="23" t="n">
         <v>1.33</v>
       </c>
-      <c r="N21" s="28" t="n">
+      <c r="N21" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="O21" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="29" t="n">
-        <v>0.5106000000000001</v>
-      </c>
-      <c r="Q21" s="29" t="n">
-        <v>-0.868</v>
-      </c>
-      <c r="R21" s="30" t="n">
-        <v>2.5405</v>
+      <c r="O21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="25" t="n">
+        <v>0.5178</v>
+      </c>
+      <c r="Q21" s="25" t="n">
+        <v>-0.894</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>3.4231</v>
+        <v>3.8758</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.13</v>
+        <v>0.109</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.4048</v>
+        <v>0.4086</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>0</v>
@@ -1975,43 +1957,43 @@
       <c r="I22" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="J22" s="26" t="n">
+      <c r="J22" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K22" s="27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L22" s="27" t="n">
+      <c r="K22" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L22" s="23" t="n">
         <v>2.55</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="23" t="n">
         <v>1.87</v>
       </c>
-      <c r="N22" s="28" t="n">
+      <c r="N22" s="24" t="n">
         <v>122</v>
       </c>
-      <c r="O22" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="29" t="n">
-        <v>0.4296</v>
-      </c>
-      <c r="Q22" s="29" t="n">
-        <v>-0.892</v>
-      </c>
-      <c r="R22" s="30" t="n">
+      <c r="O22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="Q22" s="25" t="n">
+        <v>-0.914</v>
+      </c>
+      <c r="R22" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="17" t="n">
-        <v>4.3066</v>
+        <v>4.7535</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.2441</v>
+        <v>0.2477</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
@@ -2028,43 +2010,43 @@
       <c r="I23" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="J23" s="26" t="n">
+      <c r="J23" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="L23" s="27" t="n">
+      <c r="L23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="23" t="n">
         <v>4.8</v>
       </c>
-      <c r="N23" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="29" t="n">
-        <v>0.2974</v>
-      </c>
-      <c r="Q23" s="29" t="n">
-        <v>-0.945</v>
-      </c>
-      <c r="R23" s="30" t="n">
+      <c r="N23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="25" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Q23" s="25" t="n">
+        <v>-0.962</v>
+      </c>
+      <c r="R23" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="17" t="n">
-        <v>4.1776</v>
+        <v>4.5534</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.1886</v>
+        <v>0.1912</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>0</v>
@@ -2081,31 +2063,31 @@
       <c r="I24" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J24" s="26" t="n">
+      <c r="J24" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K24" s="27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L24" s="27" t="n">
+      <c r="K24" s="23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L24" s="23" t="n">
         <v>7.6</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="23" t="n">
         <v>7.3</v>
       </c>
-      <c r="N24" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="29" t="n">
-        <v>0.2438</v>
-      </c>
-      <c r="Q24" s="29" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="R24" s="30" t="n">
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="25" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="Q24" s="25" t="n">
+        <v>-0.983</v>
+      </c>
+      <c r="R24" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -2114,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (93 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (92 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2206,120 +2188,120 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="n">
-        <v>1.4515</v>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="D29" s="23" t="n">
-        <v>1.0065</v>
-      </c>
-      <c r="E29" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="24" t="n">
+      <c r="B29" s="17" t="n">
+        <v>1.0584</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>1.2858</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>332</v>
+      </c>
+      <c r="F29" s="14" t="n">
         <v>9837</v>
       </c>
-      <c r="G29" s="25" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H29" s="25" t="n">
+      <c r="G29" s="16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I29" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="I29" s="25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J29" s="26" t="n">
+      <c r="J29" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="K29" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="L29" s="16" t="n">
+      <c r="L29" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="M29" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N29" s="14" t="n">
+      <c r="N29" s="24" t="n">
         <v>2093</v>
       </c>
-      <c r="O29" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" s="15" t="n">
-        <v>1.0268</v>
-      </c>
-      <c r="Q29" s="15" t="n">
-        <v>-0.297</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>1.2884</v>
+      <c r="O29" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" s="25" t="n">
+        <v>1.3166</v>
+      </c>
+      <c r="Q29" s="25" t="n">
+        <v>-0.397</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>1.2345</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.4668</v>
+        <v>1.5306</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.407</v>
+        <v>0.352</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.8762</v>
+        <v>0.9347</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6858</v>
+        <v>6877</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="J30" s="26" t="n">
+      <c r="J30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="27" t="n">
+      <c r="K30" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M30" s="23" t="n">
         <v>0.48</v>
       </c>
-      <c r="N30" s="28" t="n">
+      <c r="N30" s="24" t="n">
         <v>641</v>
       </c>
-      <c r="O30" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="29" t="n">
-        <v>0.9121</v>
-      </c>
-      <c r="Q30" s="29" t="n">
-        <v>-0.632</v>
-      </c>
-      <c r="R30" s="30" t="n">
-        <v>1.5602</v>
+      <c r="O30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="25" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="Q30" s="25" t="n">
+        <v>-0.6879999999999999</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.3691</v>
+        <v>1.6018</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.302</v>
+        <v>0.267</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.6722</v>
+        <v>0.7134</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
@@ -2336,96 +2318,96 @@
       <c r="I31" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J31" s="26" t="n">
+      <c r="J31" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="K31" s="27" t="n">
+      <c r="K31" s="23" t="n">
         <v>0.7</v>
       </c>
-      <c r="L31" s="27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M31" s="27" t="n">
+      <c r="L31" s="23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M31" s="23" t="n">
         <v>0.97</v>
       </c>
-      <c r="N31" s="28" t="n">
+      <c r="N31" s="24" t="n">
         <v>455</v>
       </c>
-      <c r="O31" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="29" t="n">
-        <v>0.7161</v>
-      </c>
-      <c r="Q31" s="29" t="n">
-        <v>-0.741</v>
-      </c>
-      <c r="R31" s="30" t="n">
-        <v>2.5009</v>
+      <c r="O31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="25" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="Q31" s="25" t="n">
+        <v>-0.779</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>3.7506</v>
+        <v>3.8267</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5585</v>
+        <v>0.5948</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32" s="14" t="n">
         <v>2815</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J32" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L32" s="27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M32" s="27" t="n">
+      <c r="K32" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L32" s="23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M32" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="N32" s="28" t="n">
+      <c r="N32" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="O32" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="29" t="n">
-        <v>0.6102</v>
-      </c>
-      <c r="Q32" s="29" t="n">
-        <v>-0.795</v>
-      </c>
-      <c r="R32" s="30" t="n">
-        <v>1.764</v>
+      <c r="O32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="25" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="Q32" s="25" t="n">
+        <v>-0.825</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.6567</v>
+        <v>2.9997</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.4872</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
@@ -2442,43 +2424,43 @@
       <c r="I33" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="J33" s="26" t="n">
+      <c r="J33" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L33" s="27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M33" s="27" t="n">
+      <c r="K33" s="23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L33" s="23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M33" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="N33" s="28" t="n">
+      <c r="N33" s="24" t="n">
         <v>153</v>
       </c>
-      <c r="O33" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="29" t="n">
-        <v>0.5447</v>
-      </c>
-      <c r="Q33" s="29" t="n">
-        <v>-0.829</v>
-      </c>
-      <c r="R33" s="30" t="n">
-        <v>1.981</v>
+      <c r="O33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="25" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="Q33" s="25" t="n">
+        <v>-0.855</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>3.9161</v>
+        <v>4.3589</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.16</v>
+        <v>0.146</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.3602</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
@@ -2495,43 +2477,43 @@
       <c r="I34" s="16" t="n">
         <v>0.35</v>
       </c>
-      <c r="J34" s="26" t="n">
+      <c r="J34" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K34" s="27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L34" s="27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M34" s="27" t="n">
+      <c r="K34" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="N34" s="28" t="n">
+      <c r="N34" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="O34" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="29" t="n">
-        <v>0.4222</v>
-      </c>
-      <c r="Q34" s="29" t="n">
-        <v>-0.909</v>
-      </c>
-      <c r="R34" s="30" t="n">
-        <v>7.1875</v>
+      <c r="O34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="25" t="n">
+        <v>0.5227000000000001</v>
+      </c>
+      <c r="Q34" s="25" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>7.0313</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.2342</v>
+        <v>4.6704</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2746</v>
+        <v>0.2984</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
@@ -2548,43 +2530,43 @@
       <c r="I35" s="16" t="n">
         <v>0.35</v>
       </c>
-      <c r="J35" s="26" t="n">
+      <c r="J35" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K35" s="27" t="n">
+      <c r="K35" s="23" t="n">
         <v>6.4</v>
       </c>
-      <c r="L35" s="27" t="n">
+      <c r="L35" s="23" t="n">
         <v>7.4</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="23" t="n">
         <v>6.2</v>
       </c>
-      <c r="N35" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>0.4153</v>
-      </c>
-      <c r="Q35" s="29" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="R35" s="30" t="n">
-        <v>7.5</v>
+      <c r="N35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="25" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="Q35" s="25" t="n">
+        <v>-0.969</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>7.3125</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>2.8279</v>
+        <v>3.0429</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.123</v>
+        <v>0.113</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.242</v>
+        <v>0.2638</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>0</v>
@@ -2601,43 +2583,43 @@
       <c r="I36" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J36" s="26" t="n">
+      <c r="J36" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="27" t="n">
+      <c r="K36" s="23" t="n">
         <v>8.9</v>
       </c>
-      <c r="L36" s="27" t="n">
+      <c r="L36" s="23" t="n">
         <v>9.9</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="N36" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="29" t="n">
-        <v>0.3026</v>
-      </c>
-      <c r="Q36" s="29" t="n">
-        <v>-0.974</v>
-      </c>
-      <c r="R36" s="30" t="n">
-        <v>6.2813</v>
+      <c r="N36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="25" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="Q36" s="25" t="n">
+        <v>-0.988</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>6.0313</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>2.9732</v>
+        <v>3.1876</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.114</v>
+        <v>0.105</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.2205</v>
+        <v>0.241</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2654,32 +2636,32 @@
       <c r="I37" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J37" s="26" t="n">
+      <c r="J37" s="22" t="n">
         <v>12.5</v>
       </c>
-      <c r="K37" s="27" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L37" s="27" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M37" s="27" t="n">
+      <c r="K37" s="23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L37" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M37" s="23" t="n">
         <v>10.94</v>
       </c>
-      <c r="N37" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="29" t="n">
-        <v>0.1363</v>
-      </c>
-      <c r="Q37" s="29" t="n">
-        <v>-0.988</v>
-      </c>
-      <c r="R37" s="30" t="n">
-        <v>7.8125</v>
+      <c r="N37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="25" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="Q37" s="25" t="n">
+        <v>-0.998</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>7.6563</v>
       </c>
     </row>
     <row r="38"/>
@@ -2687,7 +2669,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (128 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (127 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2779,123 +2761,123 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="22" t="n">
-        <v>1.4493</v>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>0.7053</v>
-      </c>
-      <c r="E42" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="F42" s="24" t="n">
-        <v>2569</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H42" s="25" t="n">
+      <c r="B42" s="17" t="n">
+        <v>1.7549</v>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>2554</v>
+      </c>
+      <c r="G42" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="I42" s="25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J42" s="26" t="n">
+      <c r="H42" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J42" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="16" t="n">
+      <c r="K42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="23" t="n">
         <v>0.95</v>
       </c>
-      <c r="M42" s="16" t="n">
+      <c r="M42" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="N42" s="14" t="n">
+      <c r="N42" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O42" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="15" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="Q42" s="15" t="n">
-        <v>-0.281</v>
-      </c>
-      <c r="R42" s="17" t="n">
-        <v>6.9814</v>
+      <c r="O42" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="25" t="n">
+        <v>0.8142</v>
+      </c>
+      <c r="Q42" s="25" t="n">
+        <v>-0.336</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>6.8935</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.7512</v>
+        <v>2.0918</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.407</v>
+        <v>0.392</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7935</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F43" s="14" t="n">
         <v>6384</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J43" s="26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J43" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="27" t="n">
+      <c r="K43" s="23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L43" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="M43" s="27" t="n">
+      <c r="M43" s="23" t="n">
         <v>0.45</v>
       </c>
-      <c r="N43" s="28" t="n">
+      <c r="N43" s="24" t="n">
         <v>151</v>
       </c>
-      <c r="O43" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="29" t="n">
-        <v>0.7493</v>
-      </c>
-      <c r="Q43" s="29" t="n">
-        <v>-0.5610000000000001</v>
-      </c>
-      <c r="R43" s="30" t="n">
-        <v>1.1949</v>
+      <c r="O43" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="25" t="n">
+        <v>0.8153</v>
+      </c>
+      <c r="Q43" s="25" t="n">
+        <v>-0.588</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>1.3774</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.2398</v>
+        <v>2.2346</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.6031</v>
+        <v>0.655</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
         <v>5582</v>
@@ -2907,45 +2889,45 @@
         <v>0</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J44" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J44" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="K44" s="27" t="n">
+      <c r="K44" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="L44" s="27" t="n">
+      <c r="L44" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="M44" s="27" t="n">
+      <c r="M44" s="23" t="n">
         <v>1.02</v>
       </c>
-      <c r="N44" s="28" t="n">
+      <c r="N44" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O44" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="29" t="n">
-        <v>0.6297</v>
-      </c>
-      <c r="Q44" s="29" t="n">
-        <v>-0.671</v>
-      </c>
-      <c r="R44" s="30" t="n">
-        <v>1.6142</v>
+      <c r="O44" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="25" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="Q44" s="25" t="n">
+        <v>-0.6889999999999999</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>1.9802</v>
+        <v>2.2288</v>
       </c>
       <c r="C45" s="15" t="n">
         <v>0.248</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5099</v>
+        <v>0.5626</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
@@ -2962,43 +2944,43 @@
       <c r="I45" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J45" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L45" s="27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M45" s="27" t="n">
+      <c r="K45" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M45" s="23" t="n">
         <v>1.35</v>
       </c>
-      <c r="N45" s="28" t="n">
+      <c r="N45" s="24" t="n">
         <v>41</v>
       </c>
-      <c r="O45" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="29" t="n">
-        <v>0.5538</v>
-      </c>
-      <c r="Q45" s="29" t="n">
-        <v>-0.728</v>
-      </c>
-      <c r="R45" s="30" t="n">
-        <v>1.3002</v>
+      <c r="O45" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="25" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="Q45" s="25" t="n">
+        <v>-0.745</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>1.6176</v>
+        <v>3.3376</v>
       </c>
       <c r="C46" s="15" t="n">
         <v>0.217</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4479</v>
+        <v>0.4992</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -3013,45 +2995,45 @@
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J46" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J46" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K46" s="23" t="n">
         <v>1.45</v>
       </c>
-      <c r="L46" s="27" t="n">
+      <c r="L46" s="23" t="n">
         <v>2.45</v>
       </c>
-      <c r="M46" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="29" t="n">
-        <v>0.5077</v>
-      </c>
-      <c r="Q46" s="29" t="n">
-        <v>-0.765</v>
-      </c>
-      <c r="R46" s="30" t="n">
-        <v>1.5031</v>
+      <c r="M46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="25" t="n">
+        <v>0.5865</v>
+      </c>
+      <c r="Q46" s="25" t="n">
+        <v>-0.782</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.0607</v>
+        <v>4.5498</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3062</v>
+        <v>0.3472</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3068,43 +3050,43 @@
       <c r="I47" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="J47" s="26" t="n">
+      <c r="J47" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K47" s="27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L47" s="27" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M47" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="29" t="n">
-        <v>0.4307</v>
-      </c>
-      <c r="Q47" s="29" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="R47" s="30" t="n">
-        <v>2.1314</v>
+      <c r="K47" s="23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="25" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="Q47" s="25" t="n">
+        <v>-0.883</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>6.8851</v>
+        <v>6.4145</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2494</v>
+        <v>0.2832</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3119,34 +3101,34 @@
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J48" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J48" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K48" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L48" s="27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="29" t="n">
-        <v>0.4304</v>
-      </c>
-      <c r="Q48" s="29" t="n">
-        <v>-0.914</v>
-      </c>
-      <c r="R48" s="30" t="n">
-        <v>2.5099</v>
+      <c r="K48" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L48" s="23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="25" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="Q48" s="25" t="n">
+        <v>-0.9419999999999999</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="49"/>
@@ -3154,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (219 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (218 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3246,73 +3228,73 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="22" t="n">
-        <v>1.9085</v>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>0.7335</v>
-      </c>
-      <c r="E53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="24" t="n">
+      <c r="B53" s="17" t="n">
+        <v>4.9398</v>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>1.0437</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14" t="n">
         <v>336</v>
       </c>
-      <c r="G53" s="25" t="n">
+      <c r="G53" s="16" t="n">
         <v>0.35</v>
       </c>
-      <c r="H53" s="25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I53" s="25" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J53" s="26" t="n">
+      <c r="H53" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J53" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L53" s="16" t="n">
+      <c r="K53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="M53" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="14" t="n">
+      <c r="N53" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="P53" s="15" t="n">
-        <v>0.7667</v>
-      </c>
-      <c r="Q53" s="15" t="n">
-        <v>-0.277</v>
-      </c>
-      <c r="R53" s="17" t="n">
-        <v>1.2287</v>
+      <c r="O53" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="25" t="n">
+        <v>1.1063</v>
+      </c>
+      <c r="Q53" s="25" t="n">
+        <v>-0.364</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>1.4576</v>
+        <v>2.1162</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.471</v>
+        <v>0.42</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.8709</v>
+        <v>0.9432</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G54" s="16" t="n">
         <v>0.2</v>
@@ -3321,45 +3303,45 @@
         <v>0.05</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J54" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J54" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="27" t="n">
+      <c r="K54" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="L54" s="27" t="n">
+      <c r="L54" s="23" t="n">
         <v>1.05</v>
       </c>
-      <c r="M54" s="27" t="n">
+      <c r="M54" s="23" t="n">
         <v>0.59</v>
       </c>
-      <c r="N54" s="28" t="n">
+      <c r="N54" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O54" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="29" t="n">
-        <v>0.9706</v>
-      </c>
-      <c r="Q54" s="29" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="R54" s="30" t="n">
-        <v>1.3939</v>
+      <c r="O54" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="25" t="n">
+        <v>1.0711</v>
+      </c>
+      <c r="Q54" s="25" t="n">
+        <v>-0.676</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>1.0435</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>4.1759</v>
+        <v>2.5795</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.367</v>
+        <v>0.335</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.696</v>
+        <v>0.7506</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
@@ -3374,45 +3356,45 @@
         <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J55" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="K55" s="27" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L55" s="27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M55" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="29" t="n">
-        <v>0.8153</v>
-      </c>
-      <c r="Q55" s="29" t="n">
-        <v>-0.736</v>
-      </c>
-      <c r="R55" s="30" t="n">
-        <v>1.7434</v>
+      <c r="K55" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L55" s="23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="25" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="Q55" s="25" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>2.4288</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>4.3352</v>
+        <v>7.7388</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.318</v>
+        <v>0.293</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.5944</v>
+        <v>0.6444</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
@@ -3429,43 +3411,43 @@
       <c r="I56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="26" t="n">
+      <c r="J56" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K56" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="29" t="n">
-        <v>0.7338</v>
-      </c>
-      <c r="Q56" s="29" t="n">
-        <v>-0.795</v>
-      </c>
-      <c r="R56" s="30" t="n">
-        <v>1.674</v>
+      <c r="K56" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L56" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q56" s="25" t="n">
+        <v>-0.827</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>2.6568</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>4.4534</v>
+        <v>3.9533</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.288</v>
+        <v>0.267</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5296</v>
+        <v>0.5768</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
@@ -3480,45 +3462,45 @@
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J57" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K57" s="27" t="n">
+      <c r="K57" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="L57" s="27" t="n">
+      <c r="L57" s="23" t="n">
         <v>4.7</v>
       </c>
-      <c r="M57" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="29" t="n">
-        <v>0.6791</v>
-      </c>
-      <c r="Q57" s="29" t="n">
-        <v>-0.834</v>
-      </c>
-      <c r="R57" s="30" t="n">
-        <v>6.1518</v>
+      <c r="M57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="25" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="Q57" s="25" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>6.058</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>1.5059</v>
+        <v>1.6403</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.219</v>
+        <v>0.205</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.3841</v>
+        <v>0.4224</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
@@ -3535,43 +3517,43 @@
       <c r="I58" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J58" s="26" t="n">
+      <c r="J58" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K58" s="27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L58" s="27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M58" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="29" t="n">
-        <v>0.5596</v>
-      </c>
-      <c r="Q58" s="29" t="n">
-        <v>-0.945</v>
-      </c>
-      <c r="R58" s="30" t="n">
-        <v>1.2</v>
+      <c r="K58" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L58" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="25" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="Q58" s="25" t="n">
+        <v>-0.967</v>
+      </c>
+      <c r="R58" s="26" t="n">
+        <v>2.2485</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>1.9358</v>
+        <v>2.0936</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.19</v>
+        <v>0.177</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3242</v>
+        <v>0.3577</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
@@ -3588,32 +3570,32 @@
       <c r="I59" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="J59" s="26" t="n">
+      <c r="J59" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="K59" s="27" t="n">
+      <c r="K59" s="23" t="n">
         <v>4.5</v>
       </c>
-      <c r="L59" s="27" t="n">
+      <c r="L59" s="23" t="n">
         <v>9.4</v>
       </c>
-      <c r="M59" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="29" t="n">
-        <v>0.1532</v>
-      </c>
-      <c r="Q59" s="29" t="n">
-        <v>-0.987</v>
-      </c>
-      <c r="R59" s="30" t="n">
-        <v>2.2529</v>
+      <c r="M59" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R59" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -3627,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3730,31 +3712,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0.5639999999999999</v>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0.47</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.098</v>
@@ -3763,43 +3745,43 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1.8127</v>
-      </c>
-      <c r="N6" s="31" t="inlineStr">
+        <v>1.2617</v>
+      </c>
+      <c r="N6" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>0.585</v>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0.5639999999999999</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -3808,43 +3790,43 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>2.1738</v>
-      </c>
-      <c r="N7" s="34" t="inlineStr">
+        <v>1.8127</v>
+      </c>
+      <c r="N7" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0.599</v>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0.585</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.098</v>
@@ -3853,40 +3835,40 @@
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.7667</v>
-      </c>
-      <c r="N8" s="31" t="inlineStr">
+        <v>2.1738</v>
+      </c>
+      <c r="N8" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0.5639999999999999</v>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>0.599</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>5157</v>
@@ -3898,88 +3880,88 @@
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>1.6438</v>
-      </c>
-      <c r="N9" s="34" t="inlineStr">
+        <v>1.7667</v>
+      </c>
+      <c r="N9" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>0.59</v>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>0.5639999999999999</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>5157</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>1.5704</v>
-      </c>
-      <c r="N10" s="31" t="inlineStr">
+        <v>1.6438</v>
+      </c>
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="n">
-        <v>0.572</v>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>0.59</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.099</v>
@@ -3988,43 +3970,43 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.565</v>
-      </c>
-      <c r="N11" s="34" t="inlineStr">
+        <v>1.5704</v>
+      </c>
+      <c r="N11" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="n">
-        <v>0.596</v>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>0.572</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.099</v>
@@ -4033,40 +4015,40 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.7067</v>
-      </c>
-      <c r="N12" s="31" t="inlineStr">
+        <v>1.565</v>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0.593</v>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>0.596</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>5161</v>
@@ -4078,31 +4060,31 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.5299</v>
-      </c>
-      <c r="N13" s="34" t="inlineStr">
+        <v>1.7067</v>
+      </c>
+      <c r="N13" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="n">
-        <v>0.575</v>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>0.593</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>0</v>
@@ -4111,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>5161</v>
@@ -4123,43 +4105,43 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.3543</v>
-      </c>
-      <c r="N14" s="31" t="inlineStr">
+        <v>1.5299</v>
+      </c>
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0.574</v>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>0.575</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0.099</v>
@@ -4168,88 +4150,88 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.9768</v>
-      </c>
-      <c r="N15" s="34" t="inlineStr">
+        <v>1.3543</v>
+      </c>
+      <c r="N15" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="n">
-        <v>0.626</v>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>0.574</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>5159</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.4818</v>
-      </c>
-      <c r="N16" s="31" t="inlineStr">
+        <v>1.9768</v>
+      </c>
+      <c r="N16" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0.621</v>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>0.626</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0.098</v>
@@ -4258,43 +4240,43 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.7835</v>
-      </c>
-      <c r="N17" s="34" t="inlineStr">
+        <v>1.4818</v>
+      </c>
+      <c r="N17" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="n">
-        <v>0.64</v>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>0.621</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.098</v>
@@ -4303,40 +4285,40 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.8306</v>
-      </c>
-      <c r="N18" s="31" t="inlineStr">
+        <v>1.7835</v>
+      </c>
+      <c r="N18" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0.656</v>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>0.64</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>5156</v>
@@ -4348,178 +4330,178 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.8394</v>
-      </c>
-      <c r="N19" s="34" t="inlineStr">
+        <v>1.8306</v>
+      </c>
+      <c r="N19" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="n">
-        <v>0.662</v>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>0.656</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.7796</v>
-      </c>
-      <c r="N20" s="31" t="inlineStr">
+        <v>1.8394</v>
+      </c>
+      <c r="N20" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="n">
-        <v>0.6962</v>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>0.662</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K21" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.7491</v>
-      </c>
-      <c r="N21" s="34" t="inlineStr">
+        <v>1.7796</v>
+      </c>
+      <c r="N21" s="30" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="n">
-        <v>0.6860000000000001</v>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>0.6962</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.9942</v>
-      </c>
-      <c r="N22" s="31" t="inlineStr">
+        <v>1.7491</v>
+      </c>
+      <c r="N22" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.653</v>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>0.6860000000000001</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0.093</v>
@@ -4528,199 +4510,205 @@
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
+        <v>2418880</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>1.9942</v>
+      </c>
+      <c r="N23" s="30" t="inlineStr">
+        <is>
+          <t>Heavy call skew 🟢🟢</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>52119</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>4863</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>2361798</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M24" s="11" t="n">
         <v>1.8962</v>
       </c>
-      <c r="N23" s="34" t="inlineStr">
+      <c r="N24" s="27" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="31" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C25" s="31" t="n">
         <v>1.39</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="14" t="n">
         <v>3394</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E25" s="14" t="n">
         <v>3244</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F25" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G25" s="15" t="n">
         <v>0.046</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H25" s="14" t="n">
         <v>45759</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I25" s="14" t="n">
         <v>7845</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J25" s="15" t="n">
         <v>0.171</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="11" t="inlineStr"/>
-      <c r="N24" s="31" t="inlineStr">
-        <is>
-          <t>NO DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>4661</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>3922</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>739</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>44316</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>7547</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>0.17</v>
       </c>
       <c r="K25" s="16" t="inlineStr"/>
       <c r="L25" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="17" t="inlineStr"/>
-      <c r="N25" s="34" t="inlineStr">
+      <c r="N25" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="n">
-        <v>1.55</v>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>1.46</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K26" s="10" t="inlineStr"/>
       <c r="L26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="11" t="inlineStr"/>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="N26" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>1.73</v>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n">
+        <v>1.55</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="15" t="inlineStr"/>
+        <v>7194</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K27" s="16" t="inlineStr"/>
       <c r="L27" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="17" t="inlineStr"/>
-      <c r="N27" s="34" t="inlineStr">
+      <c r="N27" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="n">
-        <v>1.55</v>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>1.73</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>0</v>
@@ -4734,112 +4722,112 @@
         <v>0</v>
       </c>
       <c r="M28" s="11" t="inlineStr"/>
-      <c r="N28" s="31" t="inlineStr">
+      <c r="N28" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>1.59</v>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>1.55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J29" s="15" t="inlineStr"/>
       <c r="K29" s="16" t="inlineStr"/>
       <c r="L29" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="17" t="inlineStr"/>
-      <c r="N29" s="34" t="inlineStr">
+      <c r="N29" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="n">
-        <v>1.69</v>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>1.59</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9" t="inlineStr"/>
+        <v>6136</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K30" s="10" t="inlineStr"/>
       <c r="L30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
-      <c r="N30" s="31" t="inlineStr">
+      <c r="N30" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n">
         <v>1.69</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H31" s="14" t="n">
         <v>0</v>
@@ -4853,180 +4841,180 @@
         <v>0</v>
       </c>
       <c r="M31" s="17" t="inlineStr"/>
-      <c r="N31" s="34" t="inlineStr">
+      <c r="N31" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="n">
-        <v>1.46</v>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>1.69</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="inlineStr"/>
       <c r="K32" s="10" t="inlineStr"/>
       <c r="L32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="11" t="inlineStr"/>
-      <c r="N32" s="31" t="inlineStr">
+      <c r="N32" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
-        <v>1.42</v>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>1.46</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="15" t="inlineStr"/>
+        <v>5834</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K33" s="16" t="inlineStr"/>
       <c r="L33" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="17" t="inlineStr"/>
-      <c r="N33" s="34" t="inlineStr">
+      <c r="N33" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>1.45</v>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>1.42</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="inlineStr"/>
       <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
-      <c r="N34" s="31" t="inlineStr">
+      <c r="N34" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="34" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>1.48</v>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="n">
+        <v>1.45</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="15" t="inlineStr"/>
+        <v>4272</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K35" s="16" t="inlineStr"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="17" t="inlineStr"/>
-      <c r="N35" s="34" t="inlineStr">
+      <c r="N35" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="n">
-        <v>1.5</v>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>1.48</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2568</v>
@@ -5041,33 +5029,31 @@
         <v>0.27</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="11" t="inlineStr"/>
-      <c r="N36" s="31" t="inlineStr">
+      <c r="N36" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>1.69</v>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>1.5</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>2568</v>
@@ -5082,31 +5068,33 @@
         <v>0.27</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="15" t="inlineStr"/>
+        <v>4145</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K37" s="16" t="inlineStr"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="17" t="inlineStr"/>
-      <c r="N37" s="34" t="inlineStr">
+      <c r="N37" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="n">
-        <v>1.71</v>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>1.69</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2568</v>
@@ -5121,70 +5109,72 @@
         <v>0.27</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J38" s="9" t="inlineStr"/>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="11" t="inlineStr"/>
-      <c r="N38" s="31" t="inlineStr">
+      <c r="N38" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="n">
-        <v>1.61</v>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1.71</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="15" t="inlineStr"/>
+        <v>546</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H39" s="14" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="15" t="inlineStr"/>
+        <v>4059</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K39" s="16" t="inlineStr"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="17" t="inlineStr"/>
-      <c r="N39" s="34" t="inlineStr">
+      <c r="N39" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="n">
-        <v>1.68</v>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>1.61</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>0</v>
@@ -5208,20 +5198,20 @@
         <v>0</v>
       </c>
       <c r="M40" s="11" t="inlineStr"/>
-      <c r="N40" s="31" t="inlineStr">
+      <c r="N40" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>1.7</v>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1.68</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>0</v>
@@ -5245,20 +5235,20 @@
         <v>0</v>
       </c>
       <c r="M41" s="17" t="inlineStr"/>
-      <c r="N41" s="34" t="inlineStr">
+      <c r="N41" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C42" s="32" t="n">
-        <v>1.83</v>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>1.7</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>0</v>
@@ -5282,20 +5272,20 @@
         <v>0</v>
       </c>
       <c r="M42" s="11" t="inlineStr"/>
-      <c r="N42" s="31" t="inlineStr">
+      <c r="N42" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="n">
-        <v>1.58</v>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>1.83</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
@@ -5319,20 +5309,20 @@
         <v>0</v>
       </c>
       <c r="M43" s="17" t="inlineStr"/>
-      <c r="N43" s="34" t="inlineStr">
+      <c r="N43" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="C44" s="32" t="n">
-        <v>0</v>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>1.58</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>0</v>
@@ -5356,19 +5346,19 @@
         <v>0</v>
       </c>
       <c r="M44" s="11" t="inlineStr"/>
-      <c r="N44" s="31" t="inlineStr">
+      <c r="N44" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C45" s="35" t="n">
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="14" t="n">
@@ -5393,19 +5383,19 @@
         <v>0</v>
       </c>
       <c r="M45" s="17" t="inlineStr"/>
-      <c r="N45" s="34" t="inlineStr">
+      <c r="N45" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C46" s="32" t="n">
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="8" t="n">
@@ -5430,19 +5420,19 @@
         <v>0</v>
       </c>
       <c r="M46" s="11" t="inlineStr"/>
-      <c r="N46" s="31" t="inlineStr">
+      <c r="N46" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="34" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C47" s="35" t="n">
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="14" t="n">
@@ -5467,7 +5457,44 @@
         <v>0</v>
       </c>
       <c r="M47" s="17" t="inlineStr"/>
-      <c r="N47" s="34" t="inlineStr">
+      <c r="N47" s="30" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr"/>
+      <c r="H48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9" t="inlineStr"/>
+      <c r="K48" s="10" t="inlineStr"/>
+      <c r="L48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="11" t="inlineStr"/>
+      <c r="N48" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5569,12 +5596,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00000500</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5582,7 +5609,7 @@
       <c r="D6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -5602,19 +5629,19 @@
       <c r="J6" s="8" t="n">
         <v>232</v>
       </c>
-      <c r="K6" s="31" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00000500</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5622,7 +5649,7 @@
       <c r="D7" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -5642,19 +5669,19 @@
       <c r="J7" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="34" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00001000</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5662,7 +5689,7 @@
       <c r="D8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -5682,19 +5709,19 @@
       <c r="J8" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="K8" s="31" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00001000</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5702,7 +5729,7 @@
       <c r="D9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -5722,19 +5749,19 @@
       <c r="J9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="34" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00001500</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5742,7 +5769,7 @@
       <c r="D10" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -5762,19 +5789,19 @@
       <c r="J10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="K10" s="31" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00001500</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5782,7 +5809,7 @@
       <c r="D11" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -5802,19 +5829,19 @@
       <c r="J11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00002000</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5822,7 +5849,7 @@
       <c r="D12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -5842,19 +5869,19 @@
       <c r="J12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="31" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00002000</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5862,7 +5889,7 @@
       <c r="D13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -5882,19 +5909,19 @@
       <c r="J13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00002500</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5902,7 +5929,7 @@
       <c r="D14" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E14" s="31" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -5922,19 +5949,19 @@
       <c r="J14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="31" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00002500</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5942,7 +5969,7 @@
       <c r="D15" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -5962,19 +5989,19 @@
       <c r="J15" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00005000</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -5982,7 +6009,7 @@
       <c r="D16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6002,19 +6029,19 @@
       <c r="J16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="31" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00005000</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -6022,7 +6049,7 @@
       <c r="D17" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6042,19 +6069,19 @@
       <c r="J17" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>OTLK261016C00007500</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -6062,7 +6089,7 @@
       <c r="D18" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6082,19 +6109,19 @@
       <c r="J18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="31" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>OTLK261016P00007500</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -6102,7 +6129,7 @@
       <c r="D19" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6122,19 +6149,19 @@
       <c r="J19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="K19" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00000500</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6142,39 +6169,39 @@
       <c r="D20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1725</v>
-      </c>
-      <c r="K20" s="31" t="inlineStr">
+        <v>1726</v>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00000500</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6182,7 +6209,7 @@
       <c r="D21" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E21" s="34" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6202,19 +6229,19 @@
       <c r="J21" s="14" t="n">
         <v>871</v>
       </c>
-      <c r="K21" s="34" t="inlineStr">
+      <c r="K21" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00001000</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6222,7 +6249,7 @@
       <c r="D22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6242,19 +6269,19 @@
       <c r="J22" s="8" t="n">
         <v>1611</v>
       </c>
-      <c r="K22" s="31" t="inlineStr">
+      <c r="K22" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00001000</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6262,7 +6289,7 @@
       <c r="D23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="34" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6282,19 +6309,19 @@
       <c r="J23" s="14" t="n">
         <v>358</v>
       </c>
-      <c r="K23" s="34" t="inlineStr">
+      <c r="K23" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00001500</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6302,7 +6329,7 @@
       <c r="D24" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6322,19 +6349,19 @@
       <c r="J24" s="8" t="n">
         <v>2128</v>
       </c>
-      <c r="K24" s="31" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00001500</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6342,7 +6369,7 @@
       <c r="D25" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6362,19 +6389,19 @@
       <c r="J25" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="K25" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00002000</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6382,7 +6409,7 @@
       <c r="D26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6402,19 +6429,19 @@
       <c r="J26" s="8" t="n">
         <v>1358</v>
       </c>
-      <c r="K26" s="31" t="inlineStr">
+      <c r="K26" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00002000</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6422,7 +6449,7 @@
       <c r="D27" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6442,19 +6469,19 @@
       <c r="J27" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00002500</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6462,7 +6489,7 @@
       <c r="D28" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6482,19 +6509,19 @@
       <c r="J28" s="8" t="n">
         <v>301</v>
       </c>
-      <c r="K28" s="31" t="inlineStr">
+      <c r="K28" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00002500</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6502,7 +6529,7 @@
       <c r="D29" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6522,19 +6549,19 @@
       <c r="J29" s="14" t="n">
         <v>122</v>
       </c>
-      <c r="K29" s="34" t="inlineStr">
+      <c r="K29" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00005000</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6542,7 +6569,7 @@
       <c r="D30" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6562,19 +6589,19 @@
       <c r="J30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="K30" s="31" t="inlineStr">
+      <c r="K30" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00005000</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6582,7 +6609,7 @@
       <c r="D31" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6602,19 +6629,19 @@
       <c r="J31" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00007500</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6622,7 +6649,7 @@
       <c r="D32" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6642,19 +6669,19 @@
       <c r="J32" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="K32" s="31" t="inlineStr">
+      <c r="K32" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00007500</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -6662,7 +6689,7 @@
       <c r="D33" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6682,19 +6709,19 @@
       <c r="J33" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="34" t="inlineStr">
+      <c r="K33" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00000500</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6702,7 +6729,7 @@
       <c r="D34" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E34" s="31" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6722,19 +6749,19 @@
       <c r="J34" s="8" t="n">
         <v>9837</v>
       </c>
-      <c r="K34" s="31" t="inlineStr">
+      <c r="K34" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00000500</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6742,7 +6769,7 @@
       <c r="D35" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6762,19 +6789,19 @@
       <c r="J35" s="14" t="n">
         <v>2093</v>
       </c>
-      <c r="K35" s="34" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00001000</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6782,39 +6809,39 @@
       <c r="D36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6858</v>
+        <v>6877</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6858</v>
+        <v>6877</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6858</v>
+        <v>6877</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>6858</v>
-      </c>
-      <c r="K36" s="31" t="inlineStr">
+        <v>6877</v>
+      </c>
+      <c r="K36" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00001000</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6822,7 +6849,7 @@
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="34" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6842,19 +6869,19 @@
       <c r="J37" s="14" t="n">
         <v>641</v>
       </c>
-      <c r="K37" s="34" t="inlineStr">
+      <c r="K37" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00001500</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6862,7 +6889,7 @@
       <c r="D38" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="E38" s="31" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6882,19 +6909,19 @@
       <c r="J38" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="K38" s="31" t="inlineStr">
+      <c r="K38" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="38" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00001500</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6902,7 +6929,7 @@
       <c r="D39" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="E39" s="34" t="inlineStr">
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -6922,19 +6949,19 @@
       <c r="J39" s="14" t="n">
         <v>455</v>
       </c>
-      <c r="K39" s="34" t="inlineStr">
+      <c r="K39" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00002000</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6942,7 +6969,7 @@
       <c r="D40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="31" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -6962,19 +6989,19 @@
       <c r="J40" s="8" t="n">
         <v>2815</v>
       </c>
-      <c r="K40" s="31" t="inlineStr">
+      <c r="K40" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00002000</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -6982,7 +7009,7 @@
       <c r="D41" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="34" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7002,19 +7029,19 @@
       <c r="J41" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="K41" s="34" t="inlineStr">
+      <c r="K41" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00002500</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7022,7 +7049,7 @@
       <c r="D42" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E42" s="31" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7042,19 +7069,19 @@
       <c r="J42" s="8" t="n">
         <v>3053</v>
       </c>
-      <c r="K42" s="31" t="inlineStr">
+      <c r="K42" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00002500</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7062,7 +7089,7 @@
       <c r="D43" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="E43" s="34" t="inlineStr">
+      <c r="E43" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7082,19 +7109,19 @@
       <c r="J43" s="14" t="n">
         <v>153</v>
       </c>
-      <c r="K43" s="34" t="inlineStr">
+      <c r="K43" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00005000</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7102,7 +7129,7 @@
       <c r="D44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="31" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7122,59 +7149,59 @@
       <c r="J44" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="K44" s="31" t="inlineStr">
+      <c r="K44" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>OTLK270115P00005000</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D45" s="41" t="n">
+      <c r="D45" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="40" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F45" s="42" t="n">
+      <c r="F45" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="G45" s="42" t="n">
+      <c r="G45" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="H45" s="42" t="n">
+      <c r="H45" s="38" t="n">
         <v>30</v>
       </c>
-      <c r="I45" s="42" t="n">
+      <c r="I45" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="42" t="n">
+      <c r="J45" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="K45" s="40" t="inlineStr">
+      <c r="K45" s="36" t="inlineStr">
         <is>
           <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00007500</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7182,7 +7209,7 @@
       <c r="D46" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E46" s="31" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7202,19 +7229,19 @@
       <c r="J46" s="8" t="n">
         <v>252</v>
       </c>
-      <c r="K46" s="31" t="inlineStr">
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="38" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00007500</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7222,7 +7249,7 @@
       <c r="D47" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="E47" s="34" t="inlineStr">
+      <c r="E47" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7242,19 +7269,19 @@
       <c r="J47" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K47" s="34" t="inlineStr">
+      <c r="K47" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00010000</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7262,7 +7289,7 @@
       <c r="D48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="E48" s="31" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7282,19 +7309,19 @@
       <c r="J48" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="K48" s="31" t="inlineStr">
+      <c r="K48" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="38" t="inlineStr">
+      <c r="B49" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00010000</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7302,7 +7329,7 @@
       <c r="D49" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="E49" s="34" t="inlineStr">
+      <c r="E49" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7322,19 +7349,19 @@
       <c r="J49" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="K49" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="37" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00012500</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7342,7 +7369,7 @@
       <c r="D50" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="E50" s="31" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7362,19 +7389,19 @@
       <c r="J50" s="8" t="n">
         <v>439</v>
       </c>
-      <c r="K50" s="31" t="inlineStr">
+      <c r="K50" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="38" t="inlineStr">
+      <c r="B51" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00012500</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C51" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
@@ -7382,7 +7409,7 @@
       <c r="D51" s="16" t="n">
         <v>12.5</v>
       </c>
-      <c r="E51" s="34" t="inlineStr">
+      <c r="E51" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7402,19 +7429,19 @@
       <c r="J51" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="34" t="inlineStr">
+      <c r="K51" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00000500</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7422,39 +7449,39 @@
       <c r="D52" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E52" s="31" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>2569</v>
-      </c>
-      <c r="K52" s="31" t="inlineStr">
+        <v>2554</v>
+      </c>
+      <c r="K52" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="38" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00000500</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7462,7 +7489,7 @@
       <c r="D53" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E53" s="34" t="inlineStr">
+      <c r="E53" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7482,19 +7509,19 @@
       <c r="J53" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K53" s="34" t="inlineStr">
+      <c r="K53" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00001000</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7502,7 +7529,7 @@
       <c r="D54" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="31" t="inlineStr">
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7522,19 +7549,19 @@
       <c r="J54" s="8" t="n">
         <v>6384</v>
       </c>
-      <c r="K54" s="31" t="inlineStr">
+      <c r="K54" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="38" t="inlineStr">
+      <c r="B55" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00001000</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7542,7 +7569,7 @@
       <c r="D55" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="34" t="inlineStr">
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7562,19 +7589,19 @@
       <c r="J55" s="14" t="n">
         <v>151</v>
       </c>
-      <c r="K55" s="34" t="inlineStr">
+      <c r="K55" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="37" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00001500</t>
         </is>
       </c>
-      <c r="C56" s="31" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7582,7 +7609,7 @@
       <c r="D56" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="E56" s="31" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7602,19 +7629,19 @@
       <c r="J56" s="8" t="n">
         <v>5582</v>
       </c>
-      <c r="K56" s="31" t="inlineStr">
+      <c r="K56" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="38" t="inlineStr">
+      <c r="B57" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00001500</t>
         </is>
       </c>
-      <c r="C57" s="34" t="inlineStr">
+      <c r="C57" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7622,7 +7649,7 @@
       <c r="D57" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="E57" s="34" t="inlineStr">
+      <c r="E57" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7642,19 +7669,19 @@
       <c r="J57" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="34" t="inlineStr">
+      <c r="K57" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="37" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00002000</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7662,7 +7689,7 @@
       <c r="D58" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="31" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7682,19 +7709,19 @@
       <c r="J58" s="8" t="n">
         <v>1071</v>
       </c>
-      <c r="K58" s="31" t="inlineStr">
+      <c r="K58" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="38" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00002000</t>
         </is>
       </c>
-      <c r="C59" s="34" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7702,7 +7729,7 @@
       <c r="D59" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="34" t="inlineStr">
+      <c r="E59" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7722,19 +7749,19 @@
       <c r="J59" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="K59" s="34" t="inlineStr">
+      <c r="K59" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="37" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00002500</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7742,7 +7769,7 @@
       <c r="D60" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E60" s="31" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7762,19 +7789,19 @@
       <c r="J60" s="8" t="n">
         <v>848</v>
       </c>
-      <c r="K60" s="31" t="inlineStr">
+      <c r="K60" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="38" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00002500</t>
         </is>
       </c>
-      <c r="C61" s="34" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7782,7 +7809,7 @@
       <c r="D61" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="E61" s="34" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7802,19 +7829,19 @@
       <c r="J61" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="34" t="inlineStr">
+      <c r="K61" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="37" t="inlineStr">
+      <c r="B62" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00005000</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7822,7 +7849,7 @@
       <c r="D62" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E62" s="31" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7842,19 +7869,19 @@
       <c r="J62" s="8" t="n">
         <v>732</v>
       </c>
-      <c r="K62" s="31" t="inlineStr">
+      <c r="K62" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="38" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00005000</t>
         </is>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7862,7 +7889,7 @@
       <c r="D63" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E63" s="34" t="inlineStr">
+      <c r="E63" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7882,19 +7909,19 @@
       <c r="J63" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="34" t="inlineStr">
+      <c r="K63" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="37" t="inlineStr">
+      <c r="B64" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00007500</t>
         </is>
       </c>
-      <c r="C64" s="31" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7902,7 +7929,7 @@
       <c r="D64" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E64" s="31" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -7922,19 +7949,19 @@
       <c r="J64" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="K64" s="31" t="inlineStr">
+      <c r="K64" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="38" t="inlineStr">
+      <c r="B65" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00007500</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -7942,7 +7969,7 @@
       <c r="D65" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="E65" s="34" t="inlineStr">
+      <c r="E65" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -7962,19 +7989,19 @@
       <c r="J65" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K65" s="34" t="inlineStr">
+      <c r="K65" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="37" t="inlineStr">
+      <c r="B66" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00000500</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -7982,7 +8009,7 @@
       <c r="D66" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" s="31" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8002,19 +8029,19 @@
       <c r="J66" s="8" t="n">
         <v>336</v>
       </c>
-      <c r="K66" s="31" t="inlineStr">
+      <c r="K66" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="38" t="inlineStr">
+      <c r="B67" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00000500</t>
         </is>
       </c>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8022,16 +8049,16 @@
       <c r="D67" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" s="34" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="14" t="n">
         <v>0</v>
@@ -8040,21 +8067,21 @@
         <v>0</v>
       </c>
       <c r="J67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="34" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="37" t="inlineStr">
+      <c r="B68" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00001000</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8062,16 +8089,16 @@
       <c r="D68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="31" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>0</v>
@@ -8080,21 +8107,21 @@
         <v>0</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="K68" s="31" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="K68" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="38" t="inlineStr">
+      <c r="B69" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00001000</t>
         </is>
       </c>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8102,7 +8129,7 @@
       <c r="D69" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="34" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8122,19 +8149,19 @@
       <c r="J69" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K69" s="34" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="37" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00001500</t>
         </is>
       </c>
-      <c r="C70" s="31" t="inlineStr">
+      <c r="C70" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8142,7 +8169,7 @@
       <c r="D70" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="E70" s="31" t="inlineStr">
+      <c r="E70" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8162,19 +8189,19 @@
       <c r="J70" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="31" t="inlineStr">
+      <c r="K70" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="38" t="inlineStr">
+      <c r="B71" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00001500</t>
         </is>
       </c>
-      <c r="C71" s="34" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8182,7 +8209,7 @@
       <c r="D71" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="E71" s="34" t="inlineStr">
+      <c r="E71" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8202,19 +8229,19 @@
       <c r="J71" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="34" t="inlineStr">
+      <c r="K71" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="37" t="inlineStr">
+      <c r="B72" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00002000</t>
         </is>
       </c>
-      <c r="C72" s="31" t="inlineStr">
+      <c r="C72" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8222,7 +8249,7 @@
       <c r="D72" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="31" t="inlineStr">
+      <c r="E72" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8242,19 +8269,19 @@
       <c r="J72" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="K72" s="31" t="inlineStr">
+      <c r="K72" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="38" t="inlineStr">
+      <c r="B73" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00002000</t>
         </is>
       </c>
-      <c r="C73" s="34" t="inlineStr">
+      <c r="C73" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8262,7 +8289,7 @@
       <c r="D73" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E73" s="34" t="inlineStr">
+      <c r="E73" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8282,19 +8309,19 @@
       <c r="J73" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="34" t="inlineStr">
+      <c r="K73" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="37" t="inlineStr">
+      <c r="B74" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00002500</t>
         </is>
       </c>
-      <c r="C74" s="31" t="inlineStr">
+      <c r="C74" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8302,7 +8329,7 @@
       <c r="D74" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E74" s="31" t="inlineStr">
+      <c r="E74" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8322,19 +8349,19 @@
       <c r="J74" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="K74" s="31" t="inlineStr">
+      <c r="K74" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="38" t="inlineStr">
+      <c r="B75" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00002500</t>
         </is>
       </c>
-      <c r="C75" s="34" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8342,7 +8369,7 @@
       <c r="D75" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="E75" s="34" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8362,19 +8389,19 @@
       <c r="J75" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K75" s="34" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="37" t="inlineStr">
+      <c r="B76" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00005000</t>
         </is>
       </c>
-      <c r="C76" s="31" t="inlineStr">
+      <c r="C76" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8382,7 +8409,7 @@
       <c r="D76" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="31" t="inlineStr">
+      <c r="E76" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8402,19 +8429,19 @@
       <c r="J76" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="K76" s="31" t="inlineStr">
+      <c r="K76" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="38" t="inlineStr">
+      <c r="B77" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00005000</t>
         </is>
       </c>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8422,7 +8449,7 @@
       <c r="D77" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E77" s="34" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8442,19 +8469,19 @@
       <c r="J77" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="34" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="37" t="inlineStr">
+      <c r="B78" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00007500</t>
         </is>
       </c>
-      <c r="C78" s="31" t="inlineStr">
+      <c r="C78" s="27" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8462,7 +8489,7 @@
       <c r="D78" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E78" s="31" t="inlineStr">
+      <c r="E78" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
@@ -8482,19 +8509,19 @@
       <c r="J78" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="K78" s="31" t="inlineStr">
+      <c r="K78" s="27" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="38" t="inlineStr">
+      <c r="B79" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00007500</t>
         </is>
       </c>
-      <c r="C79" s="34" t="inlineStr">
+      <c r="C79" s="30" t="inlineStr">
         <is>
           <t>2027-05-21</t>
         </is>
@@ -8502,7 +8529,7 @@
       <c r="D79" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="E79" s="34" t="inlineStr">
+      <c r="E79" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -8522,7 +8549,7 @@
       <c r="J79" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K79" s="34" t="inlineStr">
+      <c r="K79" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 08:42 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 15/10/2026 08:53 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 08:53 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 15/10/2026 10:35 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -361,7 +361,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6858000" cy="3238500"/>
@@ -389,7 +389,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6858000" cy="3238500"/>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 10:35 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 15/10/2026 15:42 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
         </is>
       </c>
     </row>
@@ -975,80 +975,80 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27300</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>3364</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.2038</v>
+        <v>1.2</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>904865</v>
+        <v>0</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Heavy call skew 🟢🟢</t>
+          <t>NO DATA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17203</v>
+        <v>27300</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>197</v>
+        <v>3364</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.011</v>
+        <v>0.123</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>133</v>
+        <v>444</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="J19" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>2.0133</v>
+        <v>1.2038</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>624383</v>
+        <v>904865</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1059,50 +1059,92 @@
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>534</v>
+        <v>17203</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>9.99</v>
+        <v>0</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
+        <v>2.0133</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>624383</v>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Heavy call skew 🟢🟢</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>218</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>534</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L21" s="18" t="n">
         <v>29612</v>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>3. CHARTS</t>
         </is>
@@ -1120,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2096,7 +2138,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (92 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-12-18 (64 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2189,358 +2231,358 @@
     </row>
     <row r="29">
       <c r="B29" s="17" t="n">
-        <v>1.0584</v>
+        <v>1.2</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.636</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.2858</v>
+        <v>1.6718</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>9837</v>
+        <v>0</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J29" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="K29" s="23" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="23" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="N29" s="24" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="O29" s="24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P29" s="25" t="n">
-        <v>1.3166</v>
+        <v>1.6718</v>
       </c>
       <c r="Q29" s="25" t="n">
-        <v>-0.397</v>
+        <v>-0.443</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>1.2345</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.5306</v>
+        <v>1.2</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.352</v>
+        <v>0.108</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.9347</v>
+        <v>0.7873</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6877</v>
+        <v>0</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M30" s="23" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="N30" s="24" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="O30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="25" t="n">
-        <v>0.9813</v>
+        <v>0.7873</v>
       </c>
       <c r="Q30" s="25" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.892</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.6018</v>
+        <v>1.2</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.267</v>
+        <v>0.021</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.7134</v>
+        <v>0.2098</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J31" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M31" s="23" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="N31" s="24" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="O31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>0.771</v>
+        <v>0.2098</v>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>-0.779</v>
+        <v>-0.98</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>3.8267</v>
+        <v>1.2</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.225</v>
+        <v>0.004</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5948</v>
+        <v>0.0553</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>2815</v>
+        <v>0</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M32" s="23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>0.6633</v>
+        <v>0.0553</v>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>-0.825</v>
+        <v>-0.996</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.9997</v>
+        <v>1.2</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.2</v>
+        <v>0.001</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.0157</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M33" s="23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>0.5951</v>
+        <v>0.0157</v>
       </c>
       <c r="Q33" s="25" t="n">
-        <v>-0.855</v>
+        <v>-0.999</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>4.3589</v>
+        <v>1.2</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.3602</v>
+        <v>0.0001</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="J34" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M34" s="23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>-0.93</v>
+        <v>-1</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>7.0313</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.6704</v>
+        <v>1.2</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2984</v>
+        <v>0</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="J35" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M35" s="23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N35" s="24" t="n">
         <v>0</v>
@@ -2549,341 +2591,341 @@
         <v>0</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>0.4323</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="25" t="n">
-        <v>-0.969</v>
+        <v>-1</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>7.3125</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="17" t="n">
-        <v>3.0429</v>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>0.2638</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>55</v>
-      </c>
-      <c r="G36" s="16" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRATION: 2027-01-15 (92 days) — Max Pain: $0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>CALLS — IV</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>OI</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>STRIKE</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="M39" s="21" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="inlineStr">
+        <is>
+          <t>OI</t>
+        </is>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="P39" s="21" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Q39" s="21" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="R39" s="21" t="inlineStr">
+        <is>
+          <t>PUTS — IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="17" t="n">
+        <v>1.0584</v>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>1.2858</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>332</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>9837</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H40" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="H36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="16" t="n">
+      <c r="I40" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K40" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="J36" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L36" s="23" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N36" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="25" t="n">
-        <v>0.1623</v>
-      </c>
-      <c r="Q36" s="25" t="n">
-        <v>-0.988</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>6.0313</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="17" t="n">
-        <v>3.1876</v>
-      </c>
-      <c r="C37" s="15" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>439</v>
-      </c>
-      <c r="G37" s="16" t="n">
+      <c r="L40" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M40" s="23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>2093</v>
+      </c>
+      <c r="O40" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P40" s="25" t="n">
+        <v>1.3166</v>
+      </c>
+      <c r="Q40" s="25" t="n">
+        <v>-0.397</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>1.2345</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="17" t="n">
+        <v>1.5306</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>0.9347</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>6877</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="H37" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J37" s="22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L37" s="23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M37" s="23" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="N37" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="25" t="n">
-        <v>0.0316</v>
-      </c>
-      <c r="Q37" s="25" t="n">
-        <v>-0.998</v>
-      </c>
-      <c r="R37" s="26" t="n">
-        <v>7.6563</v>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRATION: 2027-02-19 (127 days) — Max Pain: $0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>CALLS — IV</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="J41" s="20" t="inlineStr">
-        <is>
-          <t>STRIKE</t>
-        </is>
-      </c>
-      <c r="K41" s="21" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="N41" s="21" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="O41" s="21" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="P41" s="21" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="Q41" s="21" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="R41" s="21" t="inlineStr">
-        <is>
-          <t>PUTS — IV</t>
-        </is>
+      <c r="J41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L41" s="23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M41" s="23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N41" s="24" t="n">
+        <v>641</v>
+      </c>
+      <c r="O41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="25" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="Q41" s="25" t="n">
+        <v>-0.6879999999999999</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="17" t="n">
-        <v>1.7549</v>
+        <v>1.6018</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.643</v>
+        <v>0.267</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.8254</v>
+        <v>0.7134</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>2554</v>
+        <v>1986</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>0.95</v>
+        <v>1.3</v>
       </c>
       <c r="M42" s="23" t="n">
-        <v>0.11</v>
+        <v>0.97</v>
       </c>
       <c r="N42" s="24" t="n">
-        <v>4</v>
+        <v>455</v>
       </c>
       <c r="O42" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="25" t="n">
-        <v>0.8142</v>
+        <v>0.771</v>
       </c>
       <c r="Q42" s="25" t="n">
-        <v>-0.336</v>
+        <v>-0.779</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>6.8935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>2.0918</v>
+        <v>3.8267</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.392</v>
+        <v>0.225</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.7935</v>
+        <v>0.5948</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6384</v>
+        <v>2815</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="23" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="O43" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="25" t="n">
-        <v>0.8153</v>
+        <v>0.6633</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>-0.588</v>
+        <v>-0.825</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.3774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>2.2346</v>
+        <v>2.9997</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.297</v>
+        <v>0.2</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.655</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>5582</v>
+        <v>3053</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>0</v>
@@ -2892,28 +2934,28 @@
         <v>0.2</v>
       </c>
       <c r="J44" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L44" s="23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M44" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="K44" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L44" s="23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M44" s="23" t="n">
-        <v>1.02</v>
-      </c>
       <c r="N44" s="24" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="O44" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="25" t="n">
-        <v>0.701</v>
+        <v>0.5951</v>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.855</v>
       </c>
       <c r="R44" s="26" t="n">
         <v>0</v>
@@ -2921,75 +2963,75 @@
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>2.2288</v>
+        <v>4.3589</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.248</v>
+        <v>0.146</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5626</v>
+        <v>0.3602</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1071</v>
+        <v>1986</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="M45" s="23" t="n">
-        <v>1.35</v>
+        <v>3.8</v>
       </c>
       <c r="N45" s="24" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="O45" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="25" t="n">
-        <v>0.6299</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="Q45" s="25" t="n">
-        <v>-0.745</v>
+        <v>-0.93</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>0</v>
+        <v>7.0313</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>3.3376</v>
+        <v>4.6704</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.217</v>
+        <v>0.125</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4992</v>
+        <v>0.2984</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>848</v>
+        <v>252</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H46" s="16" t="n">
         <v>0</v>
@@ -2998,16 +3040,16 @@
         <v>0.35</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>1.45</v>
+        <v>6.4</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>2.45</v>
+        <v>7.4</v>
       </c>
       <c r="M46" s="23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N46" s="24" t="n">
         <v>0</v>
@@ -3016,30 +3058,30 @@
         <v>0</v>
       </c>
       <c r="P46" s="25" t="n">
-        <v>0.5865</v>
+        <v>0.4323</v>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>-0.782</v>
+        <v>-0.969</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>1.2</v>
+        <v>7.3125</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.5498</v>
+        <v>3.0429</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.149</v>
+        <v>0.113</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3472</v>
+        <v>0.2638</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>0.05</v>
@@ -3048,19 +3090,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>2.75</v>
+        <v>8.9</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>6.2</v>
+        <v>9.9</v>
       </c>
       <c r="M47" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N47" s="24" t="n">
         <v>0</v>
@@ -3069,51 +3111,51 @@
         <v>0</v>
       </c>
       <c r="P47" s="25" t="n">
-        <v>0.5105</v>
+        <v>0.1623</v>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>-0.883</v>
+        <v>-0.988</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>1.2</v>
+        <v>6.0313</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>6.4145</v>
+        <v>3.1876</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.122</v>
+        <v>0.105</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2832</v>
+        <v>0.241</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="G48" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="H48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="16" t="n">
-        <v>0.75</v>
-      </c>
       <c r="J48" s="22" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="M48" s="23" t="n">
-        <v>0</v>
+        <v>10.94</v>
       </c>
       <c r="N48" s="24" t="n">
         <v>0</v>
@@ -3122,13 +3164,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="25" t="n">
-        <v>0.5305</v>
+        <v>0.0316</v>
       </c>
       <c r="Q48" s="25" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.998</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>1.2</v>
+        <v>7.6563</v>
       </c>
     </row>
     <row r="49"/>
@@ -3136,7 +3178,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (218 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (127 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3229,28 +3271,28 @@
     </row>
     <row r="53">
       <c r="B53" s="17" t="n">
-        <v>4.9398</v>
+        <v>1.7549</v>
       </c>
       <c r="C53" s="15" t="n">
-        <v>0.709</v>
+        <v>0.643</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>1.0437</v>
+        <v>0.8254</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>336</v>
+        <v>2554</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H53" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J53" s="22" t="n">
         <v>0.5</v>
@@ -3259,219 +3301,219 @@
         <v>0</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M53" s="23" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="25" t="n">
-        <v>1.1063</v>
+        <v>0.8142</v>
       </c>
       <c r="Q53" s="25" t="n">
-        <v>-0.364</v>
+        <v>-0.336</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>1.2</v>
+        <v>6.8935</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>2.1162</v>
+        <v>2.0918</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.42</v>
+        <v>0.392</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.9432</v>
+        <v>0.7935</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>76</v>
+        <v>6384</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J54" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="23" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M54" s="23" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="N54" s="24" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="O54" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="25" t="n">
-        <v>1.0711</v>
+        <v>0.8153</v>
       </c>
       <c r="Q54" s="25" t="n">
-        <v>-0.676</v>
+        <v>-0.588</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>1.0435</v>
+        <v>1.3774</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>2.5795</v>
+        <v>2.2346</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.7506</v>
+        <v>0.655</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>1</v>
+        <v>5582</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="H55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J55" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M55" s="23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N55" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="25" t="n">
-        <v>0.9038</v>
+        <v>0.701</v>
       </c>
       <c r="Q55" s="25" t="n">
-        <v>-0.774</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>2.4288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>7.7388</v>
+        <v>2.2288</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.293</v>
+        <v>0.248</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.6444</v>
+        <v>0.5626</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>64</v>
+        <v>1071</v>
       </c>
       <c r="G56" s="16" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="J56" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K56" s="23" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M56" s="23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="N56" s="24" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O56" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="25" t="n">
-        <v>0.82</v>
+        <v>0.6299</v>
       </c>
       <c r="Q56" s="25" t="n">
-        <v>-0.827</v>
+        <v>-0.745</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>2.6568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>3.9533</v>
+        <v>3.3376</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.267</v>
+        <v>0.217</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5768</v>
+        <v>0.4992</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="J57" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>0.2</v>
+        <v>1.45</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="M57" s="23" t="n">
         <v>0</v>
@@ -3483,30 +3525,30 @@
         <v>0</v>
       </c>
       <c r="P57" s="25" t="n">
-        <v>0.7673</v>
+        <v>0.5865</v>
       </c>
       <c r="Q57" s="25" t="n">
-        <v>-0.864</v>
+        <v>-0.782</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>6.058</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>1.6403</v>
+        <v>4.5498</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.205</v>
+        <v>0.149</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.4224</v>
+        <v>0.3472</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="G58" s="16" t="n">
         <v>0.05</v>
@@ -3515,16 +3557,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="J58" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="23" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="M58" s="23" t="n">
         <v>0</v>
@@ -3536,65 +3578,532 @@
         <v>0</v>
       </c>
       <c r="P58" s="25" t="n">
-        <v>0.4866</v>
+        <v>0.5105</v>
       </c>
       <c r="Q58" s="25" t="n">
-        <v>-0.967</v>
+        <v>-0.883</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>2.2485</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>2.0936</v>
+        <v>6.4145</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.177</v>
+        <v>0.122</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3577</v>
+        <v>0.2832</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G59" s="16" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="H59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="J59" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K59" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L59" s="23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M59" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="25" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="Q59" s="25" t="n">
+        <v>-0.9419999999999999</v>
+      </c>
+      <c r="R59" s="26" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRATION: 2027-05-21 (218 days) — Max Pain: $0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>CALLS — IV</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>OI</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
+        <is>
+          <t>STRIKE</t>
+        </is>
+      </c>
+      <c r="K63" s="21" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="L63" s="21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="M63" s="21" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="N63" s="21" t="inlineStr">
+        <is>
+          <t>OI</t>
+        </is>
+      </c>
+      <c r="O63" s="21" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="P63" s="21" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Q63" s="21" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="R63" s="21" t="inlineStr">
+        <is>
+          <t>PUTS — IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="17" t="n">
+        <v>4.9398</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>1.0437</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>336</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J64" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N64" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O64" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="25" t="n">
+        <v>1.1063</v>
+      </c>
+      <c r="Q64" s="25" t="n">
+        <v>-0.364</v>
+      </c>
+      <c r="R64" s="26" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="17" t="n">
+        <v>2.1162</v>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J65" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L65" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M65" s="23" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N65" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="25" t="n">
+        <v>1.0711</v>
+      </c>
+      <c r="Q65" s="25" t="n">
+        <v>-0.676</v>
+      </c>
+      <c r="R65" s="26" t="n">
+        <v>1.0435</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="17" t="n">
+        <v>2.5795</v>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>0.7506</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J66" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K66" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L66" s="23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M66" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="25" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="Q66" s="25" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="R66" s="26" t="n">
+        <v>2.4288</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="17" t="n">
+        <v>7.7388</v>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D67" s="15" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L67" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M67" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q67" s="25" t="n">
+        <v>-0.827</v>
+      </c>
+      <c r="R67" s="26" t="n">
+        <v>2.6568</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="17" t="n">
+        <v>3.9533</v>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D68" s="15" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J68" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K68" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L68" s="23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="25" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="Q68" s="25" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>6.058</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="17" t="n">
+        <v>1.6403</v>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="D69" s="15" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J69" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L69" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="25" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="Q69" s="25" t="n">
+        <v>-0.967</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>2.2485</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="17" t="n">
+        <v>2.0936</v>
+      </c>
+      <c r="C70" s="15" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J70" s="22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K70" s="23" t="n">
         <v>4.5</v>
       </c>
-      <c r="L59" s="23" t="n">
+      <c r="L70" s="23" t="n">
         <v>9.4</v>
       </c>
-      <c r="M59" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="25" t="n">
+      <c r="M70" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="R59" s="26" t="n">
+      <c r="R70" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5511,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5621,7 +6130,7 @@
         <v>232</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>232</v>
@@ -5661,7 +6170,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>6</v>
@@ -5701,7 +6210,7 @@
         <v>154</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>154</v>
@@ -5741,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>1</v>
@@ -5901,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>1</v>
@@ -6156,42 +6665,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>OTLK261120C00000500</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="37" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="38" t="n">
         <v>1726</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="38" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>1728</v>
+      </c>
+      <c r="I20" s="38" t="n">
+        <v>1728</v>
+      </c>
+      <c r="J20" s="38" t="n">
         <v>1726</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>1726</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>1726</v>
-      </c>
-      <c r="K20" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K20" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6730,7 @@
         <v>871</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>871</v>
@@ -6261,7 +6770,7 @@
         <v>1611</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>1611</v>
@@ -6301,7 +6810,7 @@
         <v>358</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>358</v>
@@ -6341,7 +6850,7 @@
         <v>2128</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>2128</v>
@@ -6381,7 +6890,7 @@
         <v>150</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>150</v>
@@ -6421,7 +6930,7 @@
         <v>1358</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>1358</v>
@@ -6436,42 +6945,42 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>OTLK261120P00002000</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="38" t="n">
         <v>90</v>
       </c>
-      <c r="G27" s="14" t="n">
+      <c r="G27" s="38" t="n">
+        <v>78</v>
+      </c>
+      <c r="H27" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="38" t="n">
+        <v>78</v>
+      </c>
+      <c r="J27" s="38" t="n">
         <v>90</v>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="K27" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K27" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
@@ -6718,12 +7227,12 @@
     <row r="34">
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00000500</t>
+          <t>OTLK_2026-12-18_C_0.5</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
@@ -6735,19 +7244,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>9837</v>
+        <v>0</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>9837</v>
+        <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>9837</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>9837</v>
+        <v>0</v>
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
@@ -6758,12 +7267,12 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00000500</t>
+          <t>OTLK_2026-12-18_P_0.5</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
@@ -6775,19 +7284,19 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
@@ -6798,12 +7307,12 @@
     <row r="36">
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00001000</t>
+          <t>OTLK_2026-12-18_C_1.0</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -6815,19 +7324,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6877</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6877</v>
+        <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6877</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>6877</v>
+        <v>0</v>
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
@@ -6838,12 +7347,12 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001000</t>
+          <t>OTLK_2026-12-18_P_1.0</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
@@ -6855,19 +7364,19 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="H37" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
@@ -6878,12 +7387,12 @@
     <row r="38">
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00001500</t>
+          <t>OTLK_2026-12-18_C_1.5</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -6895,19 +7404,19 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="K38" s="27" t="inlineStr">
         <is>
@@ -6918,12 +7427,12 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001500</t>
+          <t>OTLK_2026-12-18_P_1.5</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
@@ -6935,19 +7444,19 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="H39" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="K39" s="30" t="inlineStr">
         <is>
@@ -6958,12 +7467,12 @@
     <row r="40">
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00002000</t>
+          <t>OTLK_2026-12-18_C_2.0</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -6975,19 +7484,19 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2815</v>
+        <v>0</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>2815</v>
+        <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>2815</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>2815</v>
+        <v>0</v>
       </c>
       <c r="K40" s="27" t="inlineStr">
         <is>
@@ -6998,12 +7507,12 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002000</t>
+          <t>OTLK_2026-12-18_P_2.0</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
@@ -7015,19 +7524,19 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K41" s="30" t="inlineStr">
         <is>
@@ -7038,12 +7547,12 @@
     <row r="42">
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00002500</t>
+          <t>OTLK_2026-12-18_C_2.5</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
@@ -7055,19 +7564,19 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="K42" s="27" t="inlineStr">
         <is>
@@ -7078,12 +7587,12 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002500</t>
+          <t>OTLK_2026-12-18_P_2.5</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D43" s="16" t="n">
@@ -7095,19 +7604,19 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="H43" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="K43" s="30" t="inlineStr">
         <is>
@@ -7118,12 +7627,12 @@
     <row r="44">
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00005000</t>
+          <t>OTLK_2026-12-18_C_5.0</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
@@ -7135,19 +7644,19 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="K44" s="27" t="inlineStr">
         <is>
@@ -7156,54 +7665,54 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115P00005000</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="n">
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>OTLK_2026-12-18_P_5.0</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="36" t="inlineStr">
+      <c r="E45" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00007500</t>
+          <t>OTLK_2026-12-18_C_7.5</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -7215,19 +7724,19 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="K46" s="27" t="inlineStr">
         <is>
@@ -7238,12 +7747,12 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00007500</t>
+          <t>OTLK_2026-12-18_P_7.5</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
@@ -7276,49 +7785,49 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270115C00010000</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115C00000500</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" s="27" t="inlineStr">
+      <c r="D48" s="37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E48" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="H48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J48" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="K48" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F48" s="38" t="n">
+        <v>9837</v>
+      </c>
+      <c r="G48" s="38" t="n">
+        <v>10046</v>
+      </c>
+      <c r="H48" s="38" t="n">
+        <v>10046</v>
+      </c>
+      <c r="I48" s="38" t="n">
+        <v>10046</v>
+      </c>
+      <c r="J48" s="38" t="n">
+        <v>9837</v>
+      </c>
+      <c r="K48" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00010000</t>
+          <t>OTLK270115P00000500</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
@@ -7327,7 +7836,7 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -7335,19 +7844,19 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="K49" s="30" t="inlineStr">
         <is>
@@ -7356,49 +7865,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270115C00012500</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115C00001000</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E50" s="27" t="inlineStr">
+      <c r="D50" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>439</v>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>439</v>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>439</v>
-      </c>
-      <c r="J50" s="8" t="n">
-        <v>439</v>
-      </c>
-      <c r="K50" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F50" s="38" t="n">
+        <v>6877</v>
+      </c>
+      <c r="G50" s="38" t="n">
+        <v>6791</v>
+      </c>
+      <c r="H50" s="38" t="n">
+        <v>6791</v>
+      </c>
+      <c r="I50" s="38" t="n">
+        <v>6791</v>
+      </c>
+      <c r="J50" s="38" t="n">
+        <v>6877</v>
+      </c>
+      <c r="K50" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00012500</t>
+          <t>OTLK270115P00001000</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
@@ -7407,7 +7916,7 @@
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -7415,19 +7924,19 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="J51" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="K51" s="30" t="inlineStr">
         <is>
@@ -7438,16 +7947,16 @@
     <row r="52">
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00000500</t>
+          <t>OTLK270115C00001500</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
@@ -7455,19 +7964,19 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2554</v>
+        <v>1986</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2554</v>
+        <v>1986</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>2554</v>
+        <v>1986</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>2554</v>
+        <v>1986</v>
       </c>
       <c r="K52" s="27" t="inlineStr">
         <is>
@@ -7478,16 +7987,16 @@
     <row r="53">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00000500</t>
+          <t>OTLK270115P00001500</t>
         </is>
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
@@ -7495,19 +8004,19 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>4</v>
+        <v>455</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>4</v>
+        <v>455</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>4</v>
+        <v>455</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>4</v>
+        <v>455</v>
       </c>
       <c r="K53" s="30" t="inlineStr">
         <is>
@@ -7516,58 +8025,58 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270219C00001000</t>
-        </is>
-      </c>
-      <c r="C54" s="27" t="inlineStr">
-        <is>
-          <t>2027-02-19</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="27" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115C00002000</t>
+        </is>
+      </c>
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D54" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n">
-        <v>6384</v>
-      </c>
-      <c r="G54" s="8" t="n">
-        <v>6384</v>
-      </c>
-      <c r="H54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>6384</v>
-      </c>
-      <c r="J54" s="8" t="n">
-        <v>6384</v>
-      </c>
-      <c r="K54" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F54" s="38" t="n">
+        <v>2815</v>
+      </c>
+      <c r="G54" s="38" t="n">
+        <v>2820</v>
+      </c>
+      <c r="H54" s="38" t="n">
+        <v>2820</v>
+      </c>
+      <c r="I54" s="38" t="n">
+        <v>2820</v>
+      </c>
+      <c r="J54" s="38" t="n">
+        <v>2815</v>
+      </c>
+      <c r="K54" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001000</t>
+          <t>OTLK270115P00002000</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
@@ -7575,19 +8084,19 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
@@ -7598,16 +8107,16 @@
     <row r="56">
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00001500</t>
+          <t>OTLK270115C00002500</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
@@ -7615,19 +8124,19 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>5582</v>
+        <v>3053</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>5582</v>
+        <v>3053</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>5582</v>
+        <v>3053</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>5582</v>
+        <v>3053</v>
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
@@ -7638,16 +8147,16 @@
     <row r="57">
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001500</t>
+          <t>OTLK270115P00002500</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E57" s="30" t="inlineStr">
         <is>
@@ -7655,19 +8164,19 @@
         </is>
       </c>
       <c r="F57" s="14" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="H57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
@@ -7678,16 +8187,16 @@
     <row r="58">
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002000</t>
+          <t>OTLK270115C00005000</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
@@ -7695,19 +8204,19 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1071</v>
+        <v>1986</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1071</v>
+        <v>1986</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1071</v>
+        <v>1986</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1071</v>
+        <v>1986</v>
       </c>
       <c r="K58" s="27" t="inlineStr">
         <is>
@@ -7716,58 +8225,58 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270219P00002000</t>
-        </is>
-      </c>
-      <c r="C59" s="30" t="inlineStr">
-        <is>
-          <t>2027-02-19</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" s="30" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115P00005000</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D59" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" s="36" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F59" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="G59" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="H59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="K59" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F59" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002500</t>
+          <t>OTLK270115C00007500</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
@@ -7775,19 +8284,19 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>848</v>
+        <v>252</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>848</v>
+        <v>252</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>848</v>
+        <v>252</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>848</v>
+        <v>252</v>
       </c>
       <c r="K60" s="27" t="inlineStr">
         <is>
@@ -7798,16 +8307,16 @@
     <row r="61">
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00002500</t>
+          <t>OTLK270115P00007500</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D61" s="16" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
@@ -7838,16 +8347,16 @@
     <row r="62">
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00005000</t>
+          <t>OTLK270115C00010000</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
@@ -7855,19 +8364,19 @@
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="K62" s="27" t="inlineStr">
         <is>
@@ -7878,16 +8387,16 @@
     <row r="63">
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00005000</t>
+          <t>OTLK270115P00010000</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D63" s="16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" s="30" t="inlineStr">
         <is>
@@ -7918,16 +8427,16 @@
     <row r="64">
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00007500</t>
+          <t>OTLK270115C00012500</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
@@ -7935,19 +8444,19 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="K64" s="27" t="inlineStr">
         <is>
@@ -7958,92 +8467,92 @@
     <row r="65">
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00007500</t>
+          <t>OTLK270115P00012500</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E65" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270219C00000500</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="inlineStr">
+        <is>
           <t>2027-02-19</t>
         </is>
       </c>
-      <c r="D65" s="16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E65" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00000500</t>
-        </is>
-      </c>
-      <c r="C66" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="n">
+      <c r="D66" s="37" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="E66" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="K66" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F66" s="38" t="n">
+        <v>2554</v>
+      </c>
+      <c r="G66" s="38" t="n">
+        <v>2525</v>
+      </c>
+      <c r="H66" s="38" t="n">
+        <v>2525</v>
+      </c>
+      <c r="I66" s="38" t="n">
+        <v>2525</v>
+      </c>
+      <c r="J66" s="38" t="n">
+        <v>2554</v>
+      </c>
+      <c r="K66" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00000500</t>
+          <t>OTLK270219P00000500</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D67" s="16" t="n">
@@ -8055,19 +8564,19 @@
         </is>
       </c>
       <c r="F67" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H67" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J67" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="30" t="inlineStr">
         <is>
@@ -8076,54 +8585,54 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00001000</t>
-        </is>
-      </c>
-      <c r="C68" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="n">
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270219C00001000</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D68" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="27" t="inlineStr">
+      <c r="E68" s="36" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="K68" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F68" s="38" t="n">
+        <v>6384</v>
+      </c>
+      <c r="G68" s="38" t="n">
+        <v>6486</v>
+      </c>
+      <c r="H68" s="38" t="n">
+        <v>6486</v>
+      </c>
+      <c r="I68" s="38" t="n">
+        <v>6486</v>
+      </c>
+      <c r="J68" s="38" t="n">
+        <v>6384</v>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00001000</t>
+          <t>OTLK270219P00001000</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D69" s="16" t="n">
@@ -8135,19 +8644,19 @@
         </is>
       </c>
       <c r="F69" s="14" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J69" s="14" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="K69" s="30" t="inlineStr">
         <is>
@@ -8158,12 +8667,12 @@
     <row r="70">
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>OTLK270521C00001500</t>
+          <t>OTLK270219C00001500</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
@@ -8175,19 +8684,19 @@
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>1</v>
+        <v>5582</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>1</v>
+        <v>5582</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>0</v>
+        <v>5582</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0</v>
+        <v>5582</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>1</v>
+        <v>5582</v>
       </c>
       <c r="K70" s="27" t="inlineStr">
         <is>
@@ -8198,12 +8707,12 @@
     <row r="71">
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00001500</t>
+          <t>OTLK270219P00001500</t>
         </is>
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D71" s="16" t="n">
@@ -8215,19 +8724,19 @@
         </is>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="30" t="inlineStr">
         <is>
@@ -8238,12 +8747,12 @@
     <row r="72">
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>OTLK270521C00002000</t>
+          <t>OTLK270219C00002000</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
@@ -8255,19 +8764,19 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>64</v>
+        <v>1071</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>64</v>
+        <v>1071</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>0</v>
+        <v>1071</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0</v>
+        <v>1071</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>64</v>
+        <v>1071</v>
       </c>
       <c r="K72" s="27" t="inlineStr">
         <is>
@@ -8278,12 +8787,12 @@
     <row r="73">
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00002000</t>
+          <t>OTLK270219P00002000</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D73" s="16" t="n">
@@ -8295,19 +8804,19 @@
         </is>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H73" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J73" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K73" s="30" t="inlineStr">
         <is>
@@ -8318,12 +8827,12 @@
     <row r="74">
       <c r="B74" s="33" t="inlineStr">
         <is>
-          <t>OTLK270521C00002500</t>
+          <t>OTLK270219C00002500</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
@@ -8335,19 +8844,19 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
       <c r="K74" s="27" t="inlineStr">
         <is>
@@ -8358,12 +8867,12 @@
     <row r="75">
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00002500</t>
+          <t>OTLK270219P00002500</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D75" s="16" t="n">
@@ -8398,12 +8907,12 @@
     <row r="76">
       <c r="B76" s="33" t="inlineStr">
         <is>
-          <t>OTLK270521C00005000</t>
+          <t>OTLK270219C00005000</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
@@ -8415,19 +8924,19 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="H76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K76" s="27" t="inlineStr">
         <is>
@@ -8438,12 +8947,12 @@
     <row r="77">
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00005000</t>
+          <t>OTLK270219P00005000</t>
         </is>
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D77" s="16" t="n">
@@ -8478,12 +8987,12 @@
     <row r="78">
       <c r="B78" s="33" t="inlineStr">
         <is>
-          <t>OTLK270521C00007500</t>
+          <t>OTLK270219C00007500</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
@@ -8495,19 +9004,19 @@
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K78" s="27" t="inlineStr">
         <is>
@@ -8518,12 +9027,12 @@
     <row r="79">
       <c r="B79" s="34" t="inlineStr">
         <is>
-          <t>OTLK270521P00007500</t>
+          <t>OTLK270219P00007500</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D79" s="16" t="n">
@@ -8550,6 +9059,566 @@
         <v>0</v>
       </c>
       <c r="K79" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00000500</t>
+        </is>
+      </c>
+      <c r="C80" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00000500</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E81" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00001000</t>
+        </is>
+      </c>
+      <c r="C82" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00001000</t>
+        </is>
+      </c>
+      <c r="C83" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K83" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00001500</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00001500</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E85" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00002000</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00002000</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00002500</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00002500</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E89" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00005000</t>
+        </is>
+      </c>
+      <c r="C90" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00005000</t>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00007500</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270521P00007500</t>
+        </is>
+      </c>
+      <c r="C93" s="30" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E93" s="30" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 15:42 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
+          <t>Updated: 15/10/2026 15:59 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0</v>
+        <v>28.625</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>7615</v>
@@ -961,7 +961,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.6297</v>
+        <v>1.5256</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>89600</v>
@@ -1345,7 +1345,7 @@
         <v>-0.652</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>0</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="8">
@@ -1398,7 +1398,7 @@
         <v>-0.998</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>0</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="9">
@@ -1504,7 +1504,7 @@
         <v>-1</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>0</v>
+        <v>28.625</v>
       </c>
     </row>
     <row r="11">
@@ -1782,7 +1782,7 @@
         <v>0.1</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I18" s="16" t="n">
         <v>0.1</v>
@@ -1865,7 +1865,7 @@
         <v>-0.787</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="20">
@@ -1918,7 +1918,7 @@
         <v>-0.86</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>0</v>
+        <v>2.6875</v>
       </c>
     </row>
     <row r="21">
@@ -2799,7 +2799,7 @@
         <v>-0.6879999999999999</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>0</v>
+        <v>1.2813</v>
       </c>
     </row>
     <row r="42">
@@ -2852,7 +2852,7 @@
         <v>-0.779</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>0</v>
+        <v>2.5938</v>
       </c>
     </row>
     <row r="43">
@@ -2905,7 +2905,7 @@
         <v>-0.825</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="44">
@@ -3011,7 +3011,7 @@
         <v>-0.93</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>7.0313</v>
+        <v>7.0625</v>
       </c>
     </row>
     <row r="46">
@@ -3117,7 +3117,7 @@
         <v>-0.988</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>6.0313</v>
+        <v>6.0625</v>
       </c>
     </row>
     <row r="48">
@@ -3170,7 +3170,7 @@
         <v>-0.998</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>7.6563</v>
+        <v>7.6875</v>
       </c>
     </row>
     <row r="49"/>
@@ -3425,7 +3425,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>0</v>
+        <v>1.4375</v>
       </c>
     </row>
     <row r="56">
@@ -3478,7 +3478,7 @@
         <v>-0.745</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>0</v>
+        <v>1.6563</v>
       </c>
     </row>
     <row r="57">

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 15:59 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
+          <t>Updated: 15/10/2026 16:04 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>28.625</v>
+        <v>29.125</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>7615</v>
@@ -961,7 +961,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>1.5256</v>
+        <v>1.6297</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>89600</v>
@@ -1345,7 +1345,7 @@
         <v>-0.652</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>24.75</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="8">
@@ -1398,7 +1398,7 @@
         <v>-0.998</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>18.25</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="9">
@@ -1504,7 +1504,7 @@
         <v>-1</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>28.625</v>
+        <v>29.125</v>
       </c>
     </row>
     <row r="11">
@@ -1865,7 +1865,7 @@
         <v>-0.787</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>1.25</v>
+        <v>1.8125</v>
       </c>
     </row>
     <row r="20">
@@ -1918,7 +1918,7 @@
         <v>-0.86</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>2.6875</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2799,7 +2799,7 @@
         <v>-0.6879999999999999</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>1.2813</v>
+        <v>1.4688</v>
       </c>
     </row>
     <row r="42">
@@ -2852,7 +2852,7 @@
         <v>-0.779</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>2.5938</v>
+        <v>2.7031</v>
       </c>
     </row>
     <row r="43">
@@ -2905,7 +2905,7 @@
         <v>-0.825</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.25</v>
+        <v>1.7813</v>
       </c>
     </row>
     <row r="44">
@@ -3011,7 +3011,7 @@
         <v>-0.93</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>7.0625</v>
+        <v>7.0938</v>
       </c>
     </row>
     <row r="46">
@@ -3064,7 +3064,7 @@
         <v>-0.969</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>7.3125</v>
+        <v>7.375</v>
       </c>
     </row>
     <row r="47">
@@ -3117,7 +3117,7 @@
         <v>-0.988</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>6.0625</v>
+        <v>6.125</v>
       </c>
     </row>
     <row r="48">
@@ -3170,7 +3170,7 @@
         <v>-0.998</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>7.6875</v>
+        <v>7.7188</v>
       </c>
     </row>
     <row r="49"/>
@@ -3425,7 +3425,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>1.4375</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="56">
@@ -3478,7 +3478,7 @@
         <v>-0.745</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>1.6563</v>
+        <v>1.8438</v>
       </c>
     </row>
     <row r="57">

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 16:04 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
+          <t>Updated: 15/10/2026 16:23 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>1.6297</v>
+        <v>1.6193</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>89600</v>
@@ -1398,7 +1398,7 @@
         <v>-0.998</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>18.875</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="9">
@@ -1918,7 +1918,7 @@
         <v>-0.86</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>3</v>
+        <v>2.9688</v>
       </c>
     </row>
     <row r="21">
@@ -2905,7 +2905,7 @@
         <v>-0.825</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.7813</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="44">
@@ -3425,7 +3425,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>1.625</v>
+        <v>1.5938</v>
       </c>
     </row>
     <row r="56">
@@ -3478,7 +3478,7 @@
         <v>-0.745</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>1.8438</v>
+        <v>1.8281</v>
       </c>
     </row>
     <row r="57">

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -355,67 +355,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6858000" cy="3238500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6858000" cy="3238500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1152,7 +1091,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -355,6 +355,67 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="3238500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="3238500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -644,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -672,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 15/10/2026 16:23 | Market session: 2026-10-14 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0 | ⚠️ Market hours: partial volume</t>
+          <t>Updated: 16/10/2026 08:04 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -692,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.4700</t>
+          <t>$0.5000</t>
         </is>
       </c>
     </row>
@@ -704,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>588 contracts</t>
+          <t>21 contracts</t>
         </is>
       </c>
     </row>
@@ -716,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.016 (call-skewed volume)</t>
+          <t>0.000 (very low volume (21 contracts): not meaningful)</t>
         </is>
       </c>
     </row>
@@ -728,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,606</t>
+          <t>52,809</t>
         </is>
       </c>
     </row>
@@ -740,7 +801,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,168</t>
+          <t>5,156</t>
         </is>
       </c>
     </row>
@@ -834,7 +895,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>397</v>
@@ -846,22 +907,22 @@
         <v>0.02</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>9.99</v>
+        <v>0</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>29.125</v>
+        <v>1.5616</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>7615</v>
+        <v>11559</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -876,34 +937,34 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7172</v>
+        <v>7174</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>1.6193</v>
+        <v>2.7475</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>89600</v>
+        <v>108926</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -914,23 +975,23 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>27428</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>3364</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>0</v>
@@ -942,52 +1003,52 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.2</v>
+        <v>2.2641</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>0</v>
+        <v>959924</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>27300</v>
+        <v>17276</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>3364</v>
+        <v>197</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.123</v>
+        <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>444</v>
+        <v>1</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="J19" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>1.2038</v>
+        <v>2.051</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>904865</v>
+        <v>647389</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -998,23 +1059,23 @@
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>127</v>
+        <v>217</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>17203</v>
+        <v>534</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>197</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0</v>
@@ -1026,10 +1087,10 @@
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>2.0133</v>
+        <v>3.2868</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>624383</v>
+        <v>30676</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1037,53 +1098,11 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>218</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>534</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>29612</v>
-      </c>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>Heavy call skew 🟢🟢</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>3. CHARTS</t>
         </is>
@@ -1091,6 +1110,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1100,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1134,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.4700 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.5000 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-10-16 (1 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-10-16 (0 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1235,13 +1255,13 @@
     </row>
     <row r="7">
       <c r="B7" s="17" t="n">
-        <v>4.2772</v>
+        <v>2.3689</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.351</v>
+        <v>0.518</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>6.7598</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>0</v>
@@ -1256,48 +1276,48 @@
         <v>0</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J7" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="23" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M7" s="23" t="n">
+      <c r="K7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M7" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="N7" s="24" t="n">
+      <c r="N7" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="25" t="n">
-        <v>6.8086</v>
-      </c>
-      <c r="Q7" s="25" t="n">
-        <v>-0.652</v>
-      </c>
-      <c r="R7" s="26" t="n">
-        <v>25.25</v>
+      <c r="O7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>9.183999999999999</v>
+      </c>
+      <c r="Q7" s="15" t="n">
+        <v>-0.483</v>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>8.5214</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.0847</v>
+        <v>0.0564</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>154</v>
@@ -1315,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M8" s="23" t="n">
         <v>0.41</v>
@@ -1330,13 +1350,13 @@
         <v>0</v>
       </c>
       <c r="P8" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0359</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>-0.998</v>
+        <v>-0.999</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1344,10 +1364,10 @@
         <v>0.5</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.013</v>
+        <v>0.0066</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1368,10 +1388,10 @@
         <v>1.5</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>0</v>
@@ -1383,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="25" t="n">
-        <v>0.004</v>
+        <v>0.0021</v>
       </c>
       <c r="Q9" s="25" t="n">
         <v>-1</v>
@@ -1400,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.0042</v>
+        <v>0.0018</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
@@ -1421,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="M10" s="23" t="n">
         <v>1.44</v>
@@ -1433,16 +1453,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="25" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="Q10" s="25" t="n">
         <v>-1</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>29.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1453,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.0018</v>
+        <v>0.0007</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1474,10 +1494,10 @@
         <v>2.5</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M11" s="23" t="n">
         <v>0</v>
@@ -1506,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1527,10 +1547,10 @@
         <v>5</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M12" s="23" t="n">
         <v>0</v>
@@ -1559,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1580,10 +1600,10 @@
         <v>7.5</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="M13" s="23" t="n">
         <v>0</v>
@@ -1609,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (36 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (35 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1702,22 +1722,22 @@
     </row>
     <row r="18">
       <c r="B18" s="17" t="n">
-        <v>0.9446</v>
+        <v>1.1397</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>1.9038</v>
+        <v>1.8289</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H18" s="16" t="n">
         <v>0.05</v>
@@ -1728,43 +1748,43 @@
       <c r="J18" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M18" s="23" t="n">
+      <c r="K18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M18" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="N18" s="24" t="n">
+      <c r="N18" s="14" t="n">
         <v>871</v>
       </c>
-      <c r="O18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="25" t="n">
-        <v>1.9276</v>
-      </c>
-      <c r="Q18" s="25" t="n">
-        <v>-0.452</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>6.4666</v>
+      <c r="O18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <v>1.8496</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>-0.409</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>7.3921</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>1.961</v>
+        <v>1.8728</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.231</v>
+        <v>0.246</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.9543</v>
+        <v>0.9579</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="14" t="n">
         <v>1611</v>
@@ -1782,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M19" s="23" t="n">
         <v>0.45</v>
@@ -1797,24 +1817,24 @@
         <v>0</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>0.9798</v>
+        <v>0.9808</v>
       </c>
       <c r="Q19" s="25" t="n">
-        <v>-0.787</v>
+        <v>-0.771</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>1.8125</v>
+        <v>2.0238</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.5804</v>
+        <v>2.5079</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.6339</v>
+        <v>0.6355</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>0</v>
@@ -1835,10 +1855,10 @@
         <v>1.5</v>
       </c>
       <c r="K20" s="23" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M20" s="23" t="n">
         <v>1</v>
@@ -1847,27 +1867,27 @@
         <v>150</v>
       </c>
       <c r="O20" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="25" t="n">
-        <v>0.6592</v>
+        <v>0.6601</v>
       </c>
       <c r="Q20" s="25" t="n">
-        <v>-0.86</v>
+        <v>-0.849</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>2.9688</v>
+        <v>3.2213</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>4.9072</v>
+        <v>4.7922</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.128</v>
+        <v>0.137</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.4906</v>
+        <v>0.4924</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>0</v>
@@ -1888,39 +1908,39 @@
         <v>2</v>
       </c>
       <c r="K21" s="23" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M21" s="23" t="n">
         <v>1.33</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O21" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="25" t="n">
-        <v>0.5178</v>
+        <v>0.518</v>
       </c>
       <c r="Q21" s="25" t="n">
-        <v>-0.894</v>
+        <v>-0.884</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>3.6816</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>3.8758</v>
+        <v>3.805</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.109</v>
+        <v>0.117</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.4086</v>
+        <v>0.4109</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>0</v>
@@ -1941,10 +1961,10 @@
         <v>2.5</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M22" s="23" t="n">
         <v>1.87</v>
@@ -1956,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="25" t="n">
-        <v>0.4398</v>
+        <v>0.4362</v>
       </c>
       <c r="Q22" s="25" t="n">
-        <v>-0.914</v>
+        <v>-0.905</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -1967,13 +1987,13 @@
     </row>
     <row r="23">
       <c r="B23" s="17" t="n">
-        <v>4.7535</v>
+        <v>4.7</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.2477</v>
+        <v>0.2514</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
@@ -1994,10 +2014,10 @@
         <v>5</v>
       </c>
       <c r="K23" s="23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M23" s="23" t="n">
         <v>4.8</v>
@@ -2009,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3263</v>
+        <v>0.3331</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>-0.962</v>
+        <v>-0.952</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>1.2</v>
@@ -2020,13 +2040,13 @@
     </row>
     <row r="24">
       <c r="B24" s="17" t="n">
-        <v>4.5534</v>
+        <v>4.5187</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.1912</v>
+        <v>0.1955</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>0</v>
@@ -2050,7 +2070,7 @@
         <v>6.3</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M24" s="23" t="n">
         <v>7.3</v>
@@ -2062,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="25" t="n">
-        <v>0.2103</v>
+        <v>0.2532</v>
       </c>
       <c r="Q24" s="25" t="n">
-        <v>-0.983</v>
+        <v>-0.976</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>1.2</v>
@@ -2076,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-12-18 (64 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (91 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2169,358 +2189,358 @@
     </row>
     <row r="29">
       <c r="B29" s="17" t="n">
-        <v>1.2</v>
+        <v>1.6858</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.664</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.6718</v>
+        <v>1.2184</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>10046</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J29" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="25" t="n">
-        <v>1.6718</v>
-      </c>
-      <c r="Q29" s="25" t="n">
-        <v>-0.443</v>
-      </c>
-      <c r="R29" s="26" t="n">
-        <v>1.2</v>
+      <c r="K29" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L29" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>2093</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="15" t="n">
+        <v>1.2461</v>
+      </c>
+      <c r="Q29" s="15" t="n">
+        <v>-0.368</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>1.3444</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.2</v>
+        <v>1.7162</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.108</v>
+        <v>0.363</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.7873</v>
+        <v>0.9212</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>6791</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M30" s="23" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="N30" s="24" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="O30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="25" t="n">
-        <v>0.7873</v>
+        <v>0.964</v>
       </c>
       <c r="Q30" s="25" t="n">
-        <v>-0.892</v>
+        <v>-0.676</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>1.2</v>
+        <v>1.6589</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.2</v>
+        <v>1.8791</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.021</v>
+        <v>0.272</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.2098</v>
+        <v>0.7002</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J31" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M31" s="23" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="N31" s="24" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="O31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>0.2098</v>
+        <v>0.7539</v>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>-0.98</v>
+        <v>-0.772</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>1.2</v>
+        <v>2.6556</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>1.2</v>
+        <v>4.2015</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.004</v>
+        <v>0.228</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.0553</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J32" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M32" s="23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>0.0553</v>
+        <v>0.6439</v>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>-0.996</v>
+        <v>-0.821</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>1.2</v>
+        <v>2.1132</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>1.2</v>
+        <v>2.9136</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.001</v>
+        <v>0.201</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.0157</v>
+        <v>0.5069</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J33" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" s="23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="O33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>0.0157</v>
+        <v>0.5793</v>
       </c>
       <c r="Q33" s="25" t="n">
-        <v>-0.999</v>
+        <v>-0.852</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>1.2</v>
+        <v>2.3364</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>1.2</v>
+        <v>4.249</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.0001</v>
+        <v>0.347</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J34" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M34" s="23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>0.0001</v>
+        <v>0.4669</v>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>-1</v>
+        <v>-0.927</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>1.2</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>1.2</v>
+        <v>4.5647</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J35" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M35" s="23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N35" s="24" t="n">
         <v>0</v>
@@ -2529,341 +2549,341 @@
         <v>0</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>0</v>
+        <v>0.4724</v>
       </c>
       <c r="Q35" s="25" t="n">
+        <v>-0.966</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>7.4375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="17" t="n">
+        <v>2.9977</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L36" s="23" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M36" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="25" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="Q36" s="25" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>6.1563</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="17" t="n">
+        <v>3.1436</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>439</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J37" s="22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K37" s="23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L37" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M37" s="23" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="N37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="25" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="Q37" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="R35" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRATION: 2027-01-15 (92 days) — Max Pain: $0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="R37" s="26" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRATION: 2027-02-19 (126 days) — Max Pain: $0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>CALLS — IV</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>Last</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J39" s="20" t="inlineStr">
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>STRIKE</t>
         </is>
       </c>
-      <c r="K39" s="21" t="inlineStr">
+      <c r="K41" s="21" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="L39" s="21" t="inlineStr">
+      <c r="L41" s="21" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="M39" s="21" t="inlineStr">
+      <c r="M41" s="21" t="inlineStr">
         <is>
           <t>Last</t>
         </is>
       </c>
-      <c r="N39" s="21" t="inlineStr">
+      <c r="N41" s="21" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="O39" s="21" t="inlineStr">
+      <c r="O41" s="21" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="P39" s="21" t="inlineStr">
+      <c r="P41" s="21" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="Q39" s="21" t="inlineStr">
+      <c r="Q41" s="21" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="R39" s="21" t="inlineStr">
+      <c r="R41" s="21" t="inlineStr">
         <is>
           <t>PUTS — IV</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="17" t="n">
-        <v>1.0584</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>1.2858</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>332</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>9837</v>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H40" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I40" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J40" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K40" s="23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L40" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M40" s="23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N40" s="24" t="n">
-        <v>2093</v>
-      </c>
-      <c r="O40" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="P40" s="25" t="n">
-        <v>1.3166</v>
-      </c>
-      <c r="Q40" s="25" t="n">
-        <v>-0.397</v>
-      </c>
-      <c r="R40" s="26" t="n">
-        <v>1.2345</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="17" t="n">
-        <v>1.5306</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0.9347</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>107</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>6877</v>
-      </c>
-      <c r="G41" s="16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J41" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L41" s="23" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M41" s="23" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="N41" s="24" t="n">
-        <v>641</v>
-      </c>
-      <c r="O41" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="25" t="n">
-        <v>0.9813</v>
-      </c>
-      <c r="Q41" s="25" t="n">
-        <v>-0.6879999999999999</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>1.4688</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="17" t="n">
-        <v>1.6018</v>
+        <v>2.9527</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.267</v>
+        <v>0.664</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.7134</v>
+        <v>0.7653</v>
       </c>
       <c r="E42" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L42" s="23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M42" s="23" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N42" s="24" t="n">
-        <v>455</v>
-      </c>
-      <c r="O42" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="25" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="Q42" s="25" t="n">
-        <v>-0.779</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>2.7031</v>
+        <v>0.5</v>
+      </c>
+      <c r="K42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M42" s="16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N42" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="15" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="Q42" s="15" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="R42" s="17" t="n">
+        <v>6.9557</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>3.8267</v>
+        <v>1.547</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.225</v>
+        <v>0.406</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.5948</v>
+        <v>0.771</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>2815</v>
+        <v>6486</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>1.05</v>
+        <v>0.1</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="M43" s="23" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="O43" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="25" t="n">
-        <v>0.6633</v>
+        <v>0.7893</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>-0.825</v>
+        <v>-0.574</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.75</v>
+        <v>1.7672</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>2.9997</v>
+        <v>2.1502</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.2</v>
+        <v>0.306</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.6398</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>0</v>
@@ -2872,122 +2892,122 @@
         <v>0.2</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K44" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L44" s="23" t="n">
         <v>1.55</v>
       </c>
-      <c r="L44" s="23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="M44" s="23" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="N44" s="24" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="O44" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="25" t="n">
-        <v>0.5951</v>
+        <v>0.6804</v>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>-0.855</v>
+        <v>-0.68</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>0</v>
+        <v>1.7105</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>4.3589</v>
+        <v>2.1576</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.146</v>
+        <v>0.254</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.3602</v>
+        <v>0.5495</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="M45" s="23" t="n">
-        <v>3.8</v>
+        <v>1.35</v>
       </c>
       <c r="N45" s="24" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="O45" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="25" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6098</v>
       </c>
       <c r="Q45" s="25" t="n">
-        <v>-0.93</v>
+        <v>-0.738</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>7.0938</v>
+        <v>1.9819</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>4.6704</v>
+        <v>0.5</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.125</v>
+        <v>0.222</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.2984</v>
+        <v>0.4871</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H46" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>6.4</v>
+        <v>1.65</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="M46" s="23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N46" s="24" t="n">
         <v>0</v>
@@ -2996,30 +3016,30 @@
         <v>0</v>
       </c>
       <c r="P46" s="25" t="n">
-        <v>0.4323</v>
+        <v>0.5652</v>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>-0.969</v>
+        <v>-0.776</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>7.375</v>
+        <v>1.8825</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>3.0429</v>
+        <v>4.4047</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.113</v>
+        <v>0.151</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.2638</v>
+        <v>0.3371</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>0.05</v>
@@ -3028,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>8.9</v>
+        <v>2.75</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>9.9</v>
+        <v>6.3</v>
       </c>
       <c r="M47" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N47" s="24" t="n">
         <v>0</v>
@@ -3049,51 +3069,51 @@
         <v>0</v>
       </c>
       <c r="P47" s="25" t="n">
-        <v>0.1623</v>
+        <v>0.4849</v>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>-0.988</v>
+        <v>-0.878</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>6.125</v>
+        <v>2.5082</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>3.1876</v>
+        <v>0.5</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.105</v>
+        <v>0.123</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.241</v>
+        <v>0.2741</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M48" s="23" t="n">
-        <v>10.94</v>
+        <v>0</v>
       </c>
       <c r="N48" s="24" t="n">
         <v>0</v>
@@ -3102,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="25" t="n">
-        <v>0.0316</v>
+        <v>0.5226</v>
       </c>
       <c r="Q48" s="25" t="n">
-        <v>-0.998</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>7.7188</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="49"/>
@@ -3116,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (127 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (217 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3209,187 +3229,187 @@
     </row>
     <row r="53">
       <c r="B53" s="17" t="n">
-        <v>1.7549</v>
+        <v>3.2752</v>
       </c>
       <c r="C53" s="15" t="n">
-        <v>0.643</v>
+        <v>0.735</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>0.8254</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>2554</v>
+        <v>336</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="J53" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="23" t="n">
+      <c r="K53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="16" t="n">
         <v>0.95</v>
       </c>
-      <c r="M53" s="23" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N53" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="25" t="n">
-        <v>0.8142</v>
-      </c>
-      <c r="Q53" s="25" t="n">
+      <c r="M53" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N53" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="15" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="Q53" s="15" t="n">
         <v>-0.336</v>
       </c>
-      <c r="R53" s="26" t="n">
-        <v>6.8935</v>
+      <c r="R53" s="17" t="n">
+        <v>5.5262</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>2.0918</v>
+        <v>2.0024</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.392</v>
+        <v>0.434</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.7935</v>
+        <v>0.9205</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>6384</v>
+        <v>76</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="J54" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="23" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M54" s="23" t="n">
-        <v>0.45</v>
+        <v>0.59</v>
       </c>
       <c r="N54" s="24" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="O54" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="25" t="n">
-        <v>0.8153</v>
+        <v>1.0376</v>
       </c>
       <c r="Q54" s="25" t="n">
-        <v>-0.588</v>
+        <v>-0.66</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>1.3774</v>
+        <v>1.5061</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>2.2346</v>
+        <v>1.6761</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.297</v>
+        <v>0.344</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.655</v>
+        <v>0.7327</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="H55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J55" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M55" s="23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N55" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="25" t="n">
-        <v>0.701</v>
+        <v>0.8739</v>
       </c>
       <c r="Q55" s="25" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.762</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>1.5938</v>
+        <v>1.8461</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>2.2288</v>
+        <v>5.6311</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.248</v>
+        <v>0.3</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.5626</v>
+        <v>0.628</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="G56" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="J56" s="22" t="n">
         <v>2</v>
@@ -3398,60 +3418,60 @@
         <v>1.05</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M56" s="23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="N56" s="24" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O56" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="25" t="n">
-        <v>0.6299</v>
+        <v>0.7909</v>
       </c>
       <c r="Q56" s="25" t="n">
-        <v>-0.745</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>1.8281</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>3.3376</v>
+        <v>3.7397</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.217</v>
+        <v>0.273</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.4992</v>
+        <v>0.5614</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="J57" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>1.45</v>
+        <v>0.3</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="M57" s="23" t="n">
         <v>0</v>
@@ -3463,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="25" t="n">
-        <v>0.5865</v>
+        <v>0.7403</v>
       </c>
       <c r="Q57" s="25" t="n">
-        <v>-0.782</v>
+        <v>-0.855</v>
       </c>
       <c r="R57" s="26" t="n">
         <v>1.2</v>
@@ -3474,19 +3494,19 @@
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>4.5498</v>
+        <v>6.0378</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.149</v>
+        <v>0.209</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.3472</v>
+        <v>0.4097</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="G58" s="16" t="n">
         <v>0.05</v>
@@ -3495,16 +3515,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J58" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="23" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="M58" s="23" t="n">
         <v>0</v>
@@ -3516,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="25" t="n">
-        <v>0.5105</v>
+        <v>0.5597</v>
       </c>
       <c r="Q58" s="25" t="n">
-        <v>-0.883</v>
+        <v>-0.96</v>
       </c>
       <c r="R58" s="26" t="n">
         <v>1.2</v>
@@ -3527,37 +3547,37 @@
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>6.4145</v>
+        <v>2.0511</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.122</v>
+        <v>0.18</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.2832</v>
+        <v>0.3465</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G59" s="16" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="J59" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="M59" s="23" t="n">
         <v>0</v>
@@ -3569,480 +3589,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="25" t="n">
-        <v>0.5305</v>
+        <v>0.0433</v>
       </c>
       <c r="Q59" s="25" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.997</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62">
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRATION: 2027-05-21 (218 days) — Max Pain: $0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>CALLS — IV</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>STRIKE</t>
-        </is>
-      </c>
-      <c r="K63" s="21" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="L63" s="21" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="M63" s="21" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="N63" s="21" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="O63" s="21" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="P63" s="21" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="Q63" s="21" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="R63" s="21" t="inlineStr">
-        <is>
-          <t>PUTS — IV</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="17" t="n">
-        <v>4.9398</v>
-      </c>
-      <c r="C64" s="15" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="D64" s="15" t="n">
-        <v>1.0437</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>336</v>
-      </c>
-      <c r="G64" s="16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H64" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I64" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J64" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N64" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O64" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="25" t="n">
-        <v>1.1063</v>
-      </c>
-      <c r="Q64" s="25" t="n">
-        <v>-0.364</v>
-      </c>
-      <c r="R64" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="17" t="n">
-        <v>2.1162</v>
-      </c>
-      <c r="C65" s="15" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D65" s="15" t="n">
-        <v>0.9432</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="G65" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H65" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I65" s="16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J65" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L65" s="23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="M65" s="23" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N65" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O65" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="25" t="n">
-        <v>1.0711</v>
-      </c>
-      <c r="Q65" s="25" t="n">
-        <v>-0.676</v>
-      </c>
-      <c r="R65" s="26" t="n">
-        <v>1.0435</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="17" t="n">
-        <v>2.5795</v>
-      </c>
-      <c r="C66" s="15" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="D66" s="15" t="n">
-        <v>0.7506</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J66" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K66" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L66" s="23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M66" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="25" t="n">
-        <v>0.9038</v>
-      </c>
-      <c r="Q66" s="25" t="n">
-        <v>-0.774</v>
-      </c>
-      <c r="R66" s="26" t="n">
-        <v>2.4288</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="17" t="n">
-        <v>7.7388</v>
-      </c>
-      <c r="C67" s="15" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="D67" s="15" t="n">
-        <v>0.6444</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="G67" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H67" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" s="23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L67" s="23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M67" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="25" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Q67" s="25" t="n">
-        <v>-0.827</v>
-      </c>
-      <c r="R67" s="26" t="n">
-        <v>2.6568</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="17" t="n">
-        <v>3.9533</v>
-      </c>
-      <c r="C68" s="15" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="D68" s="15" t="n">
-        <v>0.5768</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J68" s="22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K68" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L68" s="23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="25" t="n">
-        <v>0.7673</v>
-      </c>
-      <c r="Q68" s="25" t="n">
-        <v>-0.864</v>
-      </c>
-      <c r="R68" s="26" t="n">
-        <v>6.058</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="17" t="n">
-        <v>1.6403</v>
-      </c>
-      <c r="C69" s="15" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="D69" s="15" t="n">
-        <v>0.4224</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G69" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H69" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J69" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K69" s="23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L69" s="23" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M69" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="25" t="n">
-        <v>0.4866</v>
-      </c>
-      <c r="Q69" s="25" t="n">
-        <v>-0.967</v>
-      </c>
-      <c r="R69" s="26" t="n">
-        <v>2.2485</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="17" t="n">
-        <v>2.0936</v>
-      </c>
-      <c r="C70" s="15" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="D70" s="15" t="n">
-        <v>0.3577</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="G70" s="16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J70" s="22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K70" s="23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L70" s="23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M70" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R70" s="26" t="n">
-        <v>1.2</v>
+        <v>2.7374</v>
       </c>
     </row>
   </sheetData>
@@ -4056,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4161,29 +3714,29 @@
     <row r="6">
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.098</v>
@@ -4192,10 +3745,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
@@ -4206,29 +3759,29 @@
     <row r="7">
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -4237,10 +3790,10 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N7" s="30" t="inlineStr">
         <is>
@@ -4251,29 +3804,29 @@
     <row r="8">
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.098</v>
@@ -4282,10 +3835,10 @@
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N8" s="27" t="inlineStr">
         <is>
@@ -4296,29 +3849,29 @@
     <row r="9">
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.098</v>
@@ -4327,10 +3880,10 @@
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N9" s="30" t="inlineStr">
         <is>
@@ -4341,26 +3894,26 @@
     <row r="10">
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>5157</v>
@@ -4372,10 +3925,10 @@
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N10" s="27" t="inlineStr">
         <is>
@@ -4386,41 +3939,41 @@
     <row r="11">
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C11" s="31" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>5157</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N11" s="30" t="inlineStr">
         <is>
@@ -4431,29 +3984,29 @@
     <row r="12">
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.099</v>
@@ -4462,10 +4015,10 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N12" s="27" t="inlineStr">
         <is>
@@ -4476,29 +4029,29 @@
     <row r="13">
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C13" s="31" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.099</v>
@@ -4507,10 +4060,10 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N13" s="30" t="inlineStr">
         <is>
@@ -4521,26 +4074,26 @@
     <row r="14">
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>5161</v>
@@ -4552,10 +4105,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N14" s="27" t="inlineStr">
         <is>
@@ -4566,17 +4119,17 @@
     <row r="15">
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C15" s="31" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>0</v>
@@ -4585,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>5161</v>
@@ -4597,10 +4150,10 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N15" s="30" t="inlineStr">
         <is>
@@ -4611,29 +4164,29 @@
     <row r="16">
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>0.099</v>
@@ -4642,10 +4195,10 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N16" s="27" t="inlineStr">
         <is>
@@ -4656,41 +4209,41 @@
     <row r="17">
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C17" s="31" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I17" s="14" t="n">
         <v>5159</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
@@ -4701,29 +4254,29 @@
     <row r="18">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.098</v>
@@ -4732,10 +4285,10 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N18" s="27" t="inlineStr">
         <is>
@@ -4746,29 +4299,29 @@
     <row r="19">
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C19" s="31" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>0.098</v>
@@ -4777,10 +4330,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N19" s="30" t="inlineStr">
         <is>
@@ -4791,26 +4344,26 @@
     <row r="20">
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C20" s="28" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>5156</v>
@@ -4822,10 +4375,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N20" s="27" t="inlineStr">
         <is>
@@ -4836,41 +4389,41 @@
     <row r="21">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K21" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N21" s="30" t="inlineStr">
         <is>
@@ -4881,41 +4434,41 @@
     <row r="22">
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C22" s="28" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
@@ -4926,41 +4479,41 @@
     <row r="23">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C23" s="31" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K23" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N23" s="30" t="inlineStr">
         <is>
@@ -4971,29 +4524,29 @@
     <row r="24">
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C24" s="28" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>0.093</v>
@@ -5002,10 +4555,10 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N24" s="27" t="inlineStr">
         <is>
@@ -5016,73 +4569,77 @@
     <row r="25">
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C25" s="31" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K25" s="16" t="inlineStr"/>
+        <v>0.093</v>
+      </c>
+      <c r="K25" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L25" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="17" t="inlineStr"/>
+        <v>2361798</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K26" s="10" t="inlineStr"/>
       <c r="L26" s="12" t="n">
@@ -5098,32 +4655,32 @@
     <row r="27">
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C27" s="31" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K27" s="16" t="inlineStr"/>
       <c r="L27" s="18" t="n">
@@ -5139,31 +4696,33 @@
     <row r="28">
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C28" s="28" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="9" t="inlineStr"/>
+        <v>7194</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K28" s="10" t="inlineStr"/>
       <c r="L28" s="12" t="n">
         <v>0</v>
@@ -5178,23 +4737,23 @@
     <row r="29">
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C29" s="31" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H29" s="14" t="n">
         <v>0</v>
@@ -5217,33 +4776,31 @@
     <row r="30">
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C30" s="28" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="10" t="inlineStr"/>
       <c r="L30" s="12" t="n">
         <v>0</v>
@@ -5258,31 +4815,33 @@
     <row r="31">
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C31" s="31" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="15" t="inlineStr"/>
+        <v>6136</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K31" s="16" t="inlineStr"/>
       <c r="L31" s="18" t="n">
         <v>0</v>
@@ -5297,23 +4856,23 @@
     <row r="32">
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C32" s="28" t="n">
         <v>1.69</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>0</v>
@@ -5336,33 +4895,31 @@
     <row r="33">
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C33" s="31" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J33" s="15" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J33" s="15" t="inlineStr"/>
       <c r="K33" s="16" t="inlineStr"/>
       <c r="L33" s="18" t="n">
         <v>0</v>
@@ -5377,31 +4934,33 @@
     <row r="34">
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C34" s="28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9" t="inlineStr"/>
+        <v>5834</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -5416,33 +4975,31 @@
     <row r="35">
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C35" s="31" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J35" s="15" t="inlineStr"/>
       <c r="K35" s="16" t="inlineStr"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
@@ -5457,31 +5014,33 @@
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C36" s="28" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9" t="inlineStr"/>
+        <v>4272</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
@@ -5496,11 +5055,11 @@
     <row r="37">
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C37" s="31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>2568</v>
@@ -5515,14 +5074,12 @@
         <v>0.27</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J37" s="15" t="inlineStr"/>
       <c r="K37" s="16" t="inlineStr"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
@@ -5537,11 +5094,11 @@
     <row r="38">
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C38" s="28" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2568</v>
@@ -5556,12 +5113,14 @@
         <v>0.27</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="inlineStr"/>
+        <v>4145</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
@@ -5576,11 +5135,11 @@
     <row r="39">
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C39" s="31" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>2568</v>
@@ -5595,14 +5154,12 @@
         <v>0.27</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J39" s="15" t="inlineStr"/>
       <c r="K39" s="16" t="inlineStr"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -5617,29 +5174,33 @@
     <row r="40">
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C40" s="28" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
+        <v>546</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="inlineStr"/>
+        <v>4059</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -5654,11 +5215,11 @@
     <row r="41">
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C41" s="31" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>0</v>
@@ -5691,11 +5252,11 @@
     <row r="42">
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C42" s="28" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>0</v>
@@ -5728,11 +5289,11 @@
     <row r="43">
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C43" s="31" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
@@ -5765,11 +5326,11 @@
     <row r="44">
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C44" s="28" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>0</v>
@@ -5802,11 +5363,11 @@
     <row r="45">
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C45" s="31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
@@ -5839,7 +5400,7 @@
     <row r="46">
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C46" s="28" t="n">
@@ -5876,7 +5437,7 @@
     <row r="47">
       <c r="B47" s="30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C47" s="31" t="n">
@@ -5913,7 +5474,7 @@
     <row r="48">
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C48" s="28" t="n">
@@ -5942,6 +5503,43 @@
       </c>
       <c r="M48" s="11" t="inlineStr"/>
       <c r="N48" s="27" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15" t="inlineStr"/>
+      <c r="H49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="15" t="inlineStr"/>
+      <c r="K49" s="16" t="inlineStr"/>
+      <c r="L49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="17" t="inlineStr"/>
+      <c r="N49" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5958,7 +5556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6068,7 +5666,7 @@
         <v>232</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>232</v>
@@ -6108,7 +5706,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>6</v>
@@ -6148,7 +5746,7 @@
         <v>154</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>154</v>
@@ -6188,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>1</v>
@@ -6348,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>1</v>
@@ -6603,42 +6201,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00000500</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F20" s="38" t="n">
-        <v>1726</v>
-      </c>
-      <c r="G20" s="38" t="n">
+      <c r="F20" s="8" t="n">
         <v>1728</v>
       </c>
-      <c r="H20" s="38" t="n">
+      <c r="G20" s="8" t="n">
         <v>1728</v>
       </c>
-      <c r="I20" s="38" t="n">
+      <c r="H20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>1728</v>
       </c>
-      <c r="J20" s="38" t="n">
-        <v>1726</v>
-      </c>
-      <c r="K20" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J20" s="8" t="n">
+        <v>1728</v>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6266,7 @@
         <v>871</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>871</v>
@@ -6708,7 +6306,7 @@
         <v>1611</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1611</v>
+        <v>0</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>1611</v>
@@ -6748,7 +6346,7 @@
         <v>358</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>358</v>
@@ -6788,7 +6386,7 @@
         <v>2128</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2128</v>
+        <v>0</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>2128</v>
@@ -6828,7 +6426,7 @@
         <v>150</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>150</v>
@@ -6868,7 +6466,7 @@
         <v>1358</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1358</v>
+        <v>0</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>1358</v>
@@ -6883,42 +6481,42 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00002000</t>
         </is>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="36" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F27" s="38" t="n">
-        <v>90</v>
-      </c>
-      <c r="G27" s="38" t="n">
+      <c r="F27" s="14" t="n">
         <v>78</v>
       </c>
-      <c r="H27" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="38" t="n">
+      <c r="G27" s="14" t="n">
         <v>78</v>
       </c>
-      <c r="J27" s="38" t="n">
-        <v>90</v>
-      </c>
-      <c r="K27" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="H27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="K27" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
@@ -7165,12 +6763,12 @@
     <row r="34">
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_0.5</t>
+          <t>OTLK270115C00000500</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
@@ -7182,19 +6780,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0</v>
+        <v>10046</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>0</v>
+        <v>10046</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0</v>
+        <v>10046</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0</v>
+        <v>10046</v>
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
@@ -7205,12 +6803,12 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_0.5</t>
+          <t>OTLK270115P00000500</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
@@ -7222,19 +6820,19 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
@@ -7245,12 +6843,12 @@
     <row r="36">
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_1.0</t>
+          <t>OTLK270115C00001000</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -7262,19 +6860,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0</v>
+        <v>6791</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0</v>
+        <v>6791</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>6791</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0</v>
+        <v>6791</v>
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
@@ -7285,12 +6883,12 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_1.0</t>
+          <t>OTLK270115P00001000</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
@@ -7302,19 +6900,19 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="H37" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
@@ -7325,12 +6923,12 @@
     <row r="38">
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_1.5</t>
+          <t>OTLK270115C00001500</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -7342,19 +6940,19 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="K38" s="27" t="inlineStr">
         <is>
@@ -7365,12 +6963,12 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_1.5</t>
+          <t>OTLK270115P00001500</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
@@ -7382,19 +6980,19 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="H39" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="K39" s="30" t="inlineStr">
         <is>
@@ -7405,12 +7003,12 @@
     <row r="40">
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_2.0</t>
+          <t>OTLK270115C00002000</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -7422,19 +7020,19 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="K40" s="27" t="inlineStr">
         <is>
@@ -7445,12 +7043,12 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_2.0</t>
+          <t>OTLK270115P00002000</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
@@ -7462,19 +7060,19 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K41" s="30" t="inlineStr">
         <is>
@@ -7485,12 +7083,12 @@
     <row r="42">
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_2.5</t>
+          <t>OTLK270115C00002500</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
@@ -7502,19 +7100,19 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="K42" s="27" t="inlineStr">
         <is>
@@ -7525,12 +7123,12 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_2.5</t>
+          <t>OTLK270115P00002500</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D43" s="16" t="n">
@@ -7542,19 +7140,19 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="H43" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="K43" s="30" t="inlineStr">
         <is>
@@ -7565,12 +7163,12 @@
     <row r="44">
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_5.0</t>
+          <t>OTLK270115C00005000</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
@@ -7582,19 +7180,19 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="K44" s="27" t="inlineStr">
         <is>
@@ -7603,54 +7201,54 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="34" t="inlineStr">
-        <is>
-          <t>OTLK_2026-12-18_P_5.0</t>
-        </is>
-      </c>
-      <c r="C45" s="30" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115P00005000</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D45" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="30" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F45" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_C_7.5</t>
+          <t>OTLK270115C00007500</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -7662,19 +7260,19 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="K46" s="27" t="inlineStr">
         <is>
@@ -7685,12 +7283,12 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>OTLK_2026-12-18_P_7.5</t>
+          <t>OTLK270115P00007500</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
@@ -7723,49 +7321,49 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115C00000500</t>
-        </is>
-      </c>
-      <c r="C48" s="36" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270115C00010000</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D48" s="37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E48" s="36" t="inlineStr">
+      <c r="D48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F48" s="38" t="n">
-        <v>9837</v>
-      </c>
-      <c r="G48" s="38" t="n">
-        <v>10046</v>
-      </c>
-      <c r="H48" s="38" t="n">
-        <v>10046</v>
-      </c>
-      <c r="I48" s="38" t="n">
-        <v>10046</v>
-      </c>
-      <c r="J48" s="38" t="n">
-        <v>9837</v>
-      </c>
-      <c r="K48" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F48" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="K48" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00000500</t>
+          <t>OTLK270115P00010000</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
@@ -7774,7 +7372,7 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -7782,19 +7380,19 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="K49" s="30" t="inlineStr">
         <is>
@@ -7803,49 +7401,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115C00001000</t>
-        </is>
-      </c>
-      <c r="C50" s="36" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270115C00012500</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D50" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="36" t="inlineStr">
+      <c r="D50" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F50" s="38" t="n">
-        <v>6877</v>
-      </c>
-      <c r="G50" s="38" t="n">
-        <v>6791</v>
-      </c>
-      <c r="H50" s="38" t="n">
-        <v>6791</v>
-      </c>
-      <c r="I50" s="38" t="n">
-        <v>6791</v>
-      </c>
-      <c r="J50" s="38" t="n">
-        <v>6877</v>
-      </c>
-      <c r="K50" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F50" s="8" t="n">
+        <v>439</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>439</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>439</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>439</v>
+      </c>
+      <c r="K50" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001000</t>
+          <t>OTLK270115P00012500</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
@@ -7854,7 +7452,7 @@
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -7862,19 +7460,19 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="J51" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K51" s="30" t="inlineStr">
         <is>
@@ -7885,16 +7483,16 @@
     <row r="52">
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00001500</t>
+          <t>OTLK270219C00000500</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
@@ -7902,19 +7500,19 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="K52" s="27" t="inlineStr">
         <is>
@@ -7925,16 +7523,16 @@
     <row r="53">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001500</t>
+          <t>OTLK270219P00000500</t>
         </is>
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
@@ -7942,19 +7540,19 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="K53" s="30" t="inlineStr">
         <is>
@@ -7963,58 +7561,58 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115C00002000</t>
-        </is>
-      </c>
-      <c r="C54" s="36" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="D54" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="36" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270219C00001000</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F54" s="38" t="n">
-        <v>2815</v>
-      </c>
-      <c r="G54" s="38" t="n">
-        <v>2820</v>
-      </c>
-      <c r="H54" s="38" t="n">
-        <v>2820</v>
-      </c>
-      <c r="I54" s="38" t="n">
-        <v>2820</v>
-      </c>
-      <c r="J54" s="38" t="n">
-        <v>2815</v>
-      </c>
-      <c r="K54" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F54" s="8" t="n">
+        <v>6486</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>6486</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>6486</v>
+      </c>
+      <c r="K54" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002000</t>
+          <t>OTLK270219P00001000</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
@@ -8022,19 +7620,19 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
@@ -8045,16 +7643,16 @@
     <row r="56">
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00002500</t>
+          <t>OTLK270219C00001500</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
@@ -8062,19 +7660,19 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
@@ -8085,16 +7683,16 @@
     <row r="57">
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002500</t>
+          <t>OTLK270219P00001500</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E57" s="30" t="inlineStr">
         <is>
@@ -8102,19 +7700,19 @@
         </is>
       </c>
       <c r="F57" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="H57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
@@ -8125,16 +7723,16 @@
     <row r="58">
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00005000</t>
+          <t>OTLK270219C00002000</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
@@ -8142,19 +7740,19 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="K58" s="27" t="inlineStr">
         <is>
@@ -8163,58 +7761,58 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115P00005000</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="D59" s="37" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" s="36" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270219P00002000</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F59" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="G59" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H59" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K59" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F59" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G59" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K59" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00007500</t>
+          <t>OTLK270219C00002500</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
@@ -8222,19 +7820,19 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="K60" s="27" t="inlineStr">
         <is>
@@ -8245,16 +7843,16 @@
     <row r="61">
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00007500</t>
+          <t>OTLK270219P00002500</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D61" s="16" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
@@ -8285,16 +7883,16 @@
     <row r="62">
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00010000</t>
+          <t>OTLK270219C00005000</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
@@ -8302,19 +7900,19 @@
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="K62" s="27" t="inlineStr">
         <is>
@@ -8325,16 +7923,16 @@
     <row r="63">
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00010000</t>
+          <t>OTLK270219P00005000</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D63" s="16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E63" s="30" t="inlineStr">
         <is>
@@ -8365,16 +7963,16 @@
     <row r="64">
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00012500</t>
+          <t>OTLK270219C00007500</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
@@ -8382,19 +7980,19 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="K64" s="27" t="inlineStr">
         <is>
@@ -8405,16 +8003,16 @@
     <row r="65">
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00012500</t>
+          <t>OTLK270219P00007500</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D65" s="16" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E65" s="30" t="inlineStr">
         <is>
@@ -8443,54 +8041,54 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270219C00000500</t>
-        </is>
-      </c>
-      <c r="C66" s="36" t="inlineStr">
-        <is>
-          <t>2027-02-19</t>
-        </is>
-      </c>
-      <c r="D66" s="37" t="n">
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00000500</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" s="36" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F66" s="38" t="n">
-        <v>2554</v>
-      </c>
-      <c r="G66" s="38" t="n">
-        <v>2525</v>
-      </c>
-      <c r="H66" s="38" t="n">
-        <v>2525</v>
-      </c>
-      <c r="I66" s="38" t="n">
-        <v>2525</v>
-      </c>
-      <c r="J66" s="38" t="n">
-        <v>2554</v>
-      </c>
-      <c r="K66" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F66" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="K66" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00000500</t>
+          <t>OTLK270521P00000500</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D67" s="16" t="n">
@@ -8502,19 +8100,19 @@
         </is>
       </c>
       <c r="F67" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H67" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J67" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67" s="30" t="inlineStr">
         <is>
@@ -8523,54 +8121,54 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270219C00001000</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="inlineStr">
-        <is>
-          <t>2027-02-19</t>
-        </is>
-      </c>
-      <c r="D68" s="37" t="n">
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>OTLK270521C00001000</t>
+        </is>
+      </c>
+      <c r="C68" s="27" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="36" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F68" s="38" t="n">
-        <v>6384</v>
-      </c>
-      <c r="G68" s="38" t="n">
-        <v>6486</v>
-      </c>
-      <c r="H68" s="38" t="n">
-        <v>6486</v>
-      </c>
-      <c r="I68" s="38" t="n">
-        <v>6486</v>
-      </c>
-      <c r="J68" s="38" t="n">
-        <v>6384</v>
-      </c>
-      <c r="K68" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F68" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="K68" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001000</t>
+          <t>OTLK270521P00001000</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D69" s="16" t="n">
@@ -8582,19 +8180,19 @@
         </is>
       </c>
       <c r="F69" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="J69" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="K69" s="30" t="inlineStr">
         <is>
@@ -8605,12 +8203,12 @@
     <row r="70">
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00001500</t>
+          <t>OTLK270521C00001500</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
@@ -8622,19 +8220,19 @@
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>5582</v>
+        <v>0</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>5582</v>
+        <v>0</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="K70" s="27" t="inlineStr">
         <is>
@@ -8645,12 +8243,12 @@
     <row r="71">
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001500</t>
+          <t>OTLK270521P00001500</t>
         </is>
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D71" s="16" t="n">
@@ -8662,19 +8260,19 @@
         </is>
       </c>
       <c r="F71" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="30" t="inlineStr">
         <is>
@@ -8685,12 +8283,12 @@
     <row r="72">
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002000</t>
+          <t>OTLK270521C00002000</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
@@ -8702,19 +8300,19 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>1071</v>
+        <v>0</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>1071</v>
+        <v>0</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="K72" s="27" t="inlineStr">
         <is>
@@ -8725,12 +8323,12 @@
     <row r="73">
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00002000</t>
+          <t>OTLK270521P00002000</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D73" s="16" t="n">
@@ -8742,19 +8340,19 @@
         </is>
       </c>
       <c r="F73" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H73" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J73" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K73" s="30" t="inlineStr">
         <is>
@@ -8765,12 +8363,12 @@
     <row r="74">
       <c r="B74" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002500</t>
+          <t>OTLK270521C00002500</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
@@ -8782,19 +8380,19 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="K74" s="27" t="inlineStr">
         <is>
@@ -8805,12 +8403,12 @@
     <row r="75">
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00002500</t>
+          <t>OTLK270521P00002500</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D75" s="16" t="n">
@@ -8845,12 +8443,12 @@
     <row r="76">
       <c r="B76" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00005000</t>
+          <t>OTLK270521C00005000</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
@@ -8862,19 +8460,19 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="H76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="K76" s="27" t="inlineStr">
         <is>
@@ -8885,12 +8483,12 @@
     <row r="77">
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00005000</t>
+          <t>OTLK270521P00005000</t>
         </is>
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D77" s="16" t="n">
@@ -8925,12 +8523,12 @@
     <row r="78">
       <c r="B78" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00007500</t>
+          <t>OTLK270521C00007500</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
@@ -8942,19 +8540,19 @@
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K78" s="27" t="inlineStr">
         <is>
@@ -8965,12 +8563,12 @@
     <row r="79">
       <c r="B79" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00007500</t>
+          <t>OTLK270521P00007500</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D79" s="16" t="n">
@@ -8997,566 +8595,6 @@
         <v>0</v>
       </c>
       <c r="K79" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00000500</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E80" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="I80" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="K80" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00000500</t>
-        </is>
-      </c>
-      <c r="C81" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D81" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E81" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I81" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K81" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00001000</t>
-        </is>
-      </c>
-      <c r="C82" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G82" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="H82" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="I82" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="K82" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00001000</t>
-        </is>
-      </c>
-      <c r="C83" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H83" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K83" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00001500</t>
-        </is>
-      </c>
-      <c r="C84" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E84" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00001500</t>
-        </is>
-      </c>
-      <c r="C85" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E85" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00002000</t>
-        </is>
-      </c>
-      <c r="C86" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="G86" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="H86" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="I86" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="K86" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00002000</t>
-        </is>
-      </c>
-      <c r="C87" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00002500</t>
-        </is>
-      </c>
-      <c r="C88" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E88" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00002500</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E89" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00005000</t>
-        </is>
-      </c>
-      <c r="C90" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E90" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G90" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H90" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I90" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K90" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00005000</t>
-        </is>
-      </c>
-      <c r="C91" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E91" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00007500</t>
-        </is>
-      </c>
-      <c r="C92" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D92" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E92" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="G92" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="H92" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="I92" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="K92" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00007500</t>
-        </is>
-      </c>
-      <c r="C93" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E93" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 08:04 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 08:16 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 08:16 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 09:18 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 09:18 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 10:03 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 10:03 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 10:13 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -4641,11 +4641,11 @@
       <c r="J26" s="9" t="n">
         <v>0.171</v>
       </c>
-      <c r="K26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="n"/>
       <c r="L26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="11" t="inlineStr"/>
+      <c r="M26" s="11" t="n"/>
       <c r="N26" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4682,11 +4682,11 @@
       <c r="J27" s="15" t="n">
         <v>0.17</v>
       </c>
-      <c r="K27" s="16" t="inlineStr"/>
+      <c r="K27" s="16" t="n"/>
       <c r="L27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="17" t="inlineStr"/>
+      <c r="M27" s="17" t="n"/>
       <c r="N27" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4723,11 +4723,11 @@
       <c r="J28" s="9" t="n">
         <v>0.164</v>
       </c>
-      <c r="K28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="n"/>
       <c r="L28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="n"/>
       <c r="N28" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4761,12 +4761,12 @@
       <c r="I29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="15" t="inlineStr"/>
-      <c r="K29" s="16" t="inlineStr"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16" t="n"/>
       <c r="L29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="17" t="inlineStr"/>
+      <c r="M29" s="17" t="n"/>
       <c r="N29" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4800,12 +4800,12 @@
       <c r="I30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="10" t="n"/>
       <c r="L30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="n"/>
       <c r="N30" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4842,11 +4842,11 @@
       <c r="J31" s="15" t="n">
         <v>0.157</v>
       </c>
-      <c r="K31" s="16" t="inlineStr"/>
+      <c r="K31" s="16" t="n"/>
       <c r="L31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="17" t="inlineStr"/>
+      <c r="M31" s="17" t="n"/>
       <c r="N31" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4880,12 +4880,12 @@
       <c r="I32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="n"/>
       <c r="N32" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4919,12 +4919,12 @@
       <c r="I33" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="15" t="inlineStr"/>
-      <c r="K33" s="16" t="inlineStr"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="16" t="n"/>
       <c r="L33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="17" t="inlineStr"/>
+      <c r="M33" s="17" t="n"/>
       <c r="N33" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4961,11 +4961,11 @@
       <c r="J34" s="9" t="n">
         <v>0.18</v>
       </c>
-      <c r="K34" s="10" t="inlineStr"/>
+      <c r="K34" s="10" t="n"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="n"/>
       <c r="N34" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -4999,12 +4999,12 @@
       <c r="I35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="15" t="inlineStr"/>
-      <c r="K35" s="16" t="inlineStr"/>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="17" t="inlineStr"/>
+      <c r="M35" s="17" t="n"/>
       <c r="N35" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5041,11 +5041,11 @@
       <c r="J36" s="9" t="n">
         <v>0.145</v>
       </c>
-      <c r="K36" s="10" t="inlineStr"/>
+      <c r="K36" s="10" t="n"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="n"/>
       <c r="N36" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5079,12 +5079,12 @@
       <c r="I37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="15" t="inlineStr"/>
-      <c r="K37" s="16" t="inlineStr"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="17" t="inlineStr"/>
+      <c r="M37" s="17" t="n"/>
       <c r="N37" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5121,11 +5121,11 @@
       <c r="J38" s="9" t="n">
         <v>0.152</v>
       </c>
-      <c r="K38" s="10" t="inlineStr"/>
+      <c r="K38" s="10" t="n"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="n"/>
       <c r="N38" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5159,12 +5159,12 @@
       <c r="I39" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="15" t="inlineStr"/>
-      <c r="K39" s="16" t="inlineStr"/>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="17" t="inlineStr"/>
+      <c r="M39" s="17" t="n"/>
       <c r="N39" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5201,11 +5201,11 @@
       <c r="J40" s="9" t="n">
         <v>0.159</v>
       </c>
-      <c r="K40" s="10" t="inlineStr"/>
+      <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="n"/>
       <c r="N40" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5230,19 +5230,19 @@
       <c r="F41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="15" t="inlineStr"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="15" t="inlineStr"/>
-      <c r="K41" s="16" t="inlineStr"/>
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="17" t="inlineStr"/>
+      <c r="M41" s="17" t="n"/>
       <c r="N41" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5267,19 +5267,19 @@
       <c r="F42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="n"/>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="9" t="inlineStr"/>
-      <c r="K42" s="10" t="inlineStr"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="10" t="n"/>
       <c r="L42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="n"/>
       <c r="N42" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5304,19 +5304,19 @@
       <c r="F43" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="15" t="inlineStr"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="15" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
+      <c r="J43" s="15" t="n"/>
+      <c r="K43" s="16" t="n"/>
       <c r="L43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M43" s="17" t="inlineStr"/>
+      <c r="M43" s="17" t="n"/>
       <c r="N43" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5341,19 +5341,19 @@
       <c r="F44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="9" t="inlineStr"/>
+      <c r="G44" s="9" t="n"/>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="9" t="inlineStr"/>
-      <c r="K44" s="10" t="inlineStr"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="10" t="n"/>
       <c r="L44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="n"/>
       <c r="N44" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5378,19 +5378,19 @@
       <c r="F45" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="15" t="inlineStr"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="15" t="inlineStr"/>
-      <c r="K45" s="16" t="inlineStr"/>
+      <c r="J45" s="15" t="n"/>
+      <c r="K45" s="16" t="n"/>
       <c r="L45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="17" t="inlineStr"/>
+      <c r="M45" s="17" t="n"/>
       <c r="N45" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5415,19 +5415,19 @@
       <c r="F46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="9" t="inlineStr"/>
+      <c r="G46" s="9" t="n"/>
       <c r="H46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="9" t="inlineStr"/>
-      <c r="K46" s="10" t="inlineStr"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="10" t="n"/>
       <c r="L46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="n"/>
       <c r="N46" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5452,19 +5452,19 @@
       <c r="F47" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="15" t="inlineStr"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="15" t="inlineStr"/>
-      <c r="K47" s="16" t="inlineStr"/>
+      <c r="J47" s="15" t="n"/>
+      <c r="K47" s="16" t="n"/>
       <c r="L47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="17" t="inlineStr"/>
+      <c r="M47" s="17" t="n"/>
       <c r="N47" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5489,19 +5489,19 @@
       <c r="F48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="9" t="inlineStr"/>
+      <c r="G48" s="9" t="n"/>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
-      <c r="K48" s="10" t="inlineStr"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="10" t="n"/>
       <c r="L48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="n"/>
       <c r="N48" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
@@ -5526,19 +5526,19 @@
       <c r="F49" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="15" t="inlineStr"/>
+      <c r="G49" s="15" t="n"/>
       <c r="H49" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="15" t="inlineStr"/>
-      <c r="K49" s="16" t="inlineStr"/>
+      <c r="J49" s="15" t="n"/>
+      <c r="K49" s="16" t="n"/>
       <c r="L49" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="17" t="inlineStr"/>
+      <c r="M49" s="17" t="n"/>
       <c r="N49" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 10:13 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 11:28 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 11:28 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 11:41 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 11:41 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 12:19 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 12:19 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 16/10/2026 12:42 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 16/10/2026 12:42 | Market session: 2026-10-15 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 17/10/2026 08:52 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.5000</t>
+          <t>$0.4880</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>21 contracts</t>
+          <t>1,075 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.000 (very low volume (21 contracts): not meaningful)</t>
+          <t>0.002 (call-skewed volume)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,809</t>
+          <t>52,823</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>397</v>
@@ -907,22 +907,22 @@
         <v>0.02</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>1.5616</v>
+        <v>1.2</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>11559</v>
+        <v>628</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7174</v>
+        <v>7176</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>1579</v>
@@ -949,7 +949,7 @@
         <v>0.22</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>2.7475</v>
+        <v>2.8476</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>108926</v>
+        <v>101033</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27428</v>
+        <v>27439</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3364</v>
@@ -991,7 +991,7 @@
         <v>0.123</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>0</v>
@@ -1003,10 +1003,10 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>2.2641</v>
+        <v>2.2621</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>959924</v>
+        <v>929521</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17276</v>
+        <v>17277</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>197</v>
@@ -1033,7 +1033,7 @@
         <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1</v>
+        <v>1032</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>2.051</v>
+        <v>1.996</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>647389</v>
+        <v>652540</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>534</v>
@@ -1087,10 +1087,10 @@
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>3.2868</v>
+        <v>2.6234</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>30676</v>
+        <v>30243</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.5000 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.4880 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-10-16 (0 days) — Max Pain: $0.5</t>
+          <t>VENCIMIENTO: 2026-10-16 (-1 días) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
     </row>
     <row r="7">
       <c r="B7" s="17" t="n">
-        <v>2.3689</v>
+        <v>1.2</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.518</v>
+        <v>0.06</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>9.166600000000001</v>
+        <v>17.5921</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>232</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>0</v>
@@ -1281,43 +1281,43 @@
       <c r="J7" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="M7" s="16" t="n">
+      <c r="K7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="M7" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N7" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="15" t="n">
-        <v>9.183999999999999</v>
-      </c>
-      <c r="Q7" s="15" t="n">
-        <v>-0.483</v>
-      </c>
-      <c r="R7" s="17" t="n">
-        <v>0.0625</v>
+      <c r="O7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25" t="n">
+        <v>17.5921</v>
+      </c>
+      <c r="Q7" s="25" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.0564</v>
+        <v>0</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>154</v>
@@ -1338,36 +1338,36 @@
         <v>0.4</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" s="23" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="N8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="25" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>-0.999</v>
+        <v>-1</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>1.5</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="25" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="25" t="n">
         <v>-1</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
@@ -1441,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M10" s="23" t="n">
         <v>1.44</v>
@@ -1456,13 +1456,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="25" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="25" t="n">
         <v>-1</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1488,16 +1488,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M11" s="23" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="25" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="25" t="n">
         <v>-1</v>
@@ -1547,10 +1547,10 @@
         <v>5</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="M12" s="23" t="n">
         <v>0</v>
@@ -1600,10 +1600,10 @@
         <v>7.5</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="M13" s="23" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (35 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (34 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1722,22 @@
     </row>
     <row r="18">
       <c r="B18" s="17" t="n">
-        <v>1.1397</v>
+        <v>1.2619</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.605</v>
+        <v>0.585</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>1.8289</v>
+        <v>1.8848</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="16" t="n">
         <v>0.05</v>
@@ -1748,46 +1748,46 @@
       <c r="J18" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="16" t="n">
+      <c r="K18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="23" t="n">
         <v>0.75</v>
       </c>
-      <c r="M18" s="16" t="n">
+      <c r="M18" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="24" t="n">
         <v>871</v>
       </c>
-      <c r="O18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>1.8496</v>
-      </c>
-      <c r="Q18" s="15" t="n">
-        <v>-0.409</v>
-      </c>
-      <c r="R18" s="17" t="n">
-        <v>7.3921</v>
+      <c r="O18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25" t="n">
+        <v>1.9062</v>
+      </c>
+      <c r="Q18" s="25" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>7.4489</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>1.8728</v>
+        <v>1.9502</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.246</v>
+        <v>0.239</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.9579</v>
+        <v>0.9542</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>0.05</v>
@@ -1805,7 +1805,7 @@
         <v>0.15</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="M19" s="23" t="n">
         <v>0.45</v>
@@ -1817,24 +1817,24 @@
         <v>0</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>0.9808</v>
+        <v>0.9771</v>
       </c>
       <c r="Q19" s="25" t="n">
-        <v>-0.771</v>
+        <v>-0.778</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>2.0238</v>
+        <v>4.0313</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.5079</v>
+        <v>2.591</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.17</v>
+        <v>0.166</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.6355</v>
+        <v>0.634</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>1.5</v>
       </c>
       <c r="K20" s="23" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M20" s="23" t="n">
         <v>1</v>
@@ -1870,24 +1870,24 @@
         <v>0</v>
       </c>
       <c r="P20" s="25" t="n">
-        <v>0.6601</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="Q20" s="25" t="n">
-        <v>-0.849</v>
+        <v>-0.852</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>3.2213</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>4.7922</v>
+        <v>4.9397</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.137</v>
+        <v>0.134</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.4924</v>
+        <v>0.492</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>2</v>
       </c>
       <c r="K21" s="23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M21" s="23" t="n">
         <v>1.33</v>
@@ -1923,24 +1923,24 @@
         <v>0</v>
       </c>
       <c r="P21" s="25" t="n">
-        <v>0.518</v>
+        <v>0.5194</v>
       </c>
       <c r="Q21" s="25" t="n">
-        <v>-0.884</v>
+        <v>-0.886</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>3.6816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>3.805</v>
+        <v>3.9134</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.4109</v>
+        <v>0.4111</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>0</v>
@@ -1961,10 +1961,10 @@
         <v>2.5</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="M22" s="23" t="n">
         <v>1.87</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="25" t="n">
-        <v>0.4362</v>
+        <v>0.4404</v>
       </c>
       <c r="Q22" s="25" t="n">
-        <v>-0.905</v>
+        <v>-0.906</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="23">
       <c r="B23" s="17" t="n">
-        <v>4.7</v>
+        <v>4.8187</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.2514</v>
+        <v>0.2524</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3331</v>
+        <v>0.2739</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>-0.952</v>
+        <v>-0.951</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>1.2</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="24">
       <c r="B24" s="17" t="n">
-        <v>4.5187</v>
+        <v>4.6255</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.1955</v>
+        <v>0.1966</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>6.3</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="M24" s="23" t="n">
         <v>7.3</v>
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="25" t="n">
-        <v>0.2532</v>
+        <v>0.2004</v>
       </c>
       <c r="Q24" s="25" t="n">
-        <v>-0.976</v>
+        <v>-0.969</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>1.2</v>
@@ -2096,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (91 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (90 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2189,75 +2189,75 @@
     </row>
     <row r="29">
       <c r="B29" s="17" t="n">
-        <v>1.6858</v>
+        <v>1.7823</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.664</v>
+        <v>0.65</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.2184</v>
+        <v>1.2593</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J29" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="K29" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="L29" s="16" t="n">
+      <c r="L29" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="M29" s="16" t="n">
+      <c r="M29" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="N29" s="14" t="n">
+      <c r="N29" s="24" t="n">
         <v>2093</v>
       </c>
-      <c r="O29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="15" t="n">
-        <v>1.2461</v>
-      </c>
-      <c r="Q29" s="15" t="n">
-        <v>-0.368</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>1.3444</v>
+      <c r="O29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="25" t="n">
+        <v>1.2882</v>
+      </c>
+      <c r="Q29" s="25" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>1.3062</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.7162</v>
+        <v>1.771</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.363</v>
+        <v>0.354</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.9212</v>
+        <v>0.9293</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6791</v>
+        <v>6801</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H30" s="16" t="n">
         <v>0.05</v>
@@ -2269,10 +2269,10 @@
         <v>1</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="M30" s="23" t="n">
         <v>0.48</v>
@@ -2284,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="P30" s="25" t="n">
-        <v>0.964</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="Q30" s="25" t="n">
-        <v>-0.676</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>1.6589</v>
+        <v>2.6253</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.8791</v>
+        <v>1.5804</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.272</v>
+        <v>0.264</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.7002</v>
+        <v>0.704</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J31" s="22" t="n">
         <v>1.5</v>
@@ -2325,7 +2325,7 @@
         <v>0.7</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M31" s="23" t="n">
         <v>0.97</v>
@@ -2337,24 +2337,24 @@
         <v>0</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>0.7539</v>
+        <v>0.759</v>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>-0.772</v>
+        <v>-0.779</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>2.6556</v>
+        <v>2.8552</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>4.2015</v>
+        <v>4.3083</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.228</v>
+        <v>0.221</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5833</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
@@ -2375,10 +2375,10 @@
         <v>2</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M32" s="23" t="n">
         <v>1.3</v>
@@ -2390,24 +2390,24 @@
         <v>0</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>0.6439</v>
+        <v>0.6493</v>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>-0.821</v>
+        <v>-0.827</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>2.1132</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.9136</v>
+        <v>2.3982</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.201</v>
+        <v>0.195</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.5069</v>
+        <v>0.5082</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
@@ -2422,16 +2422,16 @@
         <v>0</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J33" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M33" s="23" t="n">
         <v>1.5</v>
@@ -2443,24 +2443,24 @@
         <v>0</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>0.5793</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="Q33" s="25" t="n">
-        <v>-0.852</v>
+        <v>-0.858</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>2.3364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>4.249</v>
+        <v>4.3304</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.347</v>
+        <v>0.3466</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
@@ -2496,24 +2496,24 @@
         <v>0</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>0.4669</v>
+        <v>0.4279</v>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>-0.927</v>
+        <v>-0.931</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>7.125</v>
+        <v>7.1563</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.5647</v>
+        <v>4.6468</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.124</v>
+        <v>0.119</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2859</v>
+        <v>0.285</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>7.5</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M35" s="23" t="n">
         <v>6.2</v>
@@ -2549,33 +2549,33 @@
         <v>0</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>0.4724</v>
+        <v>0.3004</v>
       </c>
       <c r="Q35" s="25" t="n">
-        <v>-0.966</v>
+        <v>-0.962</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>7.4375</v>
+        <v>4.2573</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>2.9977</v>
+        <v>3.0413</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.112</v>
+        <v>0.107</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.2518</v>
+        <v>0.2507</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F36" s="14" t="n">
         <v>55</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H36" s="16" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         <v>10</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="M36" s="23" t="n">
         <v>10</v>
@@ -2602,24 +2602,24 @@
         <v>0</v>
       </c>
       <c r="P36" s="25" t="n">
-        <v>0.1694</v>
+        <v>0.2043</v>
       </c>
       <c r="Q36" s="25" t="n">
-        <v>-0.987</v>
+        <v>-0.978</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>6.1563</v>
+        <v>4.5533</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>3.1436</v>
+        <v>3.1878</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.2295</v>
+        <v>0.2282</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>12.5</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M37" s="23" t="n">
         <v>10.94</v>
@@ -2655,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="25" t="n">
-        <v>0.0044</v>
+        <v>0.1319</v>
       </c>
       <c r="Q37" s="25" t="n">
-        <v>-1</v>
+        <v>-0.987</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>7.75</v>
+        <v>4.7896</v>
       </c>
     </row>
     <row r="38"/>
@@ -2669,7 +2669,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (126 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (125 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2762,75 +2762,75 @@
     </row>
     <row r="42">
       <c r="B42" s="17" t="n">
-        <v>2.9527</v>
+        <v>2.7557</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.664</v>
+        <v>0.663</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.7653</v>
+        <v>0.7687</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F42" s="14" t="n">
         <v>2525</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H42" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="J42" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M42" s="16" t="n">
+      <c r="K42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="N42" s="14" t="n">
+      <c r="N42" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="O42" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="15" t="n">
-        <v>0.7536</v>
-      </c>
-      <c r="Q42" s="15" t="n">
-        <v>-0.316</v>
-      </c>
-      <c r="R42" s="17" t="n">
-        <v>6.9557</v>
+      <c r="O42" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="25" t="n">
+        <v>0.7622</v>
+      </c>
+      <c r="Q42" s="25" t="n">
+        <v>-0.321</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.547</v>
+        <v>1.5881</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.406</v>
+        <v>0.41</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.771</v>
+        <v>0.7763</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>0.05</v>
@@ -2842,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="M43" s="23" t="n">
         <v>0.45</v>
@@ -2857,48 +2857,48 @@
         <v>0</v>
       </c>
       <c r="P43" s="25" t="n">
-        <v>0.7893</v>
+        <v>0.798</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>-0.574</v>
+        <v>-0.575</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.7672</v>
+        <v>1.6875</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>2.1502</v>
+        <v>1.705</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.306</v>
+        <v>0.31</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.6398</v>
+        <v>0.6496</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F44" s="14" t="n">
         <v>5582</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J44" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M44" s="23" t="n">
         <v>1.02</v>
@@ -2910,24 +2910,24 @@
         <v>0</v>
       </c>
       <c r="P44" s="25" t="n">
-        <v>0.6804</v>
+        <v>0.6932</v>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>-0.68</v>
+        <v>-0.681</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>1.7105</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>2.1576</v>
+        <v>3.1126</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.254</v>
+        <v>0.257</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5495</v>
+        <v>0.5602</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
@@ -2942,16 +2942,16 @@
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="J45" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M45" s="23" t="n">
         <v>1.35</v>
@@ -2963,24 +2963,24 @@
         <v>0</v>
       </c>
       <c r="P45" s="25" t="n">
-        <v>0.6098</v>
+        <v>0.6229</v>
       </c>
       <c r="Q45" s="25" t="n">
-        <v>-0.738</v>
+        <v>-0.74</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>1.9819</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.222</v>
+        <v>0.224</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4871</v>
+        <v>0.4975</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         <v>2.5</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M46" s="23" t="n">
         <v>0</v>
@@ -3016,24 +3016,24 @@
         <v>0</v>
       </c>
       <c r="P46" s="25" t="n">
-        <v>0.5652</v>
+        <v>0.5782</v>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>-0.776</v>
+        <v>-0.779</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>1.8825</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.4047</v>
+        <v>4.486</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3371</v>
+        <v>0.3444</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3054,10 +3054,10 @@
         <v>5</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="M47" s="23" t="n">
         <v>0</v>
@@ -3069,24 +3069,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="25" t="n">
-        <v>0.4849</v>
+        <v>0.5059</v>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>-0.878</v>
+        <v>-0.884</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>2.5082</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>0.5</v>
+        <v>6.2495</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2741</v>
+        <v>0.2792</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3101,13 +3101,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J48" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="L48" s="23" t="n">
         <v>8.800000000000001</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="25" t="n">
-        <v>0.5226</v>
+        <v>0.4198</v>
       </c>
       <c r="Q48" s="25" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>1.2</v>
@@ -3136,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (217 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (216 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3229,13 +3229,13 @@
     </row>
     <row r="53">
       <c r="B53" s="17" t="n">
-        <v>3.2752</v>
+        <v>2.2556</v>
       </c>
       <c r="C53" s="15" t="n">
-        <v>0.735</v>
+        <v>0.724</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9837</v>
       </c>
       <c r="E53" s="14" t="n">
         <v>0</v>
@@ -3250,45 +3250,45 @@
         <v>0.1</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="J53" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M53" s="16" t="n">
+      <c r="K53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="N53" s="14" t="n">
+      <c r="N53" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="15" t="n">
-        <v>0.9976</v>
-      </c>
-      <c r="Q53" s="15" t="n">
-        <v>-0.336</v>
-      </c>
-      <c r="R53" s="17" t="n">
-        <v>5.5262</v>
+      <c r="O53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="25" t="n">
+        <v>1.0375</v>
+      </c>
+      <c r="Q53" s="25" t="n">
+        <v>-0.347</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>2.0024</v>
+        <v>2.2314</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.434</v>
+        <v>0.429</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.9205</v>
+        <v>0.9261</v>
       </c>
       <c r="E54" s="14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0.2</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I54" s="16" t="n">
         <v>0.45</v>
@@ -3324,24 +3324,24 @@
         <v>0</v>
       </c>
       <c r="P54" s="25" t="n">
-        <v>1.0376</v>
+        <v>1.0422</v>
       </c>
       <c r="Q54" s="25" t="n">
-        <v>-0.66</v>
+        <v>-0.664</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>1.5061</v>
+        <v>1.4688</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>1.6761</v>
+        <v>1.386</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.7327</v>
+        <v>0.738</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
@@ -3353,19 +3353,19 @@
         <v>0.16</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="J55" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M55" s="23" t="n">
         <v>0</v>
@@ -3377,24 +3377,24 @@
         <v>0</v>
       </c>
       <c r="P55" s="25" t="n">
-        <v>0.8739</v>
+        <v>0.8758</v>
       </c>
       <c r="Q55" s="25" t="n">
-        <v>-0.762</v>
+        <v>-0.763</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>1.8461</v>
+        <v>1.451</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>5.6311</v>
+        <v>6.1343</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.3</v>
+        <v>0.298</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.628</v>
+        <v>0.6334</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
@@ -3430,24 +3430,24 @@
         <v>0</v>
       </c>
       <c r="P56" s="25" t="n">
-        <v>0.7909</v>
+        <v>0.7991</v>
       </c>
       <c r="Q56" s="25" t="n">
         <v>-0.8169999999999999</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>1.73</v>
+        <v>1.6688</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>3.7397</v>
+        <v>3.8404</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.273</v>
+        <v>0.271</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5614</v>
+        <v>0.5667</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
         <v>2.5</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="23" t="n">
         <v>4.7</v>
@@ -3483,24 +3483,24 @@
         <v>0</v>
       </c>
       <c r="P57" s="25" t="n">
-        <v>0.7403</v>
+        <v>0.7459</v>
       </c>
       <c r="Q57" s="25" t="n">
         <v>-0.855</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>1.2</v>
+        <v>4.1539</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>6.0378</v>
+        <v>4.2004</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.209</v>
+        <v>0.208</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.4097</v>
+        <v>0.4146</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
@@ -3515,16 +3515,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J58" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="M58" s="23" t="n">
         <v>0</v>
@@ -3536,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="25" t="n">
-        <v>0.5597</v>
+        <v>0.4601</v>
       </c>
       <c r="Q58" s="25" t="n">
-        <v>-0.96</v>
+        <v>-0.955</v>
       </c>
       <c r="R58" s="26" t="n">
         <v>1.2</v>
@@ -3547,13 +3547,13 @@
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>2.0511</v>
+        <v>2.0764</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3465</v>
+        <v>0.351</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         <v>7.5</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="M59" s="23" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="25" t="n">
-        <v>0.0433</v>
+        <v>0.1748</v>
       </c>
       <c r="Q59" s="25" t="n">
-        <v>-0.997</v>
+        <v>-0.987</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>2.7374</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3714,26 +3714,26 @@
     <row r="6">
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>21</v>
+        <v>1075</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>21</v>
+        <v>1073</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52809</v>
+        <v>52823</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>5156</v>
@@ -3745,10 +3745,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1758474</v>
+        <v>1713965</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.3822</v>
+        <v>2.1858</v>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
@@ -3759,29 +3759,29 @@
     <row r="7">
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -3790,10 +3790,10 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N7" s="30" t="inlineStr">
         <is>
@@ -3804,29 +3804,29 @@
     <row r="8">
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.098</v>
@@ -3835,10 +3835,10 @@
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N8" s="27" t="inlineStr">
         <is>
@@ -3849,29 +3849,29 @@
     <row r="9">
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.098</v>
@@ -3880,10 +3880,10 @@
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N9" s="30" t="inlineStr">
         <is>
@@ -3894,29 +3894,29 @@
     <row r="10">
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.098</v>
@@ -3925,10 +3925,10 @@
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N10" s="27" t="inlineStr">
         <is>
@@ -3939,26 +3939,26 @@
     <row r="11">
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C11" s="31" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>5157</v>
@@ -3970,10 +3970,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N11" s="30" t="inlineStr">
         <is>
@@ -3984,41 +3984,41 @@
     <row r="12">
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>5157</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N12" s="27" t="inlineStr">
         <is>
@@ -4029,29 +4029,29 @@
     <row r="13">
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C13" s="31" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.099</v>
@@ -4060,10 +4060,10 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N13" s="30" t="inlineStr">
         <is>
@@ -4074,29 +4074,29 @@
     <row r="14">
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.099</v>
@@ -4105,10 +4105,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N14" s="27" t="inlineStr">
         <is>
@@ -4119,26 +4119,26 @@
     <row r="15">
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C15" s="31" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>5161</v>
@@ -4150,10 +4150,10 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N15" s="30" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="16">
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>5161</v>
@@ -4195,10 +4195,10 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N16" s="27" t="inlineStr">
         <is>
@@ -4209,29 +4209,29 @@
     <row r="17">
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C17" s="31" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0.099</v>
@@ -4240,10 +4240,10 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
@@ -4254,41 +4254,41 @@
     <row r="18">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>5159</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N18" s="27" t="inlineStr">
         <is>
@@ -4299,29 +4299,29 @@
     <row r="19">
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C19" s="31" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>0.098</v>
@@ -4330,10 +4330,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N19" s="30" t="inlineStr">
         <is>
@@ -4344,29 +4344,29 @@
     <row r="20">
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C20" s="28" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>0.098</v>
@@ -4375,10 +4375,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N20" s="27" t="inlineStr">
         <is>
@@ -4389,26 +4389,26 @@
     <row r="21">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>5156</v>
@@ -4420,10 +4420,10 @@
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N21" s="30" t="inlineStr">
         <is>
@@ -4434,41 +4434,41 @@
     <row r="22">
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C22" s="28" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
@@ -4479,41 +4479,41 @@
     <row r="23">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C23" s="31" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K23" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N23" s="30" t="inlineStr">
         <is>
@@ -4524,41 +4524,41 @@
     <row r="24">
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C24" s="28" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N24" s="27" t="inlineStr">
         <is>
@@ -4569,29 +4569,29 @@
     <row r="25">
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C25" s="31" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>0.093</v>
@@ -4600,10 +4600,10 @@
         <v>0.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
@@ -4614,73 +4614,77 @@
     <row r="26">
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K26" s="10" t="n"/>
+        <v>0.093</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="11" t="n"/>
+        <v>2361798</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N26" s="27" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C27" s="31" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="18" t="n">
@@ -4696,32 +4700,32 @@
     <row r="28">
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C28" s="28" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="12" t="n">
@@ -4737,31 +4741,33 @@
     <row r="29">
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C29" s="31" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="15" t="n"/>
+        <v>7194</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K29" s="16" t="n"/>
       <c r="L29" s="18" t="n">
         <v>0</v>
@@ -4776,23 +4782,23 @@
     <row r="30">
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C30" s="28" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>0</v>
@@ -4815,33 +4821,31 @@
     <row r="31">
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C31" s="31" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J31" s="15" t="n"/>
       <c r="K31" s="16" t="n"/>
       <c r="L31" s="18" t="n">
         <v>0</v>
@@ -4856,31 +4860,33 @@
     <row r="32">
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C32" s="28" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="9" t="n"/>
+        <v>6136</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -4895,23 +4901,23 @@
     <row r="33">
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C33" s="31" t="n">
         <v>1.69</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H33" s="14" t="n">
         <v>0</v>
@@ -4934,33 +4940,31 @@
     <row r="34">
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C34" s="28" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -4975,31 +4979,33 @@
     <row r="35">
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C35" s="31" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="15" t="n"/>
+        <v>5834</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
@@ -5014,33 +5020,31 @@
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C36" s="28" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
@@ -5055,31 +5059,33 @@
     <row r="37">
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C37" s="31" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="15" t="n"/>
+        <v>4272</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
@@ -5094,11 +5100,11 @@
     <row r="38">
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C38" s="28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2568</v>
@@ -5113,14 +5119,12 @@
         <v>0.27</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
@@ -5135,11 +5139,11 @@
     <row r="39">
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C39" s="31" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>2568</v>
@@ -5154,12 +5158,14 @@
         <v>0.27</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="15" t="n"/>
+        <v>4145</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -5174,11 +5180,11 @@
     <row r="40">
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C40" s="28" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>2568</v>
@@ -5193,14 +5199,12 @@
         <v>0.27</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -5215,29 +5219,33 @@
     <row r="41">
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C41" s="31" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="15" t="n"/>
+        <v>546</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H41" s="14" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="15" t="n"/>
+        <v>4059</v>
+      </c>
+      <c r="J41" s="15" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
@@ -5252,11 +5260,11 @@
     <row r="42">
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C42" s="28" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>0</v>
@@ -5289,11 +5297,11 @@
     <row r="43">
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C43" s="31" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
@@ -5326,11 +5334,11 @@
     <row r="44">
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C44" s="28" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>0</v>
@@ -5363,11 +5371,11 @@
     <row r="45">
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C45" s="31" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
@@ -5400,11 +5408,11 @@
     <row r="46">
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C46" s="28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>0</v>
@@ -5437,7 +5445,7 @@
     <row r="47">
       <c r="B47" s="30" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C47" s="31" t="n">
@@ -5474,7 +5482,7 @@
     <row r="48">
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C48" s="28" t="n">
@@ -5511,7 +5519,7 @@
     <row r="49">
       <c r="B49" s="30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C49" s="31" t="n">
@@ -5540,6 +5548,43 @@
       </c>
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="30" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="11" t="n"/>
+      <c r="N50" s="27" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5663,7 +5708,7 @@
         <v>232</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
@@ -5703,7 +5748,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>0</v>
@@ -5743,7 +5788,7 @@
         <v>154</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0</v>
@@ -5783,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>0</v>
@@ -5823,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>0</v>
@@ -5943,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>0</v>
@@ -6220,19 +6265,19 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0</v>
+        <v>1729</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="K20" s="27" t="inlineStr">
         <is>
@@ -6266,7 +6311,7 @@
         <v>871</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>871</v>
@@ -6300,19 +6345,19 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0</v>
+        <v>1612</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="K22" s="27" t="inlineStr">
         <is>
@@ -6346,7 +6391,7 @@
         <v>358</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>358</v>
@@ -6386,7 +6431,7 @@
         <v>2128</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>2128</v>
@@ -6426,7 +6471,7 @@
         <v>150</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>150</v>
@@ -6466,7 +6511,7 @@
         <v>1358</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>1358</v>
@@ -6780,19 +6825,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>10047</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
@@ -6826,7 +6871,7 @@
         <v>2093</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="I35" s="14" t="n">
         <v>2093</v>
@@ -6860,19 +6905,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6791</v>
+        <v>6801</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6791</v>
+        <v>6801</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>6801</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6791</v>
+        <v>6801</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>6791</v>
+        <v>6801</v>
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
@@ -6906,7 +6951,7 @@
         <v>641</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="I37" s="14" t="n">
         <v>641</v>
@@ -6946,7 +6991,7 @@
         <v>1986</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="I38" s="8" t="n">
         <v>1986</v>
@@ -6986,7 +7031,7 @@
         <v>455</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="I39" s="14" t="n">
         <v>455</v>
@@ -7026,7 +7071,7 @@
         <v>2820</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="I40" s="8" t="n">
         <v>2820</v>
@@ -7066,7 +7111,7 @@
         <v>12</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>12</v>
@@ -7106,7 +7151,7 @@
         <v>3053</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>3053</v>
@@ -7186,7 +7231,7 @@
         <v>1986</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>1986</v>
@@ -7266,7 +7311,7 @@
         <v>252</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>252</v>
@@ -7506,7 +7551,7 @@
         <v>2525</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0</v>
+        <v>2525</v>
       </c>
       <c r="I52" s="8" t="n">
         <v>0</v>
@@ -7580,19 +7625,19 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0</v>
+        <v>6487</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>6486</v>
+        <v>6487</v>
       </c>
       <c r="K54" s="27" t="inlineStr">
         <is>
@@ -7626,7 +7671,7 @@
         <v>151</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0</v>
@@ -7666,7 +7711,7 @@
         <v>5582</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0</v>
+        <v>5582</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
@@ -7706,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0</v>
@@ -7746,7 +7791,7 @@
         <v>1071</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0</v>
+        <v>1071</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>0</v>
@@ -7786,7 +7831,7 @@
         <v>41</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>0</v>
@@ -7826,7 +7871,7 @@
         <v>848</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>0</v>
@@ -8066,7 +8111,7 @@
         <v>336</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="I66" s="8" t="n">
         <v>0</v>
@@ -8106,7 +8151,7 @@
         <v>5</v>
       </c>
       <c r="H67" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" s="14" t="n">
         <v>0</v>
@@ -8146,7 +8191,7 @@
         <v>76</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I68" s="8" t="n">
         <v>0</v>
@@ -8186,7 +8231,7 @@
         <v>3</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" s="14" t="n">
         <v>0</v>
@@ -8226,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="8" t="n">
         <v>0</v>
@@ -8306,7 +8351,7 @@
         <v>64</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I72" s="8" t="n">
         <v>0</v>
@@ -8386,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="8" t="n">
         <v>0</v>
@@ -8466,7 +8511,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -8546,7 +8591,7 @@
         <v>36</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I78" s="8" t="n">
         <v>0</v>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -361,7 +361,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6858000" cy="3238500"/>
@@ -389,7 +389,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6858000" cy="3238500"/>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 17/10/2026 08:52 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 18/10/2026 09:02 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1,075 contracts</t>
+          <t>1,068 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.002 (call-skewed volume)</t>
+          <t>0.000 (call-skewed volume)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,823</t>
+          <t>52,426</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,156</t>
+          <t>5,148</t>
         </is>
       </c>
     </row>
@@ -891,38 +891,38 @@
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>397</v>
+        <v>7176</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>8</v>
+        <v>1579</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>1.2</v>
+        <v>2.8502</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>628</v>
+        <v>101033</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -933,23 +933,23 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7176</v>
+        <v>27439</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1579</v>
+        <v>3364</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.22</v>
+        <v>0.123</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H17" s="14" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>2.8476</v>
+        <v>2.2621</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>101033</v>
+        <v>929521</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -975,23 +975,23 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27439</v>
+        <v>17277</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>3364</v>
+        <v>197</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.123</v>
+        <v>0.011</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>30</v>
+        <v>1032</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>0</v>
@@ -1003,10 +1003,10 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>2.2621</v>
+        <v>1.996</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>929521</v>
+        <v>652540</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1017,23 +1017,23 @@
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17277</v>
+        <v>534</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>197</v>
+        <v>8</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>1.996</v>
+        <v>2.6234</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>652540</v>
+        <v>30243</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1056,53 +1056,11 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>216</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>534</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>2.6234</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>30243</v>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Heavy call skew 🟢🟢</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21"/>
     <row r="22"/>
-    <row r="23"/>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>3. CHARTS</t>
         </is>
@@ -1120,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1162,7 +1120,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VENCIMIENTO: 2026-10-16 (-1 días) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (33 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1213,28 @@
     </row>
     <row r="7">
       <c r="B7" s="17" t="n">
-        <v>1.2</v>
+        <v>1.2619</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.06</v>
+        <v>0.585</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>17.5921</v>
+        <v>1.8848</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>232</v>
+        <v>1729</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J7" s="22" t="n">
         <v>0.5</v>
@@ -1285,45 +1243,45 @@
         <v>0</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="M7" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="N7" s="24" t="n">
-        <v>6</v>
+        <v>871</v>
       </c>
       <c r="O7" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>17.5921</v>
+        <v>1.9062</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.429</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>1.2</v>
+        <v>7.4489</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>1.2</v>
+        <v>1.9502</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0</v>
+        <v>0.9542</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>154</v>
+        <v>1612</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>0</v>
@@ -1335,45 +1293,45 @@
         <v>1</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M8" s="23" t="n">
         <v>0.45</v>
       </c>
       <c r="N8" s="24" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="O8" s="24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="25" t="n">
-        <v>0</v>
+        <v>0.9771</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>-1</v>
+        <v>-0.778</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>1.2</v>
+        <v>4.0938</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>1.2</v>
+        <v>2.591</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0</v>
+        <v>0.634</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>11</v>
+        <v>2128</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.05</v>
@@ -1382,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="J9" s="22" t="n">
         <v>1.5</v>
@@ -1394,19 +1352,19 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O9" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="25" t="n">
-        <v>0</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="Q9" s="25" t="n">
-        <v>-1</v>
+        <v>-0.852</v>
       </c>
       <c r="R9" s="26" t="n">
         <v>1.2</v>
@@ -1414,28 +1372,28 @@
     </row>
     <row r="10">
       <c r="B10" s="17" t="n">
-        <v>1.2</v>
+        <v>4.9397</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="22" t="n">
         <v>2</v>
@@ -1447,101 +1405,101 @@
         <v>2</v>
       </c>
       <c r="M10" s="23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="O10" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="25" t="n">
-        <v>0</v>
+        <v>0.5194</v>
       </c>
       <c r="Q10" s="25" t="n">
-        <v>-1</v>
+        <v>-0.886</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="n">
-        <v>1.2</v>
+        <v>3.9134</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0</v>
+        <v>0.4111</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M11" s="23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="O11" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="25" t="n">
-        <v>0</v>
+        <v>0.4404</v>
       </c>
       <c r="Q11" s="25" t="n">
-        <v>-1</v>
+        <v>-0.906</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="n">
-        <v>1.2</v>
+        <v>4.8187</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0</v>
+        <v>0.2524</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J12" s="22" t="n">
         <v>5</v>
@@ -1553,7 +1511,7 @@
         <v>5.1</v>
       </c>
       <c r="M12" s="23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N12" s="24" t="n">
         <v>0</v>
@@ -1562,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>0</v>
+        <v>0.2739</v>
       </c>
       <c r="Q12" s="25" t="n">
-        <v>-1</v>
+        <v>-0.951</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>1.2</v>
@@ -1573,22 +1531,22 @@
     </row>
     <row r="13">
       <c r="B13" s="17" t="n">
-        <v>1.2</v>
+        <v>4.6255</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0</v>
+        <v>0.1966</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>0</v>
@@ -1606,7 +1564,7 @@
         <v>7.5</v>
       </c>
       <c r="M13" s="23" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N13" s="24" t="n">
         <v>0</v>
@@ -1615,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="P13" s="25" t="n">
-        <v>0</v>
+        <v>0.2004</v>
       </c>
       <c r="Q13" s="25" t="n">
-        <v>-1</v>
+        <v>-0.969</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>1.2</v>
@@ -1629,7 +1587,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (34 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (89 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1722,128 +1680,128 @@
     </row>
     <row r="18">
       <c r="B18" s="17" t="n">
-        <v>1.2619</v>
+        <v>1.7823</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.585</v>
+        <v>0.65</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>1.8848</v>
+        <v>1.2593</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H18" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J18" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="M18" s="23" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="O18" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="25" t="n">
-        <v>1.9062</v>
+        <v>1.2882</v>
       </c>
       <c r="Q18" s="25" t="n">
-        <v>-0.429</v>
+        <v>-0.382</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>7.4489</v>
+        <v>1.3062</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>1.9502</v>
+        <v>1.771</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.239</v>
+        <v>0.354</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.9542</v>
+        <v>0.9293</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="G19" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="H19" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>0.65</v>
+        <v>1.1</v>
       </c>
       <c r="M19" s="23" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="N19" s="24" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="O19" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>0.9771</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="Q19" s="25" t="n">
-        <v>-0.778</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>4.0313</v>
+        <v>2.6253</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.591</v>
+        <v>1.5804</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.166</v>
+        <v>0.264</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.634</v>
+        <v>0.704</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H20" s="16" t="n">
         <v>0</v>
@@ -1855,45 +1813,45 @@
         <v>1.5</v>
       </c>
       <c r="K20" s="23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M20" s="23" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="O20" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="25" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="Q20" s="25" t="n">
-        <v>-0.852</v>
+        <v>-0.779</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>1.2</v>
+        <v>2.8552</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>4.9397</v>
+        <v>4.3083</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.134</v>
+        <v>0.221</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.492</v>
+        <v>0.5833</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="G21" s="16" t="n">
         <v>0.03</v>
@@ -1902,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J21" s="22" t="n">
         <v>2</v>
@@ -1914,42 +1872,42 @@
         <v>2</v>
       </c>
       <c r="M21" s="23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="O21" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="25" t="n">
-        <v>0.5194</v>
+        <v>0.6493</v>
       </c>
       <c r="Q21" s="25" t="n">
-        <v>-0.886</v>
+        <v>-0.827</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>3.9134</v>
+        <v>2.3982</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.115</v>
+        <v>0.195</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.4111</v>
+        <v>0.5082</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>301</v>
+        <v>3053</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="16" t="n">
         <v>0</v>
@@ -1961,25 +1919,25 @@
         <v>2.5</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M22" s="23" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="O22" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="25" t="n">
-        <v>0.4404</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="Q22" s="25" t="n">
-        <v>-0.906</v>
+        <v>-0.858</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -1987,93 +1945,93 @@
     </row>
     <row r="23">
       <c r="B23" s="17" t="n">
-        <v>4.8187</v>
+        <v>4.3304</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.076</v>
+        <v>0.14</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.2524</v>
+        <v>0.3466</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="J23" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K23" s="23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M23" s="23" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.2739</v>
+        <v>0.4279</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>-0.951</v>
+        <v>-0.931</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>1.2</v>
+        <v>7.1875</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="17" t="n">
-        <v>4.6255</v>
+        <v>4.6468</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>0.062</v>
+        <v>0.119</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.1966</v>
+        <v>0.285</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="J24" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K24" s="23" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M24" s="23" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="N24" s="24" t="n">
         <v>0</v>
@@ -2082,341 +2040,341 @@
         <v>0</v>
       </c>
       <c r="P24" s="25" t="n">
-        <v>0.2004</v>
+        <v>0.3004</v>
       </c>
       <c r="Q24" s="25" t="n">
-        <v>-0.969</v>
+        <v>-0.962</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRATION: 2027-01-15 (90 days) — Max Pain: $0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+        <v>4.2573</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="17" t="n">
+        <v>3.0413</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" s="23" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="25" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="Q25" s="25" t="n">
+        <v>-0.978</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>4.5533</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="17" t="n">
+        <v>3.1878</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>439</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J26" s="22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K26" s="23" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L26" s="23" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M26" s="23" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="25" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="Q26" s="25" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>4.7896</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRATION: 2027-02-19 (124 days) — Max Pain: $0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>CALLS — IV</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Last</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>STRIKE</t>
         </is>
       </c>
-      <c r="K28" s="21" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="M28" s="21" t="inlineStr">
+      <c r="M30" s="21" t="inlineStr">
         <is>
           <t>Last</t>
         </is>
       </c>
-      <c r="N28" s="21" t="inlineStr">
+      <c r="N30" s="21" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="O28" s="21" t="inlineStr">
+      <c r="O30" s="21" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="P28" s="21" t="inlineStr">
+      <c r="P30" s="21" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="Q28" s="21" t="inlineStr">
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="R28" s="21" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
         <is>
           <t>PUTS — IV</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="17" t="n">
-        <v>1.7823</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>1.2593</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>10047</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L29" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M29" s="23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N29" s="24" t="n">
-        <v>2093</v>
-      </c>
-      <c r="O29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="25" t="n">
-        <v>1.2882</v>
-      </c>
-      <c r="Q29" s="25" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="R29" s="26" t="n">
-        <v>1.3062</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="17" t="n">
-        <v>1.771</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>0.9293</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>6801</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M30" s="23" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>641</v>
-      </c>
-      <c r="O30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="25" t="n">
-        <v>0.9733000000000001</v>
-      </c>
-      <c r="Q30" s="25" t="n">
-        <v>-0.6850000000000001</v>
-      </c>
-      <c r="R30" s="26" t="n">
-        <v>2.6253</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.5804</v>
+        <v>2.7557</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.264</v>
+        <v>0.663</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.704</v>
+        <v>0.7687</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="M31" s="23" t="n">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="N31" s="24" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="O31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>0.759</v>
+        <v>0.7622</v>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>-0.779</v>
+        <v>-0.321</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>2.8552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>4.3083</v>
+        <v>1.5881</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.221</v>
+        <v>0.41</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5833</v>
+        <v>0.7763</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="M32" s="23" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="O32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>0.6493</v>
+        <v>0.798</v>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>-0.827</v>
+        <v>-0.575</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>1.2</v>
+        <v>1.6875</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.3982</v>
+        <v>1.705</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.195</v>
+        <v>0.31</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.5082</v>
+        <v>0.6496</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>0</v>
@@ -2425,51 +2383,51 @@
         <v>0.1</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L33" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="L33" s="23" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M33" s="23" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="O33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6932</v>
       </c>
       <c r="Q33" s="25" t="n">
-        <v>-0.858</v>
+        <v>-0.681</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>4.3304</v>
+        <v>3.1126</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.14</v>
+        <v>0.257</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.3466</v>
+        <v>0.5602</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H34" s="16" t="n">
         <v>0</v>
@@ -2478,69 +2436,69 @@
         <v>0.35</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M34" s="23" t="n">
-        <v>3.8</v>
+        <v>1.35</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="O34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>0.4279</v>
+        <v>0.6229</v>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>-0.931</v>
+        <v>-0.74</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>7.1563</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.6468</v>
+        <v>1.2</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.119</v>
+        <v>0.224</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.285</v>
+        <v>0.4975</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="M35" s="23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N35" s="24" t="n">
         <v>0</v>
@@ -2549,51 +2507,51 @@
         <v>0</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>0.3004</v>
+        <v>0.5782</v>
       </c>
       <c r="Q35" s="25" t="n">
-        <v>-0.962</v>
+        <v>-0.779</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>4.2573</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>3.0413</v>
+        <v>4.486</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.107</v>
+        <v>0.152</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.2507</v>
+        <v>0.3444</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>9.1</v>
+        <v>3.9</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>10.1</v>
+        <v>5.1</v>
       </c>
       <c r="M36" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N36" s="24" t="n">
         <v>0</v>
@@ -2602,51 +2560,51 @@
         <v>0</v>
       </c>
       <c r="P36" s="25" t="n">
-        <v>0.2043</v>
+        <v>0.5059</v>
       </c>
       <c r="Q36" s="25" t="n">
-        <v>-0.978</v>
+        <v>-0.884</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>4.5533</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>3.1878</v>
+        <v>6.2495</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.1</v>
+        <v>0.122</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.2282</v>
+        <v>0.2792</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>11.6</v>
+        <v>6.2</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>12.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M37" s="23" t="n">
-        <v>10.94</v>
+        <v>0</v>
       </c>
       <c r="N37" s="24" t="n">
         <v>0</v>
@@ -2655,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="25" t="n">
-        <v>0.1319</v>
+        <v>0.4198</v>
       </c>
       <c r="Q37" s="25" t="n">
-        <v>-0.987</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>4.7896</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="38"/>
@@ -2669,7 +2627,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (125 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (215 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2720,28 @@
     </row>
     <row r="42">
       <c r="B42" s="17" t="n">
-        <v>2.7557</v>
+        <v>2.2556</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.663</v>
+        <v>0.724</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.7687</v>
+        <v>0.9837</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>2525</v>
+        <v>336</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="J42" s="22" t="n">
         <v>0.5</v>
@@ -2795,98 +2753,98 @@
         <v>1</v>
       </c>
       <c r="M42" s="23" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="N42" s="24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="25" t="n">
-        <v>0.7622</v>
+        <v>1.0375</v>
       </c>
       <c r="Q42" s="25" t="n">
-        <v>-0.321</v>
+        <v>-0.347</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.5881</v>
+        <v>2.2314</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.41</v>
+        <v>0.429</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.7763</v>
+        <v>0.9261</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6487</v>
+        <v>76</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="J43" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="M43" s="23" t="n">
-        <v>0.45</v>
+        <v>0.59</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="O43" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="25" t="n">
-        <v>0.798</v>
+        <v>1.0422</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>-0.575</v>
+        <v>-0.664</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.6875</v>
+        <v>1.4688</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.705</v>
+        <v>1.386</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.31</v>
+        <v>0.341</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.6496</v>
+        <v>0.738</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I44" s="16" t="n">
         <v>0.1</v>
@@ -2895,116 +2853,116 @@
         <v>1.5</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M44" s="23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N44" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="25" t="n">
-        <v>0.6932</v>
+        <v>0.8758</v>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>-0.681</v>
+        <v>-0.763</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>1.2</v>
+        <v>1.451</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>3.1126</v>
+        <v>6.1343</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.257</v>
+        <v>0.298</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5602</v>
+        <v>0.6334</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="J45" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M45" s="23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="N45" s="24" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O45" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="25" t="n">
-        <v>0.6229</v>
+        <v>0.7991</v>
       </c>
       <c r="Q45" s="25" t="n">
-        <v>-0.74</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>1.2</v>
+        <v>1.6688</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>1.2</v>
+        <v>3.8404</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.224</v>
+        <v>0.271</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4975</v>
+        <v>0.5667</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H46" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J46" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="M46" s="23" t="n">
         <v>0</v>
@@ -3016,30 +2974,30 @@
         <v>0</v>
       </c>
       <c r="P46" s="25" t="n">
-        <v>0.5782</v>
+        <v>0.7459</v>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>-0.779</v>
+        <v>-0.855</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>1.2</v>
+        <v>4.1539</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.486</v>
+        <v>4.2004</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.152</v>
+        <v>0.208</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3444</v>
+        <v>0.4146</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>0.05</v>
@@ -3048,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J47" s="22" t="n">
         <v>5</v>
@@ -3057,7 +3015,7 @@
         <v>3.9</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="M47" s="23" t="n">
         <v>0</v>
@@ -3069,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="25" t="n">
-        <v>0.5059</v>
+        <v>0.4601</v>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>-0.884</v>
+        <v>-0.955</v>
       </c>
       <c r="R47" s="26" t="n">
         <v>1.2</v>
@@ -3080,28 +3038,28 @@
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>6.2495</v>
+        <v>2.0764</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.122</v>
+        <v>0.179</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2792</v>
+        <v>0.351</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="J48" s="22" t="n">
         <v>7.5</v>
@@ -3110,7 +3068,7 @@
         <v>6.2</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="M48" s="23" t="n">
         <v>0</v>
@@ -3122,479 +3080,12 @@
         <v>0</v>
       </c>
       <c r="P48" s="25" t="n">
-        <v>0.4198</v>
+        <v>0.1748</v>
       </c>
       <c r="Q48" s="25" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.987</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRATION: 2027-05-21 (216 days) — Max Pain: $0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>CALLS — IV</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>STRIKE</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
-        <is>
-          <t>Last</t>
-        </is>
-      </c>
-      <c r="N52" s="21" t="inlineStr">
-        <is>
-          <t>OI</t>
-        </is>
-      </c>
-      <c r="O52" s="21" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="P52" s="21" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="Q52" s="21" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="R52" s="21" t="inlineStr">
-        <is>
-          <t>PUTS — IV</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="17" t="n">
-        <v>2.2556</v>
-      </c>
-      <c r="C53" s="15" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="D53" s="15" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>336</v>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I53" s="16" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J53" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N53" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="25" t="n">
-        <v>1.0375</v>
-      </c>
-      <c r="Q53" s="25" t="n">
-        <v>-0.347</v>
-      </c>
-      <c r="R53" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="17" t="n">
-        <v>2.2314</v>
-      </c>
-      <c r="C54" s="15" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>0.9261</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="G54" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I54" s="16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J54" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L54" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M54" s="23" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N54" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O54" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="25" t="n">
-        <v>1.0422</v>
-      </c>
-      <c r="Q54" s="25" t="n">
-        <v>-0.664</v>
-      </c>
-      <c r="R54" s="26" t="n">
-        <v>1.4688</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="17" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="C55" s="15" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="D55" s="15" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H55" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J55" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K55" s="23" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L55" s="23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="25" t="n">
-        <v>0.8758</v>
-      </c>
-      <c r="Q55" s="25" t="n">
-        <v>-0.763</v>
-      </c>
-      <c r="R55" s="26" t="n">
-        <v>1.451</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="17" t="n">
-        <v>6.1343</v>
-      </c>
-      <c r="C56" s="15" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="D56" s="15" t="n">
-        <v>0.6334</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="G56" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K56" s="23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L56" s="23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="25" t="n">
-        <v>0.7991</v>
-      </c>
-      <c r="Q56" s="25" t="n">
-        <v>-0.8169999999999999</v>
-      </c>
-      <c r="R56" s="26" t="n">
-        <v>1.6688</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="17" t="n">
-        <v>3.8404</v>
-      </c>
-      <c r="C57" s="15" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="D57" s="15" t="n">
-        <v>0.5667</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J57" s="22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="25" t="n">
-        <v>0.7459</v>
-      </c>
-      <c r="Q57" s="25" t="n">
-        <v>-0.855</v>
-      </c>
-      <c r="R57" s="26" t="n">
-        <v>4.1539</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="17" t="n">
-        <v>4.2004</v>
-      </c>
-      <c r="C58" s="15" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="D58" s="15" t="n">
-        <v>0.4146</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G58" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J58" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L58" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="M58" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="25" t="n">
-        <v>0.4601</v>
-      </c>
-      <c r="Q58" s="25" t="n">
-        <v>-0.955</v>
-      </c>
-      <c r="R58" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="17" t="n">
-        <v>2.0764</v>
-      </c>
-      <c r="C59" s="15" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="D59" s="15" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="G59" s="16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H59" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J59" s="22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K59" s="23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L59" s="23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M59" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="25" t="n">
-        <v>0.1748</v>
-      </c>
-      <c r="Q59" s="25" t="n">
-        <v>-0.987</v>
-      </c>
-      <c r="R59" s="26" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -3721,22 +3212,22 @@
         <v>0.488</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52823</v>
+        <v>52426</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5156</v>
+        <v>5148</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.098</v>
@@ -3745,10 +3236,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1713965</v>
+        <v>1713337</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.1858</v>
+        <v>2.4329</v>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
@@ -5601,7 +5092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5688,12 +5179,12 @@
     <row r="6">
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00000500</t>
+          <t>OTLK261120C00000500</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
@@ -5705,19 +5196,19 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>232</v>
+        <v>1729</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>1729</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>1729</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>232</v>
+        <v>1729</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>232</v>
+        <v>1729</v>
       </c>
       <c r="K6" s="27" t="inlineStr">
         <is>
@@ -5728,12 +5219,12 @@
     <row r="7">
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00000500</t>
+          <t>OTLK261120P00000500</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D7" s="16" t="n">
@@ -5745,19 +5236,19 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6</v>
+        <v>871</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>6</v>
+        <v>871</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>6</v>
+        <v>871</v>
       </c>
       <c r="K7" s="30" t="inlineStr">
         <is>
@@ -5768,12 +5259,12 @@
     <row r="8">
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00001000</t>
+          <t>OTLK261120C00001000</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
@@ -5785,19 +5276,19 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>154</v>
+        <v>1612</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0</v>
+        <v>1612</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0</v>
+        <v>1612</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>154</v>
+        <v>1612</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>154</v>
+        <v>1612</v>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
@@ -5808,12 +5299,12 @@
     <row r="9">
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00001000</t>
+          <t>OTLK261120P00001000</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D9" s="16" t="n">
@@ -5825,19 +5316,19 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="K9" s="30" t="inlineStr">
         <is>
@@ -5848,12 +5339,12 @@
     <row r="10">
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00001500</t>
+          <t>OTLK261120C00001500</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
@@ -5865,19 +5356,19 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>11</v>
+        <v>2128</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>11</v>
+        <v>2128</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>11</v>
+        <v>2128</v>
       </c>
       <c r="K10" s="27" t="inlineStr">
         <is>
@@ -5888,12 +5379,12 @@
     <row r="11">
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00001500</t>
+          <t>OTLK261120P00001500</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D11" s="16" t="n">
@@ -5905,19 +5396,19 @@
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K11" s="30" t="inlineStr">
         <is>
@@ -5928,12 +5419,12 @@
     <row r="12">
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00002000</t>
+          <t>OTLK261120C00002000</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
@@ -5945,19 +5436,19 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="K12" s="27" t="inlineStr">
         <is>
@@ -5968,12 +5459,12 @@
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00002000</t>
+          <t>OTLK261120P00002000</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
@@ -5985,19 +5476,19 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="K13" s="30" t="inlineStr">
         <is>
@@ -6008,12 +5499,12 @@
     <row r="14">
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00002500</t>
+          <t>OTLK261120C00002500</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
@@ -6025,19 +5516,19 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="K14" s="27" t="inlineStr">
         <is>
@@ -6048,12 +5539,12 @@
     <row r="15">
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00002500</t>
+          <t>OTLK261120P00002500</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
@@ -6065,19 +5556,19 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H15" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K15" s="30" t="inlineStr">
         <is>
@@ -6088,12 +5579,12 @@
     <row r="16">
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00005000</t>
+          <t>OTLK261120C00005000</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -6105,19 +5596,19 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K16" s="27" t="inlineStr">
         <is>
@@ -6128,12 +5619,12 @@
     <row r="17">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00005000</t>
+          <t>OTLK261120P00005000</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D17" s="16" t="n">
@@ -6168,12 +5659,12 @@
     <row r="18">
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>OTLK261016C00007500</t>
+          <t>OTLK261120C00007500</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
@@ -6185,19 +5676,19 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K18" s="27" t="inlineStr">
         <is>
@@ -6208,12 +5699,12 @@
     <row r="19">
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>OTLK261016P00007500</t>
+          <t>OTLK261120P00007500</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
@@ -6248,12 +5739,12 @@
     <row r="20">
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00000500</t>
+          <t>OTLK270115C00000500</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
@@ -6265,19 +5756,19 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1729</v>
+        <v>10047</v>
       </c>
       <c r="K20" s="27" t="inlineStr">
         <is>
@@ -6288,12 +5779,12 @@
     <row r="21">
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00000500</t>
+          <t>OTLK270115P00000500</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D21" s="16" t="n">
@@ -6305,19 +5796,19 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>871</v>
+        <v>2093</v>
       </c>
       <c r="K21" s="30" t="inlineStr">
         <is>
@@ -6328,12 +5819,12 @@
     <row r="22">
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00001000</t>
+          <t>OTLK270115C00001000</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
@@ -6345,19 +5836,19 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>1612</v>
+        <v>6801</v>
       </c>
       <c r="K22" s="27" t="inlineStr">
         <is>
@@ -6368,12 +5859,12 @@
     <row r="23">
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00001000</t>
+          <t>OTLK270115P00001000</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
@@ -6385,19 +5876,19 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>358</v>
+        <v>641</v>
       </c>
       <c r="K23" s="30" t="inlineStr">
         <is>
@@ -6408,12 +5899,12 @@
     <row r="24">
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00001500</t>
+          <t>OTLK270115C00001500</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
@@ -6425,19 +5916,19 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>2128</v>
+        <v>1986</v>
       </c>
       <c r="K24" s="27" t="inlineStr">
         <is>
@@ -6448,12 +5939,12 @@
     <row r="25">
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00001500</t>
+          <t>OTLK270115P00001500</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
@@ -6465,19 +5956,19 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="K25" s="30" t="inlineStr">
         <is>
@@ -6488,12 +5979,12 @@
     <row r="26">
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00002000</t>
+          <t>OTLK270115C00002000</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
@@ -6505,19 +5996,19 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>1358</v>
+        <v>2820</v>
       </c>
       <c r="K26" s="27" t="inlineStr">
         <is>
@@ -6528,12 +6019,12 @@
     <row r="27">
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00002000</t>
+          <t>OTLK270115P00002000</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
@@ -6545,19 +6036,19 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="K27" s="30" t="inlineStr">
         <is>
@@ -6568,12 +6059,12 @@
     <row r="28">
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00002500</t>
+          <t>OTLK270115C00002500</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
@@ -6585,19 +6076,19 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>301</v>
+        <v>3053</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>301</v>
+        <v>3053</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>301</v>
+        <v>3053</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>301</v>
+        <v>3053</v>
       </c>
       <c r="K28" s="27" t="inlineStr">
         <is>
@@ -6608,12 +6099,12 @@
     <row r="29">
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00002500</t>
+          <t>OTLK270115P00002500</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -6625,19 +6116,19 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="H29" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="K29" s="30" t="inlineStr">
         <is>
@@ -6648,12 +6139,12 @@
     <row r="30">
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00005000</t>
+          <t>OTLK270115C00005000</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
@@ -6665,19 +6156,19 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>29</v>
+        <v>1986</v>
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
@@ -6686,54 +6177,54 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>OTLK261120P00005000</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>OTLK270115P00005000</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="F31" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="36" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>OTLK261120C00007500</t>
+          <t>OTLK270115C00007500</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -6745,19 +6236,19 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="K32" s="27" t="inlineStr">
         <is>
@@ -6768,12 +6259,12 @@
     <row r="33">
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>OTLK261120P00007500</t>
+          <t>OTLK270115P00007500</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
@@ -6808,7 +6299,7 @@
     <row r="34">
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00000500</t>
+          <t>OTLK270115C00010000</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -6817,7 +6308,7 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
@@ -6825,19 +6316,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>10047</v>
+        <v>55</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10047</v>
+        <v>55</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>10047</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>10047</v>
+        <v>55</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>10047</v>
+        <v>55</v>
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
@@ -6848,7 +6339,7 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00000500</t>
+          <t>OTLK270115P00010000</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -6857,7 +6348,7 @@
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -6865,19 +6356,19 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
@@ -6888,7 +6379,7 @@
     <row r="36">
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00001000</t>
+          <t>OTLK270115C00012500</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -6897,7 +6388,7 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
@@ -6905,19 +6396,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6801</v>
+        <v>439</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6801</v>
+        <v>439</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>6801</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6801</v>
+        <v>439</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>6801</v>
+        <v>439</v>
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
@@ -6928,7 +6419,7 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001000</t>
+          <t>OTLK270115P00012500</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
@@ -6937,7 +6428,7 @@
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -6945,19 +6436,19 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
@@ -6968,16 +6459,16 @@
     <row r="38">
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00001500</t>
+          <t>OTLK270219C00000500</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
@@ -6985,19 +6476,19 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>1986</v>
+        <v>2525</v>
       </c>
       <c r="K38" s="27" t="inlineStr">
         <is>
@@ -7008,16 +6499,16 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00001500</t>
+          <t>OTLK270219P00000500</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -7025,19 +6516,19 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>455</v>
+        <v>4</v>
       </c>
       <c r="K39" s="30" t="inlineStr">
         <is>
@@ -7048,16 +6539,16 @@
     <row r="40">
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00002000</t>
+          <t>OTLK270219C00001000</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
@@ -7065,19 +6556,19 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>2820</v>
+        <v>6487</v>
       </c>
       <c r="K40" s="27" t="inlineStr">
         <is>
@@ -7088,16 +6579,16 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002000</t>
+          <t>OTLK270219P00001000</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -7105,19 +6596,19 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="K41" s="30" t="inlineStr">
         <is>
@@ -7128,16 +6619,16 @@
     <row r="42">
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00002500</t>
+          <t>OTLK270219C00001500</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
@@ -7145,19 +6636,19 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>3053</v>
+        <v>5582</v>
       </c>
       <c r="K42" s="27" t="inlineStr">
         <is>
@@ -7168,16 +6659,16 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00002500</t>
+          <t>OTLK270219P00001500</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D43" s="16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -7185,19 +6676,19 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="K43" s="30" t="inlineStr">
         <is>
@@ -7208,16 +6699,16 @@
     <row r="44">
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00005000</t>
+          <t>OTLK270219C00002000</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
@@ -7225,19 +6716,19 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>1986</v>
+        <v>1071</v>
       </c>
       <c r="K44" s="27" t="inlineStr">
         <is>
@@ -7246,58 +6737,58 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>OTLK270115P00005000</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" s="36" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>OTLK270219P00002000</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" s="36" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="F45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K45" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00007500</t>
+          <t>OTLK270219C00002500</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
@@ -7305,19 +6796,19 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="K46" s="27" t="inlineStr">
         <is>
@@ -7328,16 +6819,16 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00007500</t>
+          <t>OTLK270219P00002500</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -7368,16 +6859,16 @@
     <row r="48">
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00010000</t>
+          <t>OTLK270219C00005000</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
@@ -7385,19 +6876,19 @@
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>55</v>
+        <v>732</v>
       </c>
       <c r="K48" s="27" t="inlineStr">
         <is>
@@ -7408,16 +6899,16 @@
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00010000</t>
+          <t>OTLK270219P00005000</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
@@ -7448,16 +6939,16 @@
     <row r="50">
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>OTLK270115C00012500</t>
+          <t>OTLK270219C00007500</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
@@ -7465,19 +6956,19 @@
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>439</v>
+        <v>32</v>
       </c>
       <c r="K50" s="27" t="inlineStr">
         <is>
@@ -7488,16 +6979,16 @@
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>OTLK270115P00012500</t>
+          <t>OTLK270219P00007500</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
@@ -7528,12 +7019,12 @@
     <row r="52">
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00000500</t>
+          <t>OTLK270521C00000500</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
@@ -7545,19 +7036,19 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2525</v>
+        <v>336</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2525</v>
+        <v>336</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2525</v>
+        <v>336</v>
       </c>
       <c r="I52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>2525</v>
+        <v>336</v>
       </c>
       <c r="K52" s="27" t="inlineStr">
         <is>
@@ -7568,12 +7059,12 @@
     <row r="53">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00000500</t>
+          <t>OTLK270521P00000500</t>
         </is>
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
@@ -7585,19 +7076,19 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53" s="30" t="inlineStr">
         <is>
@@ -7608,12 +7099,12 @@
     <row r="54">
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00001000</t>
+          <t>OTLK270521C00001000</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
@@ -7625,19 +7116,19 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>6487</v>
+        <v>76</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>6487</v>
+        <v>76</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>6487</v>
+        <v>76</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>6487</v>
+        <v>76</v>
       </c>
       <c r="K54" s="27" t="inlineStr">
         <is>
@@ -7648,12 +7139,12 @@
     <row r="55">
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001000</t>
+          <t>OTLK270521P00001000</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D55" s="16" t="n">
@@ -7665,19 +7156,19 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
@@ -7688,12 +7179,12 @@
     <row r="56">
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00001500</t>
+          <t>OTLK270521C00001500</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
@@ -7705,19 +7196,19 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>5582</v>
+        <v>1</v>
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
@@ -7728,12 +7219,12 @@
     <row r="57">
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00001500</t>
+          <t>OTLK270521P00001500</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D57" s="16" t="n">
@@ -7745,19 +7236,19 @@
         </is>
       </c>
       <c r="F57" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
@@ -7768,12 +7259,12 @@
     <row r="58">
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002000</t>
+          <t>OTLK270521C00002000</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
@@ -7785,19 +7276,19 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1071</v>
+        <v>64</v>
       </c>
       <c r="K58" s="27" t="inlineStr">
         <is>
@@ -7808,12 +7299,12 @@
     <row r="59">
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00002000</t>
+          <t>OTLK270521P00002000</t>
         </is>
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D59" s="16" t="n">
@@ -7825,19 +7316,19 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K59" s="30" t="inlineStr">
         <is>
@@ -7848,12 +7339,12 @@
     <row r="60">
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00002500</t>
+          <t>OTLK270521C00002500</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
@@ -7865,19 +7356,19 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>848</v>
+        <v>1</v>
       </c>
       <c r="K60" s="27" t="inlineStr">
         <is>
@@ -7888,12 +7379,12 @@
     <row r="61">
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00002500</t>
+          <t>OTLK270521P00002500</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D61" s="16" t="n">
@@ -7928,12 +7419,12 @@
     <row r="62">
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00005000</t>
+          <t>OTLK270521C00005000</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
@@ -7945,19 +7436,19 @@
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>732</v>
+        <v>20</v>
       </c>
       <c r="K62" s="27" t="inlineStr">
         <is>
@@ -7968,12 +7459,12 @@
     <row r="63">
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00005000</t>
+          <t>OTLK270521P00005000</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D63" s="16" t="n">
@@ -8008,12 +7499,12 @@
     <row r="64">
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>OTLK270219C00007500</t>
+          <t>OTLK270521C00007500</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
@@ -8025,19 +7516,19 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K64" s="27" t="inlineStr">
         <is>
@@ -8048,12 +7539,12 @@
     <row r="65">
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>OTLK270219P00007500</t>
+          <t>OTLK270521P00007500</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="D65" s="16" t="n">
@@ -8080,566 +7571,6 @@
         <v>0</v>
       </c>
       <c r="K65" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00000500</t>
-        </is>
-      </c>
-      <c r="C66" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E66" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="K66" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00000500</t>
-        </is>
-      </c>
-      <c r="C67" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E67" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H67" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K67" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00001000</t>
-        </is>
-      </c>
-      <c r="C68" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="K68" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00001000</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H69" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I69" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00001500</t>
-        </is>
-      </c>
-      <c r="C70" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00001500</t>
-        </is>
-      </c>
-      <c r="C71" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E71" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00002000</t>
-        </is>
-      </c>
-      <c r="C72" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="K72" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00002000</t>
-        </is>
-      </c>
-      <c r="C73" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00002500</t>
-        </is>
-      </c>
-      <c r="C74" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00002500</t>
-        </is>
-      </c>
-      <c r="C75" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E75" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00005000</t>
-        </is>
-      </c>
-      <c r="C76" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E76" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G76" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H76" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I76" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K76" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00005000</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="33" t="inlineStr">
-        <is>
-          <t>OTLK270521C00007500</t>
-        </is>
-      </c>
-      <c r="C78" s="27" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E78" s="27" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="G78" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="H78" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="I78" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="K78" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="34" t="inlineStr">
-        <is>
-          <t>OTLK270521P00007500</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E79" s="30" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="30" t="inlineStr">
         <is>
           <t>✓ Full Match</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -261,12 +261,6 @@
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -278,6 +272,12 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 18/10/2026 09:02 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 19/10/2026 14:26 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>7176</v>
@@ -919,7 +919,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>2.8502</v>
+        <v>2.6622</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>101033</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>27439</v>
@@ -961,7 +961,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>2.2621</v>
+        <v>2.2616</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>929521</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>17277</v>
@@ -1003,7 +1003,7 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.996</v>
+        <v>1.9445</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>652540</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>534</v>
@@ -1045,7 +1045,7 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>2.6234</v>
+        <v>2.6123</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>30243</v>
@@ -1120,7 +1120,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (33 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (32 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         <v>-0.778</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>4.0938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1367,7 +1367,7 @@
         <v>-0.852</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1587,7 +1587,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (89 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (88 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
         <v>-0.827</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1993,7 +1993,7 @@
         <v>-0.931</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>7.1875</v>
+        <v>7.2188</v>
       </c>
     </row>
     <row r="24">
@@ -2160,7 +2160,7 @@
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (124 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (123 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>-0.575</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>1.6875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2407,7 +2407,7 @@
         <v>-0.681</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2460,12 +2460,12 @@
         <v>-0.74</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="C35" s="15" t="n">
         <v>0.224</v>
@@ -2627,7 +2627,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (215 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (214 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
         <v>-0.347</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3239,7 +3239,7 @@
         <v>1713337</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.4329</v>
+        <v>2.3701</v>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
@@ -5182,42 +5182,42 @@
           <t>OTLK261120C00000500</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="36" t="n">
         <v>1729</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="36" t="n">
+        <v>1727</v>
+      </c>
+      <c r="H6" s="36" t="n">
+        <v>1727</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>1727</v>
+      </c>
+      <c r="J6" s="36" t="n">
         <v>1729</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>1729</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>1729</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>1729</v>
-      </c>
-      <c r="K6" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K6" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00000500</t>
         </is>
@@ -5257,7 +5257,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00001000</t>
         </is>
@@ -5297,7 +5297,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00001000</t>
         </is>
@@ -5337,7 +5337,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00001500</t>
         </is>
@@ -5377,7 +5377,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00001500</t>
         </is>
@@ -5417,7 +5417,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00002000</t>
         </is>
@@ -5457,7 +5457,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00002000</t>
         </is>
@@ -5497,7 +5497,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00002500</t>
         </is>
@@ -5537,7 +5537,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00002500</t>
         </is>
@@ -5577,7 +5577,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00005000</t>
         </is>
@@ -5617,7 +5617,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00005000</t>
         </is>
@@ -5657,7 +5657,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>OTLK261120C00007500</t>
         </is>
@@ -5697,7 +5697,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>OTLK261120P00007500</t>
         </is>
@@ -5742,42 +5742,42 @@
           <t>OTLK270115C00000500</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="36" t="n">
         <v>10047</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="36" t="n">
+        <v>10050</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>10050</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>10050</v>
+      </c>
+      <c r="J20" s="36" t="n">
         <v>10047</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>10047</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>10047</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>10047</v>
-      </c>
-      <c r="K20" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K20" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00000500</t>
         </is>
@@ -5822,42 +5822,42 @@
           <t>OTLK270115C00001000</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="36" t="n">
         <v>6801</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="36" t="n">
+        <v>6802</v>
+      </c>
+      <c r="H22" s="36" t="n">
+        <v>6802</v>
+      </c>
+      <c r="I22" s="36" t="n">
+        <v>6802</v>
+      </c>
+      <c r="J22" s="36" t="n">
         <v>6801</v>
       </c>
-      <c r="H22" s="8" t="n">
-        <v>6801</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>6801</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>6801</v>
-      </c>
-      <c r="K22" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K22" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00001000</t>
         </is>
@@ -5897,7 +5897,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00001500</t>
         </is>
@@ -5937,7 +5937,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00001500</t>
         </is>
@@ -5977,7 +5977,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00002000</t>
         </is>
@@ -6017,7 +6017,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00002000</t>
         </is>
@@ -6057,7 +6057,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00002500</t>
         </is>
@@ -6097,7 +6097,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00002500</t>
         </is>
@@ -6137,7 +6137,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00005000</t>
         </is>
@@ -6177,47 +6177,47 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>OTLK270115P00005000</t>
         </is>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D31" s="37" t="n">
+      <c r="D31" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="36" t="inlineStr">
+      <c r="E31" s="34" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F31" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G31" s="38" t="n">
+      <c r="G31" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" s="36" t="inlineStr">
+      <c r="K31" s="34" t="inlineStr">
         <is>
           <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00007500</t>
         </is>
@@ -6257,7 +6257,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00007500</t>
         </is>
@@ -6297,7 +6297,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00010000</t>
         </is>
@@ -6322,7 +6322,7 @@
         <v>55</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>55</v>
@@ -6337,7 +6337,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00010000</t>
         </is>
@@ -6377,7 +6377,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>OTLK270115C00012500</t>
         </is>
@@ -6417,7 +6417,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>OTLK270115P00012500</t>
         </is>
@@ -6462,42 +6462,42 @@
           <t>OTLK270219C00000500</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="34" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="36" t="n">
         <v>2525</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="36" t="n">
+        <v>2505</v>
+      </c>
+      <c r="H38" s="36" t="n">
+        <v>2505</v>
+      </c>
+      <c r="I38" s="36" t="n">
+        <v>2505</v>
+      </c>
+      <c r="J38" s="36" t="n">
         <v>2525</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>2525</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>2525</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>2525</v>
-      </c>
-      <c r="K38" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K38" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00000500</t>
         </is>
@@ -6542,42 +6542,42 @@
           <t>OTLK270219C00001000</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="34" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="36" t="n">
         <v>6487</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="36" t="n">
+        <v>6499</v>
+      </c>
+      <c r="H40" s="36" t="n">
+        <v>6499</v>
+      </c>
+      <c r="I40" s="36" t="n">
+        <v>6499</v>
+      </c>
+      <c r="J40" s="36" t="n">
         <v>6487</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>6487</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>6487</v>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>6487</v>
-      </c>
-      <c r="K40" s="27" t="inlineStr">
-        <is>
-          <t>✓ Full Match</t>
+      <c r="K40" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Minor Discrepancy</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00001000</t>
         </is>
@@ -6617,7 +6617,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>OTLK270219C00001500</t>
         </is>
@@ -6657,7 +6657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00001500</t>
         </is>
@@ -6697,7 +6697,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="33" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>OTLK270219C00002000</t>
         </is>
@@ -6737,7 +6737,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00002000</t>
         </is>
@@ -6777,7 +6777,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="33" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>OTLK270219C00002500</t>
         </is>
@@ -6817,7 +6817,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00002500</t>
         </is>
@@ -6857,7 +6857,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="33" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>OTLK270219C00005000</t>
         </is>
@@ -6897,7 +6897,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="34" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00005000</t>
         </is>
@@ -6937,7 +6937,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="33" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>OTLK270219C00007500</t>
         </is>
@@ -6977,7 +6977,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="34" t="inlineStr">
+      <c r="B51" s="37" t="inlineStr">
         <is>
           <t>OTLK270219P00007500</t>
         </is>
@@ -7017,7 +7017,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="33" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00000500</t>
         </is>
@@ -7057,7 +7057,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00000500</t>
         </is>
@@ -7097,7 +7097,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="33" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00001000</t>
         </is>
@@ -7137,7 +7137,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="34" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00001000</t>
         </is>
@@ -7177,7 +7177,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="33" t="inlineStr">
+      <c r="B56" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00001500</t>
         </is>
@@ -7217,7 +7217,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="34" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00001500</t>
         </is>
@@ -7257,7 +7257,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="33" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00002000</t>
         </is>
@@ -7297,7 +7297,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="34" t="inlineStr">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00002000</t>
         </is>
@@ -7337,7 +7337,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="33" t="inlineStr">
+      <c r="B60" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00002500</t>
         </is>
@@ -7377,7 +7377,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="34" t="inlineStr">
+      <c r="B61" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00002500</t>
         </is>
@@ -7417,7 +7417,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="33" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00005000</t>
         </is>
@@ -7457,7 +7457,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="34" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00005000</t>
         </is>
@@ -7497,7 +7497,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="33" t="inlineStr">
+      <c r="B64" s="38" t="inlineStr">
         <is>
           <t>OTLK270521C00007500</t>
         </is>
@@ -7537,7 +7537,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="34" t="inlineStr">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>OTLK270521P00007500</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 19/10/2026 14:26 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 19/10/2026 14:46 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -69,7 +69,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -124,12 +124,6 @@
         <bgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -171,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,22 +255,10 @@
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -733,7 +715,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 19/10/2026 14:46 | Market session: 2026-10-16 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 20/10/2026 09:06 | Market session: 2026-10-19 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +735,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.4880</t>
+          <t>$0.4930</t>
         </is>
       </c>
     </row>
@@ -765,7 +747,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1,068 contracts</t>
+          <t>245 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +759,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.000 (call-skewed volume)</t>
+          <t>0.021 (call-skewed volume)</t>
         </is>
       </c>
     </row>
@@ -789,7 +771,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,426</t>
+          <t>52,420</t>
         </is>
       </c>
     </row>
@@ -801,7 +783,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,148</t>
+          <t>5,168</t>
         </is>
       </c>
     </row>
@@ -813,7 +795,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.099</t>
         </is>
       </c>
     </row>
@@ -895,10 +877,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7176</v>
+        <v>7174</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1579</v>
@@ -907,22 +889,22 @@
         <v>0.22</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>2.6622</v>
+        <v>2.5738</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>101033</v>
+        <v>116208</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -937,19 +919,19 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>27439</v>
+        <v>27443</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>3364</v>
+        <v>3384</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0.123</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H17" s="14" t="n">
         <v>0</v>
@@ -961,10 +943,10 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>2.2616</v>
+        <v>2.3527</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>929521</v>
+        <v>978373</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -979,10 +961,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>17277</v>
+        <v>17269</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>197</v>
@@ -991,7 +973,7 @@
         <v>0.011</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>0</v>
@@ -1003,10 +985,10 @@
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.9445</v>
+        <v>2.0705</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>652540</v>
+        <v>657187</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1021,7 +1003,7 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>534</v>
@@ -1033,7 +1015,7 @@
         <v>0.015</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1027,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>2.6123</v>
+        <v>1.5019</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>30243</v>
+        <v>31470</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1112,7 +1094,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.4880 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.4930 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1102,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (32 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (31 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1213,22 +1195,22 @@
     </row>
     <row r="7">
       <c r="B7" s="17" t="n">
-        <v>1.2619</v>
+        <v>1.1493</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.585</v>
+        <v>0.613</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>1.8848</v>
+        <v>1.8725</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>0.05</v>
@@ -1240,42 +1222,42 @@
         <v>0.5</v>
       </c>
       <c r="K7" s="23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="M7" s="23" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N7" s="24" t="n">
         <v>871</v>
       </c>
       <c r="O7" s="24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>1.9062</v>
+        <v>1.8909</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>-0.429</v>
+        <v>-0.4</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>7.4489</v>
+        <v>1.7978</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>1.9502</v>
+        <v>1.9586</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.239</v>
+        <v>0.251</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.9542</v>
+        <v>0.9559</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>1612</v>
@@ -1293,10 +1275,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>0.65</v>
+        <v>1.05</v>
       </c>
       <c r="M8" s="23" t="n">
         <v>0.45</v>
@@ -1308,24 +1290,24 @@
         <v>0</v>
       </c>
       <c r="P8" s="25" t="n">
-        <v>0.9771</v>
+        <v>0.9748</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>-0.778</v>
+        <v>-0.764</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>0</v>
+        <v>2.7342</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>2.591</v>
+        <v>2.6339</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.166</v>
+        <v>0.179</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.634</v>
+        <v>0.6399</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1346,10 +1328,10 @@
         <v>1.5</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>1</v>
@@ -1361,33 +1343,33 @@
         <v>0</v>
       </c>
       <c r="P9" s="25" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6601</v>
       </c>
       <c r="Q9" s="25" t="n">
-        <v>-0.852</v>
+        <v>-0.838</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>0</v>
+        <v>3.4947</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="n">
-        <v>4.9397</v>
+        <v>5.0385</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.134</v>
+        <v>0.147</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.492</v>
+        <v>0.5016</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>1358</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>0</v>
@@ -1414,24 +1396,24 @@
         <v>0</v>
       </c>
       <c r="P10" s="25" t="n">
-        <v>0.5194</v>
+        <v>0.524</v>
       </c>
       <c r="Q10" s="25" t="n">
-        <v>-0.886</v>
+        <v>-0.871</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>0</v>
+        <v>2.6555</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="n">
-        <v>3.9134</v>
+        <v>3.3828</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.115</v>
+        <v>0.128</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.4111</v>
+        <v>0.4231</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1446,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M11" s="23" t="n">
         <v>1.87</v>
@@ -1467,24 +1449,24 @@
         <v>0</v>
       </c>
       <c r="P11" s="25" t="n">
-        <v>0.4404</v>
+        <v>0.4496</v>
       </c>
       <c r="Q11" s="25" t="n">
-        <v>-0.906</v>
+        <v>-0.891</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>0</v>
+        <v>3.7947</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="n">
-        <v>4.8187</v>
+        <v>4.956</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.076</v>
+        <v>0.089</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.2524</v>
+        <v>0.2687</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1520,24 +1502,24 @@
         <v>0</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>0.2739</v>
+        <v>0.3054</v>
       </c>
       <c r="Q12" s="25" t="n">
-        <v>-0.951</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>1.2</v>
+        <v>3.9553</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="n">
-        <v>4.6255</v>
+        <v>4.7689</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.062</v>
+        <v>0.075</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.1966</v>
+        <v>0.214</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1561,7 +1543,7 @@
         <v>6.3</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="M13" s="23" t="n">
         <v>7.3</v>
@@ -1573,13 +1555,13 @@
         <v>0</v>
       </c>
       <c r="P13" s="25" t="n">
-        <v>0.2004</v>
+        <v>0.2807</v>
       </c>
       <c r="Q13" s="25" t="n">
-        <v>-0.969</v>
+        <v>-0.958</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>1.2</v>
+        <v>4.5272</v>
       </c>
     </row>
     <row r="14"/>
@@ -1587,7 +1569,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (88 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (87 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1680,25 +1662,25 @@
     </row>
     <row r="18">
       <c r="B18" s="17" t="n">
-        <v>1.7823</v>
+        <v>2.2427</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.65</v>
+        <v>0.674</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>1.2593</v>
+        <v>1.1454</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>10047</v>
+        <v>10050</v>
       </c>
       <c r="G18" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I18" s="16" t="n">
         <v>0.3</v>
@@ -1710,7 +1692,7 @@
         <v>0.05</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="M18" s="23" t="n">
         <v>0.15</v>
@@ -1722,39 +1704,39 @@
         <v>0</v>
       </c>
       <c r="P18" s="25" t="n">
-        <v>1.2882</v>
+        <v>1.1684</v>
       </c>
       <c r="Q18" s="25" t="n">
-        <v>-0.382</v>
+        <v>-0.356</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>1.3062</v>
+        <v>1.1318</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>1.771</v>
+        <v>1.4608</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.354</v>
+        <v>0.373</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.9293</v>
+        <v>0.9079</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>6801</v>
+        <v>6802</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>1</v>
@@ -1763,7 +1745,7 @@
         <v>0.2</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="M19" s="23" t="n">
         <v>0.48</v>
@@ -1775,24 +1757,24 @@
         <v>0</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9454</v>
       </c>
       <c r="Q19" s="25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.664</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>2.6253</v>
+        <v>2.0002</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>1.5804</v>
+        <v>1.9016</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.264</v>
+        <v>0.276</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.704</v>
+        <v>0.6954</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>0</v>
@@ -1807,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J20" s="22" t="n">
         <v>1.5</v>
@@ -1816,7 +1798,7 @@
         <v>0.7</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="M20" s="23" t="n">
         <v>0.97</v>
@@ -1828,27 +1810,27 @@
         <v>0</v>
       </c>
       <c r="P20" s="25" t="n">
-        <v>0.759</v>
+        <v>0.7438</v>
       </c>
       <c r="Q20" s="25" t="n">
-        <v>-0.779</v>
+        <v>-0.766</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>2.8552</v>
+        <v>1.923</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>4.3083</v>
+        <v>4.2506</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.221</v>
+        <v>0.229</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.5833</v>
+        <v>0.5767</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21" s="14" t="n">
         <v>2820</v>
@@ -1866,7 +1848,7 @@
         <v>2</v>
       </c>
       <c r="K21" s="23" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="L21" s="23" t="n">
         <v>2</v>
@@ -1881,39 +1863,39 @@
         <v>0</v>
       </c>
       <c r="P21" s="25" t="n">
-        <v>0.6493</v>
+        <v>0.6339</v>
       </c>
       <c r="Q21" s="25" t="n">
-        <v>-0.827</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>2.8135</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>2.3982</v>
+        <v>2.9548</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.5082</v>
+        <v>0.5017</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>3053</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" s="22" t="n">
         <v>2.5</v>
@@ -1934,39 +1916,39 @@
         <v>0</v>
       </c>
       <c r="P22" s="25" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5689</v>
       </c>
       <c r="Q22" s="25" t="n">
-        <v>-0.858</v>
+        <v>-0.85</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>0</v>
+        <v>2.0198</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="17" t="n">
-        <v>4.3304</v>
+        <v>3.8157</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>0.14</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.3466</v>
+        <v>0.3383</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="14" t="n">
         <v>1986</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="J23" s="22" t="n">
         <v>5</v>
@@ -1981,30 +1963,30 @@
         <v>3.8</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.4279</v>
+        <v>0.4487</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>-0.931</v>
+        <v>-0.93</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>7.2188</v>
+        <v>2.6914</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="17" t="n">
-        <v>4.6468</v>
+        <v>4.6364</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.285</v>
+        <v>0.2756</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>0</v>
@@ -2025,10 +2007,10 @@
         <v>7.5</v>
       </c>
       <c r="K24" s="23" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M24" s="23" t="n">
         <v>6.2</v>
@@ -2040,27 +2022,27 @@
         <v>0</v>
       </c>
       <c r="P24" s="25" t="n">
-        <v>0.3004</v>
+        <v>0.3869</v>
       </c>
       <c r="Q24" s="25" t="n">
-        <v>-0.962</v>
+        <v>-0.969</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>4.2573</v>
+        <v>3.0937</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="17" t="n">
-        <v>3.0413</v>
+        <v>3.0505</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>0.2507</v>
+        <v>0.2406</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14" t="n">
         <v>55</v>
@@ -2078,10 +2060,10 @@
         <v>10</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M25" s="23" t="n">
         <v>10</v>
@@ -2093,24 +2075,24 @@
         <v>0</v>
       </c>
       <c r="P25" s="25" t="n">
-        <v>0.2043</v>
+        <v>0.1476</v>
       </c>
       <c r="Q25" s="25" t="n">
-        <v>-0.978</v>
+        <v>-0.989</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>4.5533</v>
+        <v>3.391</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="17" t="n">
-        <v>3.1878</v>
+        <v>3.1997</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>0.2282</v>
+        <v>0.2177</v>
       </c>
       <c r="E26" s="14" t="n">
         <v>0</v>
@@ -2131,10 +2113,10 @@
         <v>12.5</v>
       </c>
       <c r="K26" s="23" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="M26" s="23" t="n">
         <v>10.94</v>
@@ -2146,13 +2128,13 @@
         <v>0</v>
       </c>
       <c r="P26" s="25" t="n">
-        <v>0.1319</v>
+        <v>0.0272</v>
       </c>
       <c r="Q26" s="25" t="n">
-        <v>-0.987</v>
+        <v>-0.998</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>4.7896</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="27"/>
@@ -2160,7 +2142,7 @@
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (123 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (122 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2253,19 +2235,19 @@
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>2.7557</v>
+        <v>2.333</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.663</v>
+        <v>0.675</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.7687</v>
+        <v>0.737</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>2525</v>
+        <v>2505</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>0.16</v>
@@ -2274,7 +2256,7 @@
         <v>0.15</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="J31" s="22" t="n">
         <v>0.5</v>
@@ -2283,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M31" s="23" t="n">
         <v>0.11</v>
@@ -2295,30 +2277,30 @@
         <v>0</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>0.7622</v>
+        <v>0.7299</v>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>-0.321</v>
+        <v>-0.309</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>0</v>
+        <v>4.0462</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>1.5881</v>
+        <v>1.7659</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.41</v>
+        <v>0.415</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.7763</v>
+        <v>0.7658</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>6487</v>
+        <v>6499</v>
       </c>
       <c r="G32" s="16" t="n">
         <v>0.1</v>
@@ -2327,13 +2309,13 @@
         <v>0.05</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L32" s="23" t="n">
         <v>0.6</v>
@@ -2348,10 +2330,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>0.798</v>
+        <v>0.785</v>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>-0.575</v>
+        <v>-0.57</v>
       </c>
       <c r="R32" s="26" t="n">
         <v>0</v>
@@ -2359,16 +2341,16 @@
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>1.705</v>
+        <v>1.923</v>
       </c>
       <c r="C33" s="15" t="n">
         <v>0.31</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.6496</v>
+        <v>0.6399</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
         <v>5582</v>
@@ -2377,7 +2359,7 @@
         <v>0.1</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I33" s="16" t="n">
         <v>0.1</v>
@@ -2386,10 +2368,10 @@
         <v>1.5</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M33" s="23" t="n">
         <v>1.02</v>
@@ -2401,24 +2383,24 @@
         <v>0</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>0.6932</v>
+        <v>0.6792</v>
       </c>
       <c r="Q33" s="25" t="n">
         <v>-0.681</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>0</v>
+        <v>2.0368</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>3.1126</v>
+        <v>3.0587</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.257</v>
+        <v>0.255</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.5602</v>
+        <v>0.5493</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
@@ -2439,10 +2421,10 @@
         <v>2</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M34" s="23" t="n">
         <v>1.35</v>
@@ -2454,27 +2436,27 @@
         <v>0</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>0.6229</v>
+        <v>0.6066</v>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>-0.74</v>
+        <v>-0.741</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>0.5</v>
+        <v>1.7538</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.4975</v>
+        <v>0.4858</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F35" s="14" t="n">
         <v>848</v>
@@ -2486,16 +2468,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J35" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M35" s="23" t="n">
         <v>0</v>
@@ -2507,24 +2489,24 @@
         <v>0</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>0.5782</v>
+        <v>0.5606</v>
       </c>
       <c r="Q35" s="25" t="n">
-        <v>-0.779</v>
+        <v>-0.781</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>1.2</v>
+        <v>1.5756</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>4.486</v>
+        <v>4.422</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.152</v>
+        <v>0.147</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.3444</v>
+        <v>0.3314</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>0</v>
@@ -2545,10 +2527,10 @@
         <v>5</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>5.1</v>
+        <v>6.3</v>
       </c>
       <c r="M36" s="23" t="n">
         <v>0</v>
@@ -2560,24 +2542,24 @@
         <v>0</v>
       </c>
       <c r="P36" s="25" t="n">
-        <v>0.5059</v>
+        <v>0.4862</v>
       </c>
       <c r="Q36" s="25" t="n">
-        <v>-0.884</v>
+        <v>-0.887</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>1.2</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>6.2495</v>
+        <v>0.5</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.122</v>
+        <v>0.117</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.2792</v>
+        <v>0.2663</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2592,13 +2574,13 @@
         <v>0</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>0.75</v>
+        <v>2.6</v>
       </c>
       <c r="J37" s="22" t="n">
         <v>7.5</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="L37" s="23" t="n">
         <v>8.800000000000001</v>
@@ -2613,13 +2595,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="25" t="n">
-        <v>0.4198</v>
+        <v>0.4846</v>
       </c>
       <c r="Q37" s="25" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.947</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>1.2</v>
+        <v>2.5794</v>
       </c>
     </row>
     <row r="38"/>
@@ -2627,7 +2609,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (214 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (213 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2720,13 +2702,13 @@
     </row>
     <row r="42">
       <c r="B42" s="17" t="n">
-        <v>2.2556</v>
+        <v>1.5146</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.724</v>
+        <v>0.747</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.9837</v>
+        <v>0.8625</v>
       </c>
       <c r="E42" s="14" t="n">
         <v>0</v>
@@ -2738,10 +2720,10 @@
         <v>0.35</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="J42" s="22" t="n">
         <v>0.5</v>
@@ -2762,10 +2744,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="25" t="n">
-        <v>1.0375</v>
+        <v>0.9048</v>
       </c>
       <c r="Q42" s="25" t="n">
-        <v>-0.347</v>
+        <v>-0.322</v>
       </c>
       <c r="R42" s="26" t="n">
         <v>0</v>
@@ -2773,37 +2755,37 @@
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>2.2314</v>
+        <v>1.3668</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.429</v>
+        <v>0.457</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.9261</v>
+        <v>0.8835</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F43" s="14" t="n">
         <v>76</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="J43" s="22" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M43" s="23" t="n">
         <v>0.59</v>
@@ -2815,24 +2797,24 @@
         <v>0</v>
       </c>
       <c r="P43" s="25" t="n">
-        <v>1.0422</v>
+        <v>0.9818</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>-0.664</v>
+        <v>-0.632</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>1.4688</v>
+        <v>1.7002</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.386</v>
+        <v>1.3532</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.341</v>
+        <v>0.365</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.738</v>
+        <v>0.7181</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0</v>
@@ -2844,10 +2826,10 @@
         <v>0.16</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J44" s="22" t="n">
         <v>1.5</v>
@@ -2868,48 +2850,48 @@
         <v>0</v>
       </c>
       <c r="P44" s="25" t="n">
-        <v>0.8758</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>-0.763</v>
+        <v>-0.736</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>1.451</v>
+        <v>1.5547</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>6.1343</v>
+        <v>1.357</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.298</v>
+        <v>0.319</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.6334</v>
+        <v>0.6213</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F45" s="14" t="n">
         <v>64</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J45" s="22" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M45" s="23" t="n">
         <v>0</v>
@@ -2921,24 +2903,24 @@
         <v>0</v>
       </c>
       <c r="P45" s="25" t="n">
-        <v>0.7991</v>
+        <v>0.764</v>
       </c>
       <c r="Q45" s="25" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.791</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>1.6688</v>
+        <v>1.3306</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>3.8404</v>
+        <v>1.6763</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.271</v>
+        <v>0.29</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.5667</v>
+        <v>0.5585</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -2953,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="J46" s="22" t="n">
         <v>2.5</v>
@@ -2974,24 +2956,24 @@
         <v>0</v>
       </c>
       <c r="P46" s="25" t="n">
-        <v>0.7459</v>
+        <v>0.7148</v>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>-0.855</v>
+        <v>-0.83</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>4.1539</v>
+        <v>4.2195</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.2004</v>
+        <v>1.6085</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.208</v>
+        <v>0.223</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.4146</v>
+        <v>0.4127</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3006,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
       <c r="J47" s="22" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="L47" s="23" t="n">
         <v>7</v>
@@ -3027,24 +3009,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="25" t="n">
-        <v>0.4601</v>
+        <v>0.625</v>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>-0.955</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>1.2</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>2.0764</v>
+        <v>2.058</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.179</v>
+        <v>0.193</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.351</v>
+        <v>0.3509</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3065,7 +3047,7 @@
         <v>7.5</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="L48" s="23" t="n">
         <v>9.5</v>
@@ -3080,13 +3062,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="25" t="n">
-        <v>0.1748</v>
+        <v>0.1586</v>
       </c>
       <c r="Q48" s="25" t="n">
         <v>-0.987</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>1.2</v>
+        <v>2.7949</v>
       </c>
     </row>
   </sheetData>
@@ -3100,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3205,41 +3187,41 @@
     <row r="6">
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>0.488</v>
+        <v>0.493</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1068</v>
+        <v>245</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1068</v>
+        <v>240</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52426</v>
+        <v>52420</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5148</v>
+        <v>5168</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K6" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1713337</v>
+        <v>1783238</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.3701</v>
+        <v>2.1247</v>
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
@@ -3250,17 +3232,17 @@
     <row r="7">
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>0</v>
@@ -3269,10 +3251,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52809</v>
+        <v>52426</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5156</v>
+        <v>5148</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -3281,10 +3263,10 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1758474</v>
+        <v>1713337</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>2.3822</v>
+        <v>2.3701</v>
       </c>
       <c r="N7" s="30" t="inlineStr">
         <is>
@@ -3295,29 +3277,29 @@
     <row r="8">
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.098</v>
@@ -3326,10 +3308,10 @@
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N8" s="27" t="inlineStr">
         <is>
@@ -3340,29 +3322,29 @@
     <row r="9">
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.098</v>
@@ -3371,10 +3353,10 @@
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N9" s="30" t="inlineStr">
         <is>
@@ -3385,29 +3367,29 @@
     <row r="10">
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.098</v>
@@ -3416,10 +3398,10 @@
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N10" s="27" t="inlineStr">
         <is>
@@ -3430,29 +3412,29 @@
     <row r="11">
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C11" s="31" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.098</v>
@@ -3461,10 +3443,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N11" s="30" t="inlineStr">
         <is>
@@ -3475,26 +3457,26 @@
     <row r="12">
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>5157</v>
@@ -3506,10 +3488,10 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N12" s="27" t="inlineStr">
         <is>
@@ -3520,41 +3502,41 @@
     <row r="13">
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C13" s="31" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>5157</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N13" s="30" t="inlineStr">
         <is>
@@ -3565,29 +3547,29 @@
     <row r="14">
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.099</v>
@@ -3596,10 +3578,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N14" s="27" t="inlineStr">
         <is>
@@ -3610,29 +3592,29 @@
     <row r="15">
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C15" s="31" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0.099</v>
@@ -3641,10 +3623,10 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N15" s="30" t="inlineStr">
         <is>
@@ -3655,26 +3637,26 @@
     <row r="16">
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>5161</v>
@@ -3686,10 +3668,10 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N16" s="27" t="inlineStr">
         <is>
@@ -3700,17 +3682,17 @@
     <row r="17">
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C17" s="31" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>0</v>
@@ -3719,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I17" s="14" t="n">
         <v>5161</v>
@@ -3731,10 +3713,10 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
@@ -3745,29 +3727,29 @@
     <row r="18">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.099</v>
@@ -3776,10 +3758,10 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N18" s="27" t="inlineStr">
         <is>
@@ -3790,41 +3772,41 @@
     <row r="19">
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C19" s="31" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>5159</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K19" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N19" s="30" t="inlineStr">
         <is>
@@ -3835,29 +3817,29 @@
     <row r="20">
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C20" s="28" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>0.098</v>
@@ -3866,10 +3848,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N20" s="27" t="inlineStr">
         <is>
@@ -3880,29 +3862,29 @@
     <row r="21">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>0.098</v>
@@ -3911,10 +3893,10 @@
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N21" s="30" t="inlineStr">
         <is>
@@ -3925,26 +3907,26 @@
     <row r="22">
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C22" s="28" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>5156</v>
@@ -3956,10 +3938,10 @@
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
@@ -3970,41 +3952,41 @@
     <row r="23">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C23" s="31" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K23" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N23" s="30" t="inlineStr">
         <is>
@@ -4015,41 +3997,41 @@
     <row r="24">
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C24" s="28" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N24" s="27" t="inlineStr">
         <is>
@@ -4060,41 +4042,41 @@
     <row r="25">
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C25" s="31" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K25" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
@@ -4105,29 +4087,29 @@
     <row r="26">
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J26" s="9" t="n">
         <v>0.093</v>
@@ -4136,10 +4118,10 @@
         <v>0.5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N26" s="27" t="inlineStr">
         <is>
@@ -4150,73 +4132,77 @@
     <row r="27">
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C27" s="31" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K27" s="16" t="n"/>
+        <v>0.093</v>
+      </c>
+      <c r="K27" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L27" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="17" t="n"/>
+        <v>2361798</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N27" s="30" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C28" s="28" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="12" t="n">
@@ -4232,32 +4218,32 @@
     <row r="29">
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C29" s="31" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K29" s="16" t="n"/>
       <c r="L29" s="18" t="n">
@@ -4273,31 +4259,33 @@
     <row r="30">
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C30" s="28" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9" t="n"/>
+        <v>7194</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K30" s="10" t="n"/>
       <c r="L30" s="12" t="n">
         <v>0</v>
@@ -4312,23 +4300,23 @@
     <row r="31">
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C31" s="31" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H31" s="14" t="n">
         <v>0</v>
@@ -4351,33 +4339,31 @@
     <row r="32">
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C32" s="28" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -4392,31 +4378,33 @@
     <row r="33">
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C33" s="31" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="15" t="n"/>
+        <v>6136</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K33" s="16" t="n"/>
       <c r="L33" s="18" t="n">
         <v>0</v>
@@ -4431,23 +4419,23 @@
     <row r="34">
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C34" s="28" t="n">
         <v>1.69</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
@@ -4470,33 +4458,31 @@
     <row r="35">
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C35" s="31" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J35" s="15" t="n"/>
       <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
@@ -4511,31 +4497,33 @@
     <row r="36">
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C36" s="28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9" t="n"/>
+        <v>5834</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
@@ -4550,33 +4538,31 @@
     <row r="37">
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C37" s="31" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J37" s="15" t="n"/>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
@@ -4591,31 +4577,33 @@
     <row r="38">
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C38" s="28" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="n"/>
+        <v>4272</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
@@ -4630,11 +4618,11 @@
     <row r="39">
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C39" s="31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>2568</v>
@@ -4649,14 +4637,12 @@
         <v>0.27</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J39" s="15" t="n"/>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -4671,11 +4657,11 @@
     <row r="40">
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C40" s="28" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>2568</v>
@@ -4690,12 +4676,14 @@
         <v>0.27</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="n"/>
+        <v>4145</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -4710,11 +4698,11 @@
     <row r="41">
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C41" s="31" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>2568</v>
@@ -4729,14 +4717,12 @@
         <v>0.27</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J41" s="15" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J41" s="15" t="n"/>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
@@ -4751,29 +4737,33 @@
     <row r="42">
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C42" s="28" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="9" t="n"/>
+        <v>546</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9" t="n"/>
+        <v>4059</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="12" t="n">
         <v>0</v>
@@ -4788,11 +4778,11 @@
     <row r="43">
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C43" s="31" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
@@ -4825,11 +4815,11 @@
     <row r="44">
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C44" s="28" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>0</v>
@@ -4862,11 +4852,11 @@
     <row r="45">
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C45" s="31" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
@@ -4899,11 +4889,11 @@
     <row r="46">
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C46" s="28" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>0</v>
@@ -4936,11 +4926,11 @@
     <row r="47">
       <c r="B47" s="30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C47" s="31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
@@ -4973,7 +4963,7 @@
     <row r="48">
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C48" s="28" t="n">
@@ -5010,7 +5000,7 @@
     <row r="49">
       <c r="B49" s="30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C49" s="31" t="n">
@@ -5047,7 +5037,7 @@
     <row r="50">
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C50" s="28" t="n">
@@ -5076,6 +5066,43 @@
       </c>
       <c r="M50" s="11" t="n"/>
       <c r="N50" s="27" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="16" t="n"/>
+      <c r="L51" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="17" t="n"/>
+      <c r="N51" s="30" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5182,42 +5209,42 @@
           <t>OTLK261120C00000500</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n">
-        <v>1729</v>
-      </c>
-      <c r="G6" s="36" t="n">
+      <c r="F6" s="8" t="n">
         <v>1727</v>
       </c>
-      <c r="H6" s="36" t="n">
+      <c r="G6" s="8" t="n">
         <v>1727</v>
       </c>
-      <c r="I6" s="36" t="n">
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
         <v>1727</v>
       </c>
-      <c r="J6" s="36" t="n">
-        <v>1729</v>
-      </c>
-      <c r="K6" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J6" s="8" t="n">
+        <v>1727</v>
+      </c>
+      <c r="K6" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00000500</t>
         </is>
@@ -5242,7 +5269,7 @@
         <v>871</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>871</v>
@@ -5257,7 +5284,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00001000</t>
         </is>
@@ -5282,7 +5309,7 @@
         <v>1612</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1612</v>
+        <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>1612</v>
@@ -5297,7 +5324,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00001000</t>
         </is>
@@ -5322,7 +5349,7 @@
         <v>358</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>358</v>
@@ -5337,7 +5364,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00001500</t>
         </is>
@@ -5362,7 +5389,7 @@
         <v>2128</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2128</v>
+        <v>0</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>2128</v>
@@ -5377,7 +5404,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00001500</t>
         </is>
@@ -5402,7 +5429,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>150</v>
@@ -5417,7 +5444,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00002000</t>
         </is>
@@ -5442,7 +5469,7 @@
         <v>1358</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1358</v>
+        <v>0</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>1358</v>
@@ -5457,7 +5484,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00002000</t>
         </is>
@@ -5497,7 +5524,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00002500</t>
         </is>
@@ -5537,7 +5564,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00002500</t>
         </is>
@@ -5577,7 +5604,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00005000</t>
         </is>
@@ -5617,7 +5644,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00005000</t>
         </is>
@@ -5657,7 +5684,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>OTLK261120C00007500</t>
         </is>
@@ -5697,7 +5724,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>OTLK261120P00007500</t>
         </is>
@@ -5742,42 +5769,42 @@
           <t>OTLK270115C00000500</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F20" s="36" t="n">
-        <v>10047</v>
-      </c>
-      <c r="G20" s="36" t="n">
+      <c r="F20" s="8" t="n">
         <v>10050</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="G20" s="8" t="n">
         <v>10050</v>
       </c>
-      <c r="I20" s="36" t="n">
+      <c r="H20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>10050</v>
       </c>
-      <c r="J20" s="36" t="n">
-        <v>10047</v>
-      </c>
-      <c r="K20" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J20" s="8" t="n">
+        <v>10050</v>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00000500</t>
         </is>
@@ -5802,7 +5829,7 @@
         <v>2093</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>2093</v>
+        <v>0</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>2093</v>
@@ -5822,42 +5849,42 @@
           <t>OTLK270115C00001000</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>6801</v>
-      </c>
-      <c r="G22" s="36" t="n">
+      <c r="F22" s="8" t="n">
         <v>6802</v>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="G22" s="8" t="n">
         <v>6802</v>
       </c>
-      <c r="I22" s="36" t="n">
+      <c r="H22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8" t="n">
         <v>6802</v>
       </c>
-      <c r="J22" s="36" t="n">
-        <v>6801</v>
-      </c>
-      <c r="K22" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J22" s="8" t="n">
+        <v>6802</v>
+      </c>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00001000</t>
         </is>
@@ -5882,7 +5909,7 @@
         <v>641</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>641</v>
@@ -5897,7 +5924,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00001500</t>
         </is>
@@ -5922,7 +5949,7 @@
         <v>1986</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>1986</v>
@@ -5937,7 +5964,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00001500</t>
         </is>
@@ -5962,7 +5989,7 @@
         <v>455</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>455</v>
@@ -5977,7 +6004,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00002000</t>
         </is>
@@ -6002,7 +6029,7 @@
         <v>2820</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>2820</v>
+        <v>0</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>2820</v>
@@ -6017,7 +6044,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00002000</t>
         </is>
@@ -6042,7 +6069,7 @@
         <v>12</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14" t="n">
         <v>12</v>
@@ -6057,7 +6084,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00002500</t>
         </is>
@@ -6082,7 +6109,7 @@
         <v>3053</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>3053</v>
+        <v>0</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>3053</v>
@@ -6097,7 +6124,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00002500</t>
         </is>
@@ -6137,7 +6164,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00005000</t>
         </is>
@@ -6162,7 +6189,7 @@
         <v>1986</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1986</v>
+        <v>0</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>1986</v>
@@ -6177,47 +6204,47 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00005000</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F31" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="36" t="n">
+      <c r="F31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="I31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="I31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" s="30" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00007500</t>
         </is>
@@ -6242,7 +6269,7 @@
         <v>252</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>252</v>
@@ -6257,7 +6284,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00007500</t>
         </is>
@@ -6297,7 +6324,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00010000</t>
         </is>
@@ -6322,7 +6349,7 @@
         <v>55</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>55</v>
@@ -6337,7 +6364,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00010000</t>
         </is>
@@ -6377,7 +6404,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="38" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>OTLK270115C00012500</t>
         </is>
@@ -6417,7 +6444,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>OTLK270115P00012500</t>
         </is>
@@ -6462,42 +6489,42 @@
           <t>OTLK270219C00000500</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F38" s="36" t="n">
-        <v>2525</v>
-      </c>
-      <c r="G38" s="36" t="n">
+      <c r="F38" s="8" t="n">
         <v>2505</v>
       </c>
-      <c r="H38" s="36" t="n">
+      <c r="G38" s="8" t="n">
         <v>2505</v>
       </c>
-      <c r="I38" s="36" t="n">
+      <c r="H38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="8" t="n">
         <v>2505</v>
       </c>
-      <c r="J38" s="36" t="n">
-        <v>2525</v>
-      </c>
-      <c r="K38" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J38" s="8" t="n">
+        <v>2505</v>
+      </c>
+      <c r="K38" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00000500</t>
         </is>
@@ -6542,42 +6569,42 @@
           <t>OTLK270219C00001000</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
       </c>
-      <c r="D40" s="35" t="n">
+      <c r="D40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="34" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="F40" s="36" t="n">
-        <v>6487</v>
-      </c>
-      <c r="G40" s="36" t="n">
+      <c r="F40" s="8" t="n">
         <v>6499</v>
       </c>
-      <c r="H40" s="36" t="n">
+      <c r="G40" s="8" t="n">
         <v>6499</v>
       </c>
-      <c r="I40" s="36" t="n">
+      <c r="H40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="8" t="n">
         <v>6499</v>
       </c>
-      <c r="J40" s="36" t="n">
-        <v>6487</v>
-      </c>
-      <c r="K40" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ Minor Discrepancy</t>
+      <c r="J40" s="8" t="n">
+        <v>6499</v>
+      </c>
+      <c r="K40" s="27" t="inlineStr">
+        <is>
+          <t>✓ Full Match</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00001000</t>
         </is>
@@ -6602,7 +6629,7 @@
         <v>151</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>151</v>
@@ -6617,7 +6644,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00001500</t>
         </is>
@@ -6642,7 +6669,7 @@
         <v>5582</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>5582</v>
+        <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>5582</v>
@@ -6657,7 +6684,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00001500</t>
         </is>
@@ -6682,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
         <v>1</v>
@@ -6697,7 +6724,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="38" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00002000</t>
         </is>
@@ -6722,7 +6749,7 @@
         <v>1071</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1071</v>
+        <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>1071</v>
@@ -6737,7 +6764,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00002000</t>
         </is>
@@ -6762,7 +6789,7 @@
         <v>41</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>41</v>
@@ -6777,7 +6804,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="38" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00002500</t>
         </is>
@@ -6802,7 +6829,7 @@
         <v>848</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>848</v>
@@ -6817,7 +6844,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00002500</t>
         </is>
@@ -6857,7 +6884,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="38" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00005000</t>
         </is>
@@ -6897,7 +6924,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00005000</t>
         </is>
@@ -6937,7 +6964,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="38" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>OTLK270219C00007500</t>
         </is>
@@ -6977,7 +7004,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B51" s="34" t="inlineStr">
         <is>
           <t>OTLK270219P00007500</t>
         </is>
@@ -7017,7 +7044,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="38" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00000500</t>
         </is>
@@ -7042,7 +7069,7 @@
         <v>336</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
         <v>0</v>
@@ -7057,7 +7084,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00000500</t>
         </is>
@@ -7082,7 +7109,7 @@
         <v>5</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>0</v>
@@ -7097,7 +7124,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="38" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00001000</t>
         </is>
@@ -7122,7 +7149,7 @@
         <v>76</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
@@ -7137,7 +7164,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="37" t="inlineStr">
+      <c r="B55" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00001000</t>
         </is>
@@ -7162,7 +7189,7 @@
         <v>3</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0</v>
@@ -7177,7 +7204,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="38" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00001500</t>
         </is>
@@ -7202,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
@@ -7217,7 +7244,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B57" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00001500</t>
         </is>
@@ -7257,7 +7284,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="38" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00002000</t>
         </is>
@@ -7282,7 +7309,7 @@
         <v>64</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>0</v>
@@ -7297,7 +7324,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="37" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00002000</t>
         </is>
@@ -7337,7 +7364,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="38" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00002500</t>
         </is>
@@ -7362,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>0</v>
@@ -7377,7 +7404,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00002500</t>
         </is>
@@ -7417,7 +7444,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="38" t="inlineStr">
+      <c r="B62" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00005000</t>
         </is>
@@ -7442,7 +7469,7 @@
         <v>20</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
         <v>0</v>
@@ -7457,7 +7484,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="37" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00005000</t>
         </is>
@@ -7497,7 +7524,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="38" t="inlineStr">
+      <c r="B64" s="33" t="inlineStr">
         <is>
           <t>OTLK270521C00007500</t>
         </is>
@@ -7522,7 +7549,7 @@
         <v>36</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
@@ -7537,7 +7564,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="37" t="inlineStr">
+      <c r="B65" s="34" t="inlineStr">
         <is>
           <t>OTLK270521P00007500</t>
         </is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -715,7 +715,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 20/10/2026 09:06 | Market session: 2026-10-19 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 20/10/2026 09:16 | Market session: 2026-10-19 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 21/10/2026 09:09 | Market session: 2026-10-20 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 22/10/2026 10:05 | Market session: 2026-10-21 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.5200</t>
+          <t>$0.5610</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>351 contracts</t>
+          <t>479 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.003 (call-skewed volume)</t>
+          <t>0.015 (call-skewed volume)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,615</t>
+          <t>52,837</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,172</t>
+          <t>5,173</t>
         </is>
       </c>
     </row>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7205</v>
+        <v>7180</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.22</v>
+        <v>0.221</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>2.2298</v>
+        <v>2.4653</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>139731</v>
+        <v>155951</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>1.7887</v>
+        <v>5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27459</v>
+        <v>27650</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3384</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>233</v>
+        <v>364</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>2.1826</v>
+        <v>2.0101</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1011416</v>
+        <v>1089902</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17259</v>
+        <v>17265</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>197</v>
@@ -1033,7 +1033,7 @@
         <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>1.9347</v>
+        <v>1.8307</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>657497</v>
+        <v>672809</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1063,34 +1063,34 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>692</v>
+        <v>732</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>8</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>1.5628</v>
+        <v>1.4495</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>39384</v>
+        <v>45167</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.5200 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.5610 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (30 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (29 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
     </row>
     <row r="7">
       <c r="B7" s="22" t="n">
-        <v>1.7868</v>
+        <v>0.3149</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0.653</v>
+        <v>0.716</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>1.7575</v>
+        <v>1.5708</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>1749</v>
+        <v>1724</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J7" s="26" t="n">
         <v>0.5</v>
@@ -1285,39 +1285,39 @@
         <v>0</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>1.7732</v>
+        <v>1.5836</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>-0.359</v>
+        <v>-0.295</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1.1047</v>
+        <v>3.1122</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>1.8839</v>
+        <v>1.7464</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.272</v>
+        <v>0.282</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.9552</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>1621</v>
@@ -1335,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="M8" s="27" t="n">
         <v>0.45</v>
@@ -1350,24 +1350,24 @@
         <v>0</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.9718</v>
+        <v>0.9823</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-0.743</v>
+        <v>-0.732</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>0</v>
+        <v>2.6395</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>2.5771</v>
+        <v>2.4633</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>0.197</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.6453</v>
+        <v>0.6351</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1403,24 +1403,24 @@
         <v>0</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>0.6622</v>
+        <v>0.6515</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-0.819</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>2.8581</v>
+        <v>3.4589</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="n">
-        <v>3.6137</v>
+        <v>4.7811</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.164</v>
+        <v>0.161</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.5104</v>
+        <v>0.494</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
@@ -1435,13 +1435,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K10" s="27" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>2</v>
@@ -1456,24 +1456,24 @@
         <v>0</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>0.5285</v>
+        <v>0.5108</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-0.853</v>
+        <v>-0.855</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>6.406</v>
+        <v>3.9798</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="n">
-        <v>3.3429</v>
+        <v>3.8446</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.4339</v>
+        <v>0.4152</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1488,16 +1488,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J11" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="L11" s="27" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M11" s="27" t="n">
         <v>1.87</v>
@@ -1509,24 +1509,24 @@
         <v>0</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>0.4551</v>
+        <v>0.4329</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-0.873</v>
+        <v>-0.876</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>0</v>
+        <v>7.9774</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="n">
-        <v>4.9272</v>
+        <v>4.8389</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.105</v>
+        <v>0.099</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.2831</v>
+        <v>0.2631</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1562,24 +1562,24 @@
         <v>0</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>0.3197</v>
+        <v>0.294</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-0.918</v>
+        <v>-0.923</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>4.7399</v>
+        <v>5.4674</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="n">
-        <v>4.7563</v>
+        <v>4.695</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.089</v>
+        <v>0.083</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.2292</v>
+        <v>0.21</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>6.3</v>
       </c>
       <c r="L13" s="27" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M13" s="27" t="n">
         <v>7.3</v>
@@ -1615,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>0.2836</v>
+        <v>0.265</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>1.2</v>
+        <v>4.8886</v>
       </c>
     </row>
     <row r="14"/>
@@ -1629,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-12-18 (58 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-12-18 (57 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="18">
       <c r="B18" s="22" t="n">
-        <v>1.7887</v>
+        <v>7.4923</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>1</v>
@@ -1731,10 +1731,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="24" t="n">
         <v>10</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="G18" s="25" t="n">
         <v>0.14</v>
@@ -1743,7 +1743,7 @@
         <v>0.05</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>0.2</v>
+        <v>0.85</v>
       </c>
       <c r="J18" s="26" t="n">
         <v>0.5</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M18" s="16" t="n">
         <v>0</v>
@@ -1764,24 +1764,24 @@
         <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>4.4272</v>
+        <v>7.4059</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.741</v>
+        <v>-0.492</v>
       </c>
       <c r="R18" s="17" t="n">
-        <v>1.0103</v>
+        <v>0.9056999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>3.0684</v>
+        <v>2.2355</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.533</v>
+        <v>0.419</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.6251</v>
+        <v>0.7883</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>0</v>
@@ -1796,16 +1796,16 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="J19" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="L19" s="27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M19" s="27" t="n">
         <v>0</v>
@@ -1820,15 +1820,15 @@
         <v>0</v>
       </c>
       <c r="Q19" s="29" t="n">
-        <v>-0.858</v>
+        <v>-0.86</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>2.2453</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.5646</v>
+        <v>2.4379</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="29" t="n">
-        <v>-0.858</v>
+        <v>-0.86</v>
       </c>
       <c r="R20" s="30" t="n">
         <v>1.2</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>2.4263</v>
+        <v>2.3278</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0</v>
@@ -1926,15 +1926,15 @@
         <v>0</v>
       </c>
       <c r="Q21" s="29" t="n">
-        <v>-0.858</v>
+        <v>-0.86</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>1.2</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>8.1982</v>
+        <v>1.2</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>0</v>
@@ -1955,16 +1955,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J22" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K22" s="27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="L22" s="27" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M22" s="27" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="29" t="n">
-        <v>-0.858</v>
+        <v>-0.86</v>
       </c>
       <c r="R22" s="30" t="n">
         <v>1.2</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="J23" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K23" s="27" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L23" s="27" t="n">
         <v>5.1</v>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="29" t="n">
-        <v>-0.858</v>
+        <v>-0.86</v>
       </c>
       <c r="R23" s="30" t="n">
         <v>1.2</v>
@@ -2067,7 +2067,7 @@
         <v>7.5</v>
       </c>
       <c r="K24" s="27" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>7.7</v>
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.1096</v>
+        <v>0.0397</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>-0.863</v>
+        <v>-0.862</v>
       </c>
       <c r="R24" s="30" t="n">
-        <v>2.5535</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25"/>
@@ -2096,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (86 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (85 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2189,28 +2189,28 @@
     </row>
     <row r="29">
       <c r="B29" s="22" t="n">
-        <v>1.5293</v>
+        <v>1.235</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.695</v>
+        <v>0.735</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>1.102</v>
+        <v>0.9896</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>24</v>
+        <v>308</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>10060</v>
+        <v>10049</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J29" s="26" t="n">
         <v>0.5</v>
@@ -2219,42 +2219,42 @@
         <v>0.05</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="N29" s="14" t="n">
         <v>2093</v>
       </c>
       <c r="O29" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>1.1231</v>
+        <v>1.0074</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>-0.335</v>
+        <v>-0.293</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>1.2148</v>
+        <v>1.6175</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.661</v>
+        <v>1.5246</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.38</v>
+        <v>0.401</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8793</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6807</v>
+        <v>7006</v>
       </c>
       <c r="G30" s="16" t="n">
         <v>0.1</v>
@@ -2269,10 +2269,10 @@
         <v>1</v>
       </c>
       <c r="K30" s="27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L30" s="27" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="M30" s="27" t="n">
         <v>0.48</v>
@@ -2284,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.9354</v>
+        <v>0.9114</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.656</v>
+        <v>-0.635</v>
       </c>
       <c r="R30" s="30" t="n">
-        <v>2.8523</v>
+        <v>2.3281</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.8481</v>
+        <v>1.7408</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.279</v>
+        <v>0.29</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.6861</v>
+        <v>0.6704</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
@@ -2337,24 +2337,24 @@
         <v>0</v>
       </c>
       <c r="P31" s="29" t="n">
-        <v>0.7317</v>
+        <v>0.7107</v>
       </c>
       <c r="Q31" s="29" t="n">
-        <v>-0.762</v>
+        <v>-0.749</v>
       </c>
       <c r="R31" s="30" t="n">
-        <v>3.1139</v>
+        <v>3.3017</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>4.1324</v>
+        <v>3.4506</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5668</v>
+        <v>0.5513</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="26" t="n">
         <v>2</v>
@@ -2390,24 +2390,24 @@
         <v>0</v>
       </c>
       <c r="P32" s="29" t="n">
-        <v>0.6218</v>
+        <v>0.6004</v>
       </c>
       <c r="Q32" s="29" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.806</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>2.122</v>
+        <v>2.4813</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.8936</v>
+        <v>2.7686</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.201</v>
+        <v>0.206</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.4916</v>
+        <v>0.4763</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
@@ -2431,42 +2431,42 @@
         <v>1.5</v>
       </c>
       <c r="L33" s="27" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N33" s="28" t="n">
         <v>153</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="29" t="n">
-        <v>0.5528</v>
+        <v>0.5335</v>
       </c>
       <c r="Q33" s="29" t="n">
-        <v>-0.848</v>
+        <v>-0.841</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>2.352</v>
+        <v>2.4504</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>3.755</v>
+        <v>4.0826</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.329</v>
+        <v>0.3146</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="G34" s="16" t="n">
         <v>0.04</v>
@@ -2475,16 +2475,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="J34" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L34" s="27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M34" s="27" t="n">
         <v>3.8</v>
@@ -2496,24 +2496,24 @@
         <v>0</v>
       </c>
       <c r="P34" s="29" t="n">
-        <v>0.4324</v>
+        <v>0.4121</v>
       </c>
       <c r="Q34" s="29" t="n">
-        <v>-0.928</v>
+        <v>-0.924</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>4.176</v>
+        <v>3.4445</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.5646</v>
+        <v>4.4154</v>
       </c>
       <c r="C35" s="15" t="n">
         <v>0.117</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2671</v>
+        <v>0.2537</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
@@ -2549,24 +2549,24 @@
         <v>0</v>
       </c>
       <c r="P35" s="29" t="n">
-        <v>0.3802</v>
+        <v>0.3758</v>
       </c>
       <c r="Q35" s="29" t="n">
-        <v>-0.968</v>
+        <v>-0.965</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>3.4583</v>
+        <v>3.8618</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>3.0205</v>
+        <v>2.9511</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.2327</v>
+        <v>0.22</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>0</v>
@@ -2602,24 +2602,24 @@
         <v>0</v>
       </c>
       <c r="P36" s="29" t="n">
-        <v>0.1581</v>
+        <v>0.158</v>
       </c>
       <c r="Q36" s="29" t="n">
-        <v>-0.988</v>
+        <v>-0.987</v>
       </c>
       <c r="R36" s="30" t="n">
-        <v>3.7575</v>
+        <v>4.1643</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>3.1709</v>
+        <v>3.103</v>
       </c>
       <c r="C37" s="15" t="n">
         <v>0.095</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.2103</v>
+        <v>0.1982</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>12.5</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="L37" s="27" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="M37" s="27" t="n">
         <v>10.94</v>
@@ -2655,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="29" t="n">
-        <v>0.036</v>
+        <v>0.0407</v>
       </c>
       <c r="Q37" s="29" t="n">
         <v>-0.997</v>
       </c>
       <c r="R37" s="30" t="n">
-        <v>5.1545</v>
+        <v>4.4022</v>
       </c>
     </row>
     <row r="38"/>
@@ -2669,7 +2669,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (121 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (120 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2762,13 +2762,13 @@
     </row>
     <row r="42">
       <c r="B42" s="22" t="n">
-        <v>3.0161</v>
+        <v>2.6812</v>
       </c>
       <c r="C42" s="23" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.709</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>0.7169</v>
+        <v>0.6603</v>
       </c>
       <c r="E42" s="24" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M42" s="16" t="n">
         <v>0.11</v>
@@ -2804,36 +2804,36 @@
         <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0.7075</v>
+        <v>0.6476</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>-0.297</v>
+        <v>-0.274</v>
       </c>
       <c r="R42" s="17" t="n">
-        <v>4.1067</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.2452</v>
+        <v>1.3668</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.415</v>
+        <v>0.425</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.761</v>
+        <v>0.7426</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6499</v>
+        <v>6493</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>0.1</v>
@@ -2842,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="L43" s="27" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="M43" s="27" t="n">
         <v>0.45</v>
@@ -2857,36 +2857,36 @@
         <v>0</v>
       </c>
       <c r="P43" s="29" t="n">
-        <v>0.7778</v>
+        <v>0.7548</v>
       </c>
       <c r="Q43" s="29" t="n">
-        <v>-0.569</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="R43" s="30" t="n">
-        <v>0</v>
+        <v>1.6965</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.8622</v>
+        <v>1.534</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.6294</v>
+        <v>0.6119</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>5582</v>
+        <v>5594</v>
       </c>
       <c r="G44" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I44" s="16" t="n">
         <v>0.75</v>
@@ -2895,10 +2895,10 @@
         <v>1.5</v>
       </c>
       <c r="K44" s="27" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M44" s="27" t="n">
         <v>1.02</v>
@@ -2910,48 +2910,48 @@
         <v>0</v>
       </c>
       <c r="P44" s="29" t="n">
-        <v>0.6654</v>
+        <v>0.6425</v>
       </c>
       <c r="Q44" s="29" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.675</v>
       </c>
       <c r="R44" s="30" t="n">
-        <v>1.9454</v>
+        <v>1.7229</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>1.5512</v>
+        <v>1.7757</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.252</v>
+        <v>0.255</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5366</v>
+        <v>0.5189</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F45" s="14" t="n">
         <v>1071</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J45" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L45" s="27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M45" s="27" t="n">
         <v>1.35</v>
@@ -2963,24 +2963,24 @@
         <v>0</v>
       </c>
       <c r="P45" s="29" t="n">
-        <v>0.5893</v>
+        <v>0.5644</v>
       </c>
       <c r="Q45" s="29" t="n">
-        <v>-0.743</v>
+        <v>-0.737</v>
       </c>
       <c r="R45" s="30" t="n">
-        <v>2.2276</v>
+        <v>2.0064</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>3.1533</v>
+        <v>2.8197</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.219</v>
+        <v>0.22</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4726</v>
+        <v>0.4554</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J46" s="26" t="n">
         <v>2.5</v>
@@ -3016,24 +3016,24 @@
         <v>0</v>
       </c>
       <c r="P46" s="29" t="n">
-        <v>0.5413</v>
+        <v>0.5149</v>
       </c>
       <c r="Q46" s="29" t="n">
-        <v>-0.782</v>
+        <v>-0.777</v>
       </c>
       <c r="R46" s="30" t="n">
-        <v>1.9126</v>
+        <v>2.2187</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.3114</v>
+        <v>4.1389</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3205</v>
+        <v>0.3069</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3069,24 +3069,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="29" t="n">
-        <v>0.4644</v>
+        <v>0.4248</v>
       </c>
       <c r="Q47" s="29" t="n">
-        <v>-0.884</v>
+        <v>-0.877</v>
       </c>
       <c r="R47" s="30" t="n">
-        <v>2.5464</v>
+        <v>2.8638</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>5.864</v>
+        <v>5.5527</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2577</v>
+        <v>0.2466</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>7.5</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="L48" s="27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="M48" s="27" t="n">
         <v>0</v>
@@ -3122,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="29" t="n">
-        <v>0.476</v>
+        <v>0.461</v>
       </c>
       <c r="Q48" s="29" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="R48" s="30" t="n">
-        <v>2.9272</v>
+        <v>2.6645</v>
       </c>
     </row>
     <row r="49"/>
@@ -3136,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (212 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (211 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3229,25 +3229,25 @@
     </row>
     <row r="53">
       <c r="B53" s="22" t="n">
-        <v>1.3885</v>
+        <v>1.3708</v>
       </c>
       <c r="C53" s="23" t="n">
-        <v>0.775</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.5216</v>
       </c>
       <c r="E53" s="24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F53" s="24" t="n">
         <v>336</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>0.3</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M53" s="16" t="n">
         <v>0.2</v>
@@ -3271,30 +3271,30 @@
         <v>0</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>0.7471</v>
+        <v>0.5394</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>-0.292</v>
+        <v>-0.249</v>
       </c>
       <c r="R53" s="17" t="n">
-        <v>1.5448</v>
+        <v>1.8038</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>1.7469</v>
+        <v>1.4823</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.491</v>
+        <v>0.57</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.8264</v>
+        <v>0.6864</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G54" s="16" t="n">
         <v>0.15</v>
@@ -3303,16 +3303,16 @@
         <v>0.15</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J54" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="27" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L54" s="27" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="M54" s="27" t="n">
         <v>0.59</v>
@@ -3324,24 +3324,24 @@
         <v>0</v>
       </c>
       <c r="P54" s="29" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.7379</v>
       </c>
       <c r="Q54" s="29" t="n">
-        <v>-0.593</v>
+        <v>-0.507</v>
       </c>
       <c r="R54" s="30" t="n">
-        <v>1.6119</v>
+        <v>1.2776</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>1.3062</v>
+        <v>1.0713</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.389</v>
+        <v>0.466</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
@@ -3353,10 +3353,10 @@
         <v>0.16</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J55" s="26" t="n">
         <v>1.5</v>
@@ -3377,30 +3377,30 @@
         <v>0</v>
       </c>
       <c r="P55" s="29" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.6913</v>
       </c>
       <c r="Q55" s="29" t="n">
-        <v>-0.707</v>
+        <v>-0.621</v>
       </c>
       <c r="R55" s="30" t="n">
-        <v>1.6509</v>
+        <v>1.7766</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>1.6568</v>
+        <v>1.4273</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.338</v>
+        <v>0.409</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.6054</v>
+        <v>0.5612</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G56" s="16" t="n">
         <v>0.08</v>
@@ -3409,16 +3409,16 @@
         <v>0</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J56" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K56" s="27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L56" s="27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M56" s="27" t="n">
         <v>0</v>
@@ -3430,24 +3430,24 @@
         <v>0</v>
       </c>
       <c r="P56" s="29" t="n">
-        <v>0.7317</v>
+        <v>0.6499</v>
       </c>
       <c r="Q56" s="29" t="n">
-        <v>-0.768</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="R56" s="30" t="n">
-        <v>1.8793</v>
+        <v>1.7072</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>1.4505</v>
+        <v>3.3533</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.305</v>
+        <v>0.373</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5461</v>
+        <v>0.5177</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
@@ -3462,51 +3462,51 @@
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="J57" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K57" s="27" t="n">
-        <v>0.65</v>
+        <v>1.5</v>
       </c>
       <c r="L57" s="27" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N57" s="28" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" s="29" t="n">
-        <v>0.6982</v>
+        <v>0.6244</v>
       </c>
       <c r="Q57" s="29" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="R57" s="30" t="n">
-        <v>3.1759</v>
+        <v>2.6229</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>1.579</v>
+        <v>1.5331</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.228</v>
+        <v>0.284</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.403</v>
+        <v>0.4022</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G58" s="16" t="n">
         <v>0.05</v>
@@ -3536,24 +3536,24 @@
         <v>0</v>
       </c>
       <c r="P58" s="29" t="n">
-        <v>0.6266</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="Q58" s="29" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.859</v>
       </c>
       <c r="R58" s="30" t="n">
-        <v>3.2299</v>
+        <v>3.3264</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>2.0239</v>
+        <v>1.9708</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.194</v>
+        <v>0.243</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3405</v>
+        <v>0.3474</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="29" t="n">
-        <v>0.1851</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="Q59" s="29" t="n">
-        <v>-0.985</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="R59" s="30" t="n">
-        <v>1.2</v>
+        <v>2.3058</v>
       </c>
     </row>
   </sheetData>
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3714,29 +3714,29 @@
     <row r="6">
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>0.52</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>351</v>
+        <v>479</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>350</v>
+        <v>472</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52615</v>
+        <v>52837</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.098</v>
@@ -3745,10 +3745,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1848028</v>
+        <v>1964829</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1.9397</v>
+        <v>2.5511</v>
       </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
@@ -3759,41 +3759,41 @@
     <row r="7">
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C7" s="35" t="n">
-        <v>0.493</v>
+        <v>0.52</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>245</v>
+        <v>351</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52420</v>
+        <v>52615</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5168</v>
+        <v>5172</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K7" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1783238</v>
+        <v>1848028</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>2.1247</v>
+        <v>1.9397</v>
       </c>
       <c r="N7" s="34" t="inlineStr">
         <is>
@@ -3804,41 +3804,41 @@
     <row r="8">
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>0.488</v>
+        <v>0.493</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1068</v>
+        <v>245</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1068</v>
+        <v>240</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52426</v>
+        <v>52420</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5148</v>
+        <v>5168</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1713337</v>
+        <v>1783238</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>2.3701</v>
+        <v>2.1247</v>
       </c>
       <c r="N8" s="31" t="inlineStr">
         <is>
@@ -3849,17 +3849,17 @@
     <row r="9">
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C9" s="35" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>0</v>
@@ -3868,10 +3868,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52809</v>
+        <v>52426</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5156</v>
+        <v>5148</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.098</v>
@@ -3880,10 +3880,10 @@
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>1758474</v>
+        <v>1713337</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>2.3822</v>
+        <v>2.3701</v>
       </c>
       <c r="N9" s="34" t="inlineStr">
         <is>
@@ -3894,29 +3894,29 @@
     <row r="10">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.098</v>
@@ -3925,10 +3925,10 @@
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N10" s="31" t="inlineStr">
         <is>
@@ -3939,29 +3939,29 @@
     <row r="11">
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C11" s="35" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.098</v>
@@ -3970,10 +3970,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N11" s="34" t="inlineStr">
         <is>
@@ -3984,29 +3984,29 @@
     <row r="12">
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.098</v>
@@ -4015,10 +4015,10 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N12" s="31" t="inlineStr">
         <is>
@@ -4029,29 +4029,29 @@
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C13" s="35" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.098</v>
@@ -4060,10 +4060,10 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N13" s="34" t="inlineStr">
         <is>
@@ -4074,26 +4074,26 @@
     <row r="14">
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>5157</v>
@@ -4105,10 +4105,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N14" s="31" t="inlineStr">
         <is>
@@ -4119,41 +4119,41 @@
     <row r="15">
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C15" s="35" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>5157</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K15" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N15" s="34" t="inlineStr">
         <is>
@@ -4164,29 +4164,29 @@
     <row r="16">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>0.099</v>
@@ -4195,10 +4195,10 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N16" s="31" t="inlineStr">
         <is>
@@ -4209,29 +4209,29 @@
     <row r="17">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0.099</v>
@@ -4240,10 +4240,10 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N17" s="34" t="inlineStr">
         <is>
@@ -4254,26 +4254,26 @@
     <row r="18">
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>5161</v>
@@ -4285,10 +4285,10 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N18" s="31" t="inlineStr">
         <is>
@@ -4299,17 +4299,17 @@
     <row r="19">
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C19" s="35" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F19" s="14" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>5161</v>
@@ -4330,10 +4330,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N19" s="34" t="inlineStr">
         <is>
@@ -4344,29 +4344,29 @@
     <row r="20">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>0.099</v>
@@ -4375,10 +4375,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
@@ -4389,41 +4389,41 @@
     <row r="21">
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C21" s="35" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>5159</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K21" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N21" s="34" t="inlineStr">
         <is>
@@ -4434,29 +4434,29 @@
     <row r="22">
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J22" s="9" t="n">
         <v>0.098</v>
@@ -4465,10 +4465,10 @@
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N22" s="31" t="inlineStr">
         <is>
@@ -4479,29 +4479,29 @@
     <row r="23">
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0.098</v>
@@ -4510,10 +4510,10 @@
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N23" s="34" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
     <row r="24">
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>5156</v>
@@ -4555,10 +4555,10 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N24" s="31" t="inlineStr">
         <is>
@@ -4569,41 +4569,41 @@
     <row r="25">
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C25" s="35" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K25" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N25" s="34" t="inlineStr">
         <is>
@@ -4614,41 +4614,41 @@
     <row r="26">
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N26" s="31" t="inlineStr">
         <is>
@@ -4659,41 +4659,41 @@
     <row r="27">
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C27" s="35" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N27" s="34" t="inlineStr">
         <is>
@@ -4704,29 +4704,29 @@
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>0.093</v>
@@ -4735,10 +4735,10 @@
         <v>0.5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N28" s="31" t="inlineStr">
         <is>
@@ -4749,73 +4749,77 @@
     <row r="29">
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C29" s="35" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K29" s="16" t="n"/>
+        <v>0.093</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="17" t="n"/>
+        <v>2361798</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N29" s="34" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K30" s="10" t="n"/>
       <c r="L30" s="12" t="n">
@@ -4831,32 +4835,32 @@
     <row r="31">
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K31" s="16" t="n"/>
       <c r="L31" s="18" t="n">
@@ -4872,31 +4876,33 @@
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="9" t="n"/>
+        <v>7194</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -4911,23 +4917,23 @@
     <row r="33">
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H33" s="14" t="n">
         <v>0</v>
@@ -4950,33 +4956,31 @@
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -4991,31 +4995,33 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="15" t="n"/>
+        <v>6136</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
@@ -5030,23 +5036,23 @@
     <row r="36">
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
         <v>1.69</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
@@ -5069,33 +5075,31 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J37" s="15" t="n"/>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
@@ -5110,31 +5114,33 @@
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="n"/>
+        <v>5834</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
@@ -5149,33 +5155,31 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J39" s="15" t="n"/>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -5190,31 +5194,33 @@
     <row r="40">
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="n"/>
+        <v>4272</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -5229,11 +5235,11 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>2568</v>
@@ -5248,14 +5254,12 @@
         <v>0.27</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J41" s="15" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J41" s="15" t="n"/>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
@@ -5270,11 +5274,11 @@
     <row r="42">
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>2568</v>
@@ -5289,12 +5293,14 @@
         <v>0.27</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9" t="n"/>
+        <v>4145</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="12" t="n">
         <v>0</v>
@@ -5309,11 +5315,11 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C43" s="35" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>2568</v>
@@ -5328,14 +5334,12 @@
         <v>0.27</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J43" s="15" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J43" s="15" t="n"/>
       <c r="K43" s="16" t="n"/>
       <c r="L43" s="18" t="n">
         <v>0</v>
@@ -5350,29 +5354,33 @@
     <row r="44">
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9" t="n"/>
+        <v>546</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="9" t="n"/>
+        <v>4059</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="12" t="n">
         <v>0</v>
@@ -5387,11 +5395,11 @@
     <row r="45">
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C45" s="35" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
@@ -5424,11 +5432,11 @@
     <row r="46">
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>0</v>
@@ -5461,11 +5469,11 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C47" s="35" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
@@ -5498,11 +5506,11 @@
     <row r="48">
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>0</v>
@@ -5535,11 +5543,11 @@
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C49" s="35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>0</v>
@@ -5572,7 +5580,7 @@
     <row r="50">
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
@@ -5609,7 +5617,7 @@
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C51" s="35" t="n">
@@ -5646,7 +5654,7 @@
     <row r="52">
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C52" s="32" t="n">
@@ -5675,6 +5683,43 @@
       </c>
       <c r="M52" s="11" t="n"/>
       <c r="N52" s="31" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="15" t="n"/>
+      <c r="K53" s="16" t="n"/>
+      <c r="L53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="17" t="n"/>
+      <c r="N53" s="34" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5795,19 +5840,19 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1749</v>
+        <v>1724</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1749</v>
+        <v>1724</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1749</v>
+        <v>1724</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1749</v>
+        <v>1724</v>
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
@@ -5835,19 +5880,19 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K7" s="34" t="inlineStr">
         <is>
@@ -6355,19 +6400,19 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
@@ -6915,19 +6960,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>10060</v>
+        <v>10049</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10060</v>
+        <v>10049</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>10060</v>
+        <v>10049</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>10060</v>
+        <v>10049</v>
       </c>
       <c r="K34" s="31" t="inlineStr">
         <is>
@@ -6995,19 +7040,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6807</v>
+        <v>7006</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6807</v>
+        <v>7006</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6807</v>
+        <v>7006</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>6807</v>
+        <v>7006</v>
       </c>
       <c r="K36" s="31" t="inlineStr">
         <is>
@@ -7315,19 +7360,19 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="K44" s="31" t="inlineStr">
         <is>
@@ -7715,19 +7760,19 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>6499</v>
+        <v>6493</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>6499</v>
+        <v>6493</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>6499</v>
+        <v>6493</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>6499</v>
+        <v>6493</v>
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
@@ -7795,19 +7840,19 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>5582</v>
+        <v>5594</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>5582</v>
+        <v>5594</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>5582</v>
+        <v>5594</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>5582</v>
+        <v>5594</v>
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
@@ -8275,10 +8320,10 @@
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>0</v>
@@ -8287,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="K68" s="31" t="inlineStr">
         <is>
@@ -8435,10 +8480,10 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>0</v>
@@ -8447,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="K72" s="31" t="inlineStr">
         <is>
@@ -8595,10 +8640,10 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H76" s="8" t="n">
         <v>0</v>
@@ -8607,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K76" s="31" t="inlineStr">
         <is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 22/10/2026 10:05 | Market session: 2026-10-21 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 23/10/2026 10:15 | Market session: 2026-10-22 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.5610</t>
+          <t>$0.5640</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>479 contracts</t>
+          <t>92 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.015 (call-skewed volume)</t>
+          <t>0.022 (very low volume (92 contracts): not meaningful)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,837</t>
+          <t>52,908</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5,173</t>
+          <t>5,174</t>
         </is>
       </c>
     </row>
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7180</v>
+        <v>7210</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1584</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>0</v>
@@ -919,10 +919,10 @@
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>2.4653</v>
+        <v>2.6252</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>155951</v>
+        <v>150458</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>5</v>
+        <v>2.196</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1000</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27650</v>
+        <v>27660</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3384</v>
@@ -991,22 +991,22 @@
         <v>0.122</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>364</v>
+        <v>18</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0.016</v>
+        <v>0.111</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>2.0101</v>
+        <v>1.9967</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1089902</v>
+        <v>1076364</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17265</v>
+        <v>17259</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>197</v>
@@ -1033,7 +1033,7 @@
         <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>1.8307</v>
+        <v>2.0891</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>672809</v>
+        <v>666514</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1063,34 +1063,34 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>732</v>
+        <v>769</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>1.4495</v>
+        <v>1.92</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>45167</v>
+        <v>48033</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.5610 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.5640 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (29 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (28 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
     </row>
     <row r="7">
       <c r="B7" s="22" t="n">
-        <v>0.3149</v>
+        <v>1.8704</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0.716</v>
+        <v>0.712</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>1.5708</v>
+        <v>1.6176</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="26" t="n">
         <v>0.5</v>
@@ -1297,30 +1297,30 @@
         <v>0</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>1.5836</v>
+        <v>1.6306</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>-0.295</v>
+        <v>-0.299</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>3.1122</v>
+        <v>3.1513</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>1.7464</v>
+        <v>1.788</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.282</v>
+        <v>0.272</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.04</v>
@@ -1335,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="M8" s="27" t="n">
         <v>0.45</v>
@@ -1350,24 +1350,24 @@
         <v>0</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.9823</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-0.732</v>
+        <v>-0.742</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>2.6395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>2.4633</v>
+        <v>2.5162</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.197</v>
+        <v>0.187</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.6351</v>
+        <v>0.629</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>1.5</v>
       </c>
       <c r="K9" s="27" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="L9" s="27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M9" s="27" t="n">
         <v>1</v>
@@ -1403,24 +1403,24 @@
         <v>0</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>0.6515</v>
+        <v>0.6463</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.828</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>3.4589</v>
+        <v>2.4028</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="n">
-        <v>4.7811</v>
+        <v>4.8802</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.161</v>
+        <v>0.151</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.494</v>
+        <v>0.4848</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>0</v>
@@ -1441,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="K10" s="27" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L10" s="27" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M10" s="27" t="n">
         <v>1.33</v>
@@ -1456,24 +1456,24 @@
         <v>0</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>0.5108</v>
+        <v>0.5031</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-0.855</v>
+        <v>-0.864</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>3.9798</v>
+        <v>6.8502</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="n">
-        <v>3.8446</v>
+        <v>3.9225</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.141</v>
+        <v>0.131</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.4152</v>
+        <v>0.4046</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>2.5</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="L11" s="27" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M11" s="27" t="n">
         <v>1.87</v>
@@ -1509,24 +1509,24 @@
         <v>0</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>0.4329</v>
+        <v>0.4232</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-0.876</v>
+        <v>-0.886</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>7.9774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="n">
-        <v>4.8389</v>
+        <v>4.9332</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.099</v>
+        <v>0.09</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.2631</v>
+        <v>0.2514</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>5.1</v>
@@ -1562,24 +1562,24 @@
         <v>0</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>0.294</v>
+        <v>0.2672</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-0.923</v>
+        <v>-0.931</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>5.4674</v>
+        <v>4.2797</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="n">
-        <v>4.695</v>
+        <v>4.7848</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.21</v>
+        <v>0.1985</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1615,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>0.265</v>
+        <v>0.2727</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-0.945</v>
+        <v>-0.952</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>4.8886</v>
+        <v>4.8808</v>
       </c>
     </row>
     <row r="14"/>
@@ -1629,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-12-18 (57 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-12-18 (56 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="18">
       <c r="B18" s="22" t="n">
-        <v>7.4923</v>
+        <v>2.196</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>1</v>
@@ -1740,10 +1740,10 @@
         <v>0.14</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="J18" s="26" t="n">
         <v>0.5</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="M18" s="16" t="n">
         <v>0</v>
@@ -1764,24 +1764,24 @@
         <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>7.4059</v>
+        <v>7.4409</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.492</v>
+        <v>-0.503</v>
       </c>
       <c r="R18" s="17" t="n">
-        <v>0.9056999999999999</v>
+        <v>1.2372</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>2.2355</v>
+        <v>2.262</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.419</v>
+        <v>0.422</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.7883</v>
+        <v>0.7832</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>0</v>
@@ -1802,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="27" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M19" s="27" t="n">
         <v>0</v>
@@ -1820,15 +1820,15 @@
         <v>0</v>
       </c>
       <c r="Q19" s="29" t="n">
-        <v>-0.86</v>
+        <v>-0.862</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>1.2</v>
+        <v>2.5742</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.4379</v>
+        <v>2.4646</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>1.5</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="L20" s="27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M20" s="27" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="29" t="n">
-        <v>-0.86</v>
+        <v>-0.862</v>
       </c>
       <c r="R20" s="30" t="n">
         <v>1.2</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>2.3278</v>
+        <v>2.3523</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0</v>
@@ -1926,15 +1926,15 @@
         <v>0</v>
       </c>
       <c r="Q21" s="29" t="n">
-        <v>-0.86</v>
+        <v>-0.862</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>1.577</v>
+        <v>1.4542</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>1.2</v>
+        <v>4.4321</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>0</v>
@@ -1955,16 +1955,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J22" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K22" s="27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L22" s="27" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M22" s="27" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="29" t="n">
-        <v>-0.86</v>
+        <v>-0.862</v>
       </c>
       <c r="R22" s="30" t="n">
         <v>1.2</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="J23" s="26" t="n">
         <v>5</v>
@@ -2017,7 +2017,7 @@
         <v>3.7</v>
       </c>
       <c r="L23" s="27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M23" s="27" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="29" t="n">
-        <v>-0.86</v>
+        <v>-0.862</v>
       </c>
       <c r="R23" s="30" t="n">
         <v>1.2</v>
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.0397</v>
+        <v>0.0373</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.864</v>
       </c>
       <c r="R24" s="30" t="n">
         <v>1.2</v>
@@ -2096,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (85 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (84 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2189,19 +2189,19 @@
     </row>
     <row r="29">
       <c r="B29" s="22" t="n">
-        <v>1.235</v>
+        <v>1.008</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.9896</v>
+        <v>1.0078</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>308</v>
+        <v>1</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>10049</v>
+        <v>10064</v>
       </c>
       <c r="G29" s="25" t="n">
         <v>0.15</v>
@@ -2210,7 +2210,7 @@
         <v>0.05</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="J29" s="26" t="n">
         <v>0.5</v>
@@ -2219,60 +2219,60 @@
         <v>0.05</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="N29" s="14" t="n">
         <v>2093</v>
       </c>
       <c r="O29" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>1.0074</v>
+        <v>1.0258</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>-0.293</v>
+        <v>-0.297</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>1.6175</v>
+        <v>2.4491</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.5246</v>
+        <v>1.7796</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.401</v>
+        <v>0.395</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.8793</v>
+        <v>0.8854</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>7006</v>
+        <v>7001</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H30" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J30" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M30" s="27" t="n">
         <v>0.48</v>
@@ -2284,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.9114</v>
+        <v>0.9176</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.635</v>
+        <v>-0.64</v>
       </c>
       <c r="R30" s="30" t="n">
-        <v>2.3281</v>
+        <v>1.6327</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.7408</v>
+        <v>1.7616</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.6704</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0.7</v>
       </c>
       <c r="L31" s="27" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M31" s="27" t="n">
         <v>0.97</v>
@@ -2337,24 +2337,24 @@
         <v>0</v>
       </c>
       <c r="P31" s="29" t="n">
-        <v>0.7107</v>
+        <v>0.712</v>
       </c>
       <c r="Q31" s="29" t="n">
-        <v>-0.749</v>
+        <v>-0.754</v>
       </c>
       <c r="R31" s="30" t="n">
-        <v>3.3017</v>
+        <v>2.8479</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>3.4506</v>
+        <v>3.0389</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.5513</v>
+        <v>0.551</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
@@ -2369,16 +2369,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L32" s="27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M32" s="27" t="n">
         <v>1.3</v>
@@ -2390,24 +2390,24 @@
         <v>0</v>
       </c>
       <c r="P32" s="29" t="n">
-        <v>0.6004</v>
+        <v>0.6002</v>
       </c>
       <c r="Q32" s="29" t="n">
-        <v>-0.806</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>2.4813</v>
+        <v>1.8448</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.7686</v>
+        <v>2.7974</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.206</v>
+        <v>0.201</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.4763</v>
+        <v>0.475</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>2.5</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="L33" s="27" t="n">
         <v>2.45</v>
@@ -2440,27 +2440,27 @@
         <v>153</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="29" t="n">
-        <v>0.5335</v>
+        <v>0.5331</v>
       </c>
       <c r="Q33" s="29" t="n">
-        <v>-0.841</v>
+        <v>-0.846</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>2.4504</v>
+        <v>2.0715</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>4.0826</v>
+        <v>4.1222</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.3146</v>
+        <v>0.312</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
@@ -2496,24 +2496,24 @@
         <v>0</v>
       </c>
       <c r="P34" s="29" t="n">
-        <v>0.4121</v>
+        <v>0.4042</v>
       </c>
       <c r="Q34" s="29" t="n">
-        <v>-0.924</v>
+        <v>-0.927</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>3.4445</v>
+        <v>3.4346</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.4154</v>
+        <v>4.4566</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.117</v>
+        <v>0.113</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2537</v>
+        <v>0.2508</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
@@ -2549,24 +2549,24 @@
         <v>0</v>
       </c>
       <c r="P35" s="29" t="n">
-        <v>0.3758</v>
+        <v>0.4172</v>
       </c>
       <c r="Q35" s="29" t="n">
-        <v>-0.965</v>
+        <v>-0.968</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>3.8618</v>
+        <v>3.8528</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>2.9511</v>
+        <v>2.9761</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.22</v>
+        <v>0.2171</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         <v>10</v>
       </c>
       <c r="K36" s="27" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="L36" s="27" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M36" s="27" t="n">
         <v>10</v>
@@ -2602,24 +2602,24 @@
         <v>0</v>
       </c>
       <c r="P36" s="29" t="n">
-        <v>0.158</v>
+        <v>0.1391</v>
       </c>
       <c r="Q36" s="29" t="n">
-        <v>-0.987</v>
+        <v>-0.989</v>
       </c>
       <c r="R36" s="30" t="n">
-        <v>4.1643</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>3.103</v>
+        <v>3.1288</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.095</v>
+        <v>0.091</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.1982</v>
+        <v>0.1952</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>12.5</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="L37" s="27" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="M37" s="27" t="n">
         <v>10.94</v>
@@ -2655,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="29" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="29" t="n">
-        <v>-0.997</v>
+        <v>-1</v>
       </c>
       <c r="R37" s="30" t="n">
-        <v>4.4022</v>
+        <v>8.2188</v>
       </c>
     </row>
     <row r="38"/>
@@ -2669,7 +2669,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (120 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (119 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2762,28 @@
     </row>
     <row r="42">
       <c r="B42" s="22" t="n">
-        <v>2.6812</v>
+        <v>1.688</v>
       </c>
       <c r="C42" s="23" t="n">
-        <v>0.709</v>
+        <v>0.706</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>0.6603</v>
+        <v>0.6702</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="24" t="n">
         <v>2505</v>
       </c>
       <c r="G42" s="25" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H42" s="25" t="n">
         <v>0.15</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J42" s="26" t="n">
         <v>0.5</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0.6476</v>
+        <v>0.6569</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>-0.274</v>
+        <v>-0.276</v>
       </c>
       <c r="R42" s="17" t="n">
         <v>0.125</v>
@@ -2815,19 +2815,19 @@
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.3668</v>
+        <v>1.9823</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.425</v>
+        <v>0.421</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.7426</v>
+        <v>0.748</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6493</v>
+        <v>6484</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>0.1</v>
@@ -2836,16 +2836,16 @@
         <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="J43" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L43" s="27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M43" s="27" t="n">
         <v>0.45</v>
@@ -2857,24 +2857,24 @@
         <v>0</v>
       </c>
       <c r="P43" s="29" t="n">
-        <v>0.7548</v>
+        <v>0.7599</v>
       </c>
       <c r="Q43" s="29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R43" s="30" t="n">
-        <v>1.6965</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.534</v>
+        <v>1.7785</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.311</v>
+        <v>0.308</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.6119</v>
+        <v>0.614</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I44" s="16" t="n">
         <v>0.75</v>
@@ -2910,30 +2910,30 @@
         <v>0</v>
       </c>
       <c r="P44" s="29" t="n">
-        <v>0.6425</v>
+        <v>0.6444</v>
       </c>
       <c r="Q44" s="29" t="n">
-        <v>-0.675</v>
+        <v>-0.679</v>
       </c>
       <c r="R44" s="30" t="n">
-        <v>1.7229</v>
+        <v>1.7132</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>1.7757</v>
+        <v>3.2514</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.255</v>
+        <v>0.251</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5189</v>
+        <v>0.5195</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G45" s="16" t="n">
         <v>0.02</v>
@@ -2942,16 +2942,16 @@
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="J45" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L45" s="27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M45" s="27" t="n">
         <v>1.35</v>
@@ -2963,24 +2963,24 @@
         <v>0</v>
       </c>
       <c r="P45" s="29" t="n">
-        <v>0.5644</v>
+        <v>0.5647</v>
       </c>
       <c r="Q45" s="29" t="n">
-        <v>-0.737</v>
+        <v>-0.74</v>
       </c>
       <c r="R45" s="30" t="n">
-        <v>2.0064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>2.8197</v>
+        <v>4.0779</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.22</v>
+        <v>0.217</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4554</v>
+        <v>0.4552</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -2995,16 +2995,16 @@
         <v>0</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K46" s="27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L46" s="27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M46" s="27" t="n">
         <v>0</v>
@@ -3016,24 +3016,24 @@
         <v>0</v>
       </c>
       <c r="P46" s="29" t="n">
-        <v>0.5149</v>
+        <v>0.5139</v>
       </c>
       <c r="Q46" s="29" t="n">
-        <v>-0.777</v>
+        <v>-0.78</v>
       </c>
       <c r="R46" s="30" t="n">
-        <v>2.2187</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>4.1389</v>
+        <v>3.1634</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3069</v>
+        <v>0.3054</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3048,16 +3048,16 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J47" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="L47" s="27" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="M47" s="27" t="n">
         <v>0</v>
@@ -3069,24 +3069,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="29" t="n">
-        <v>0.4248</v>
+        <v>0.4295</v>
       </c>
       <c r="Q47" s="29" t="n">
-        <v>-0.877</v>
+        <v>-0.88</v>
       </c>
       <c r="R47" s="30" t="n">
-        <v>2.8638</v>
+        <v>2.5959</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>5.5527</v>
+        <v>0.5</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2466</v>
+        <v>0.2449</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3101,16 +3101,16 @@
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>0.75</v>
+        <v>1.15</v>
       </c>
       <c r="J48" s="26" t="n">
         <v>7.5</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="L48" s="27" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M48" s="27" t="n">
         <v>0</v>
@@ -3122,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="29" t="n">
-        <v>0.461</v>
+        <v>0.4519</v>
       </c>
       <c r="Q48" s="29" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="R48" s="30" t="n">
-        <v>2.6645</v>
+        <v>2.6359</v>
       </c>
     </row>
     <row r="49"/>
@@ -3136,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (211 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (210 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3229,25 +3229,25 @@
     </row>
     <row r="53">
       <c r="B53" s="22" t="n">
-        <v>1.3708</v>
+        <v>1.2002</v>
       </c>
       <c r="C53" s="23" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>0.5216</v>
+        <v>0.5236</v>
       </c>
       <c r="E53" s="24" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F53" s="24" t="n">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>0.3</v>
@@ -3271,36 +3271,36 @@
         <v>0</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>0.5394</v>
+        <v>0.5399</v>
       </c>
       <c r="Q53" s="15" t="n">
         <v>-0.249</v>
       </c>
       <c r="R53" s="17" t="n">
-        <v>1.8038</v>
+        <v>1.8049</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>1.4823</v>
+        <v>1.3488</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.57</v>
+        <v>0.569</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.6864</v>
+        <v>0.6869</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" s="14" t="n">
         <v>176</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I54" s="16" t="n">
         <v>0.2</v>
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="K54" s="27" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L54" s="27" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="M54" s="27" t="n">
         <v>0.59</v>
@@ -3324,24 +3324,24 @@
         <v>0</v>
       </c>
       <c r="P54" s="29" t="n">
-        <v>0.7379</v>
+        <v>0.7352</v>
       </c>
       <c r="Q54" s="29" t="n">
-        <v>-0.507</v>
+        <v>-0.506</v>
       </c>
       <c r="R54" s="30" t="n">
-        <v>1.2776</v>
+        <v>1.5644</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>1.0713</v>
+        <v>2.2312</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" s="26" t="n">
         <v>1.5</v>
@@ -3377,24 +3377,24 @@
         <v>0</v>
       </c>
       <c r="P55" s="29" t="n">
-        <v>0.6913</v>
+        <v>0.6871</v>
       </c>
       <c r="Q55" s="29" t="n">
-        <v>-0.621</v>
+        <v>-0.62</v>
       </c>
       <c r="R55" s="30" t="n">
-        <v>1.7766</v>
+        <v>1.776</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>1.4273</v>
+        <v>4.4153</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.409</v>
+        <v>0.408</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.5612</v>
+        <v>0.5609</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="J56" s="26" t="n">
         <v>2</v>
@@ -3430,24 +3430,24 @@
         <v>0</v>
       </c>
       <c r="P56" s="29" t="n">
-        <v>0.6499</v>
+        <v>0.646</v>
       </c>
       <c r="Q56" s="29" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="R56" s="30" t="n">
-        <v>1.7072</v>
+        <v>1.7061</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>3.3533</v>
+        <v>0.5</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5177</v>
+        <v>0.5173</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
@@ -3462,45 +3462,45 @@
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>0.75</v>
+        <v>2.95</v>
       </c>
       <c r="J57" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K57" s="27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L57" s="27" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="M57" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="29" t="n">
-        <v>0.6244</v>
+        <v>0.6214</v>
       </c>
       <c r="Q57" s="29" t="n">
-        <v>-0.73</v>
+        <v>-0.729</v>
       </c>
       <c r="R57" s="30" t="n">
-        <v>2.6229</v>
+        <v>3.8332</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>1.5331</v>
+        <v>1.5376</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.4022</v>
+        <v>0.4016</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>5</v>
       </c>
       <c r="K58" s="27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="L58" s="27" t="n">
         <v>7</v>
@@ -3536,24 +3536,24 @@
         <v>0</v>
       </c>
       <c r="P58" s="29" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5831</v>
       </c>
       <c r="Q58" s="29" t="n">
-        <v>-0.859</v>
+        <v>-0.857</v>
       </c>
       <c r="R58" s="30" t="n">
-        <v>3.3264</v>
+        <v>2.7212</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>1.9708</v>
+        <v>1.9763</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.243</v>
+        <v>0.242</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3474</v>
+        <v>0.3467</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="29" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="Q59" s="29" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="R59" s="30" t="n">
-        <v>2.3058</v>
+        <v>2.3012</v>
       </c>
     </row>
   </sheetData>
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3714,29 +3714,29 @@
     <row r="6">
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>479</v>
+        <v>92</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>472</v>
+        <v>90</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52837</v>
+        <v>52908</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.098</v>
@@ -3745,10 +3745,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1964829</v>
+        <v>1942369</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.5511</v>
+        <v>2.1654</v>
       </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
@@ -3759,29 +3759,29 @@
     <row r="7">
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C7" s="35" t="n">
-        <v>0.52</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>351</v>
+        <v>479</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>350</v>
+        <v>472</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52615</v>
+        <v>52837</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -3790,10 +3790,10 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1848028</v>
+        <v>1964829</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1.9397</v>
+        <v>2.5511</v>
       </c>
       <c r="N7" s="34" t="inlineStr">
         <is>
@@ -3804,41 +3804,41 @@
     <row r="8">
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>0.493</v>
+        <v>0.52</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>245</v>
+        <v>351</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52420</v>
+        <v>52615</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5168</v>
+        <v>5172</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1783238</v>
+        <v>1848028</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>2.1247</v>
+        <v>1.9397</v>
       </c>
       <c r="N8" s="31" t="inlineStr">
         <is>
@@ -3849,41 +3849,41 @@
     <row r="9">
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C9" s="35" t="n">
-        <v>0.488</v>
+        <v>0.493</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1068</v>
+        <v>245</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1068</v>
+        <v>240</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52426</v>
+        <v>52420</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5148</v>
+        <v>5168</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K9" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>1713337</v>
+        <v>1783238</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>2.3701</v>
+        <v>2.1247</v>
       </c>
       <c r="N9" s="34" t="inlineStr">
         <is>
@@ -3894,17 +3894,17 @@
     <row r="10">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>0</v>
@@ -3913,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52809</v>
+        <v>52426</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5156</v>
+        <v>5148</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.098</v>
@@ -3925,10 +3925,10 @@
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1758474</v>
+        <v>1713337</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>2.3822</v>
+        <v>2.3701</v>
       </c>
       <c r="N10" s="31" t="inlineStr">
         <is>
@@ -3939,29 +3939,29 @@
     <row r="11">
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C11" s="35" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.098</v>
@@ -3970,10 +3970,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N11" s="34" t="inlineStr">
         <is>
@@ -3984,29 +3984,29 @@
     <row r="12">
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.098</v>
@@ -4015,10 +4015,10 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N12" s="31" t="inlineStr">
         <is>
@@ -4029,29 +4029,29 @@
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C13" s="35" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.098</v>
@@ -4060,10 +4060,10 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N13" s="34" t="inlineStr">
         <is>
@@ -4074,29 +4074,29 @@
     <row r="14">
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.098</v>
@@ -4105,10 +4105,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N14" s="31" t="inlineStr">
         <is>
@@ -4119,26 +4119,26 @@
     <row r="15">
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C15" s="35" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>5157</v>
@@ -4150,10 +4150,10 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N15" s="34" t="inlineStr">
         <is>
@@ -4164,41 +4164,41 @@
     <row r="16">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>5157</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N16" s="31" t="inlineStr">
         <is>
@@ -4209,29 +4209,29 @@
     <row r="17">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0.099</v>
@@ -4240,10 +4240,10 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N17" s="34" t="inlineStr">
         <is>
@@ -4254,29 +4254,29 @@
     <row r="18">
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.099</v>
@@ -4285,10 +4285,10 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N18" s="31" t="inlineStr">
         <is>
@@ -4299,26 +4299,26 @@
     <row r="19">
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C19" s="35" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>5161</v>
@@ -4330,10 +4330,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N19" s="34" t="inlineStr">
         <is>
@@ -4344,17 +4344,17 @@
     <row r="20">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>5161</v>
@@ -4375,10 +4375,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
@@ -4389,29 +4389,29 @@
     <row r="21">
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C21" s="35" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>0.099</v>
@@ -4420,10 +4420,10 @@
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N21" s="34" t="inlineStr">
         <is>
@@ -4434,41 +4434,41 @@
     <row r="22">
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>5159</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N22" s="31" t="inlineStr">
         <is>
@@ -4479,29 +4479,29 @@
     <row r="23">
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0.098</v>
@@ -4510,10 +4510,10 @@
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N23" s="34" t="inlineStr">
         <is>
@@ -4524,29 +4524,29 @@
     <row r="24">
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>0.098</v>
@@ -4555,10 +4555,10 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N24" s="31" t="inlineStr">
         <is>
@@ -4569,26 +4569,26 @@
     <row r="25">
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C25" s="35" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>5156</v>
@@ -4600,10 +4600,10 @@
         <v>0.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N25" s="34" t="inlineStr">
         <is>
@@ -4614,41 +4614,41 @@
     <row r="26">
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N26" s="31" t="inlineStr">
         <is>
@@ -4659,41 +4659,41 @@
     <row r="27">
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C27" s="35" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N27" s="34" t="inlineStr">
         <is>
@@ -4704,41 +4704,41 @@
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N28" s="31" t="inlineStr">
         <is>
@@ -4749,29 +4749,29 @@
     <row r="29">
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C29" s="35" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J29" s="15" t="n">
         <v>0.093</v>
@@ -4780,10 +4780,10 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M29" s="17" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N29" s="34" t="inlineStr">
         <is>
@@ -4794,73 +4794,77 @@
     <row r="30">
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K30" s="10" t="n"/>
+        <v>0.093</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="11" t="n"/>
+        <v>2361798</v>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N30" s="31" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K31" s="16" t="n"/>
       <c r="L31" s="18" t="n">
@@ -4876,32 +4880,32 @@
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
@@ -4917,31 +4921,33 @@
     <row r="33">
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="15" t="n"/>
+        <v>7194</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K33" s="16" t="n"/>
       <c r="L33" s="18" t="n">
         <v>0</v>
@@ -4956,23 +4962,23 @@
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
@@ -4995,33 +5001,31 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J35" s="15" t="n"/>
       <c r="K35" s="16" t="n"/>
       <c r="L35" s="18" t="n">
         <v>0</v>
@@ -5036,31 +5040,33 @@
     <row r="36">
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9" t="n"/>
+        <v>6136</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
@@ -5075,23 +5081,23 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
         <v>1.69</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H37" s="14" t="n">
         <v>0</v>
@@ -5114,33 +5120,31 @@
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="12" t="n">
         <v>0</v>
@@ -5155,31 +5159,33 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="15" t="n"/>
+        <v>5834</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -5194,33 +5200,31 @@
     <row r="40">
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -5235,31 +5239,33 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="15" t="n"/>
+        <v>4272</v>
+      </c>
+      <c r="J41" s="15" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
@@ -5274,11 +5280,11 @@
     <row r="42">
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>2568</v>
@@ -5293,14 +5299,12 @@
         <v>0.27</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J42" s="9" t="n"/>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="12" t="n">
         <v>0</v>
@@ -5315,11 +5319,11 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C43" s="35" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>2568</v>
@@ -5334,12 +5338,14 @@
         <v>0.27</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="15" t="n"/>
+        <v>4145</v>
+      </c>
+      <c r="J43" s="15" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K43" s="16" t="n"/>
       <c r="L43" s="18" t="n">
         <v>0</v>
@@ -5354,11 +5360,11 @@
     <row r="44">
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2568</v>
@@ -5373,14 +5379,12 @@
         <v>0.27</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n"/>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="12" t="n">
         <v>0</v>
@@ -5395,29 +5399,33 @@
     <row r="45">
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C45" s="35" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="15" t="n"/>
+        <v>546</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H45" s="14" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="15" t="n"/>
+        <v>4059</v>
+      </c>
+      <c r="J45" s="15" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K45" s="16" t="n"/>
       <c r="L45" s="18" t="n">
         <v>0</v>
@@ -5432,11 +5440,11 @@
     <row r="46">
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>0</v>
@@ -5469,11 +5477,11 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C47" s="35" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
@@ -5506,11 +5514,11 @@
     <row r="48">
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>0</v>
@@ -5543,11 +5551,11 @@
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C49" s="35" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>0</v>
@@ -5580,11 +5588,11 @@
     <row r="50">
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>0</v>
@@ -5617,7 +5625,7 @@
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C51" s="35" t="n">
@@ -5654,7 +5662,7 @@
     <row r="52">
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C52" s="32" t="n">
@@ -5691,7 +5699,7 @@
     <row r="53">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C53" s="35" t="n">
@@ -5720,6 +5728,43 @@
       </c>
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="34" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="31" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5840,19 +5885,19 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
@@ -5920,19 +5965,19 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="K8" s="31" t="inlineStr">
         <is>
@@ -6960,19 +7005,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>10049</v>
+        <v>10064</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10049</v>
+        <v>10064</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>10049</v>
+        <v>10064</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>10049</v>
+        <v>10064</v>
       </c>
       <c r="K34" s="31" t="inlineStr">
         <is>
@@ -7040,19 +7085,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>7006</v>
+        <v>7001</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>7006</v>
+        <v>7001</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>7006</v>
+        <v>7001</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>7006</v>
+        <v>7001</v>
       </c>
       <c r="K36" s="31" t="inlineStr">
         <is>
@@ -7760,19 +7805,19 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>6493</v>
+        <v>6484</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>6493</v>
+        <v>6484</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>6493</v>
+        <v>6484</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>6493</v>
+        <v>6484</v>
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
@@ -7920,19 +7965,19 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="K58" s="31" t="inlineStr">
         <is>
@@ -8240,10 +8285,10 @@
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>0</v>
@@ -8252,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="K66" s="31" t="inlineStr">
         <is>
@@ -8600,10 +8645,10 @@
         </is>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="14" t="n">
         <v>0</v>
@@ -8612,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" s="34" t="inlineStr">
         <is>

--- a/OTLK_Options_Chain_and_Derivatives.xlsx
+++ b/OTLK_Options_Chain_and_Derivatives.xlsx
@@ -733,7 +733,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 23/10/2026 10:15 | Market session: 2026-10-22 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
+          <t>Updated: 24/10/2026 10:23 | Market session: 2026-10-23 | Ticker: OTLK (NASDAQ) | Quantitative Model v2.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>$0.5640</t>
+          <t>$0.5190</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>92 contracts</t>
+          <t>26 contracts</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.022 (very low volume (92 contracts): not meaningful)</t>
+          <t>0.000 (very low volume (26 contracts): not meaningful)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>52,908</t>
+          <t>52,917</t>
         </is>
       </c>
     </row>
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7210</v>
+        <v>7221</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1584</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>0</v>
@@ -919,10 +919,10 @@
         <v>0.5</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>2.6252</v>
+        <v>2.7664</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>150458</v>
+        <v>119930</v>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>10</v>
@@ -961,10 +961,10 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>2.196</v>
+        <v>2.9639</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>1000</v>
+        <v>962</v>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>27660</v>
+        <v>27670</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3384</v>
@@ -991,22 +991,22 @@
         <v>0.122</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>1.9967</v>
+        <v>2.0507</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1076364</v>
+        <v>990406</v>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17259</v>
+        <v>17232</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>197</v>
@@ -1033,7 +1033,7 @@
         <v>0.011</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0.5</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>2.0891</v>
+        <v>2.4795</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>666514</v>
+        <v>624932</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>9</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0</v>
@@ -1087,10 +1087,10 @@
         <v>0.5</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>1.92</v>
+        <v>3.4981</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48033</v>
+        <v>47282</v>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spot Reference Price: $0.5640 | ITM/OTM ranges highlighted</t>
+          <t>Spot Reference Price: $0.5190 | ITM/OTM ranges highlighted</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-11-20 (28 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-11-20 (27 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1255,34 +1255,34 @@
     </row>
     <row r="7">
       <c r="B7" s="22" t="n">
-        <v>1.8704</v>
+        <v>1.4744</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0.712</v>
+        <v>0.643</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>1.6176</v>
+        <v>1.8893</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="G7" s="25" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J7" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L7" s="16" t="n">
         <v>0.3</v>
@@ -1297,24 +1297,24 @@
         <v>0</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>1.6306</v>
+        <v>1.906</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>-0.299</v>
+        <v>-0.367</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>3.1513</v>
+        <v>3.472</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="17" t="n">
-        <v>1.788</v>
+        <v>2.0025</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.272</v>
+        <v>0.243</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.9702</v>
+        <v>0.9593</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>0</v>
@@ -1335,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="27" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="M8" s="27" t="n">
         <v>0.45</v>
@@ -1350,24 +1350,24 @@
         <v>0</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9768</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-0.742</v>
+        <v>-0.77</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>0</v>
+        <v>3.1393</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="n">
-        <v>2.5162</v>
+        <v>2.7303</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.187</v>
+        <v>0.167</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.629</v>
+        <v>0.6213</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>0</v>
@@ -1403,39 +1403,39 @@
         <v>0</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>0.6463</v>
+        <v>0.6408</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-0.828</v>
+        <v>-0.847</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>2.4028</v>
+        <v>13.625</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="n">
-        <v>4.8802</v>
+        <v>4.3372</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.151</v>
+        <v>0.135</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.4848</v>
+        <v>0.4779</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>1358</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="J10" s="26" t="n">
         <v>2</v>
@@ -1444,7 +1444,7 @@
         <v>1.3</v>
       </c>
       <c r="L10" s="27" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M10" s="27" t="n">
         <v>1.33</v>
@@ -1456,24 +1456,24 @@
         <v>0</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>0.5031</v>
+        <v>0.4996</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-0.864</v>
+        <v>-0.88</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>6.8502</v>
+        <v>5.8318</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="n">
-        <v>3.9225</v>
+        <v>4.1841</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.131</v>
+        <v>0.116</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.4046</v>
+        <v>0.3979</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>2.5</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="L11" s="27" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M11" s="27" t="n">
         <v>1.87</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>0.4232</v>
+        <v>0.4203</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-0.886</v>
+        <v>-0.9</v>
       </c>
       <c r="R11" s="30" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="12">
       <c r="B12" s="17" t="n">
-        <v>4.9332</v>
+        <v>5.2039</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.2514</v>
+        <v>0.2446</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" s="27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M12" s="27" t="n">
         <v>4.8</v>
@@ -1562,24 +1562,24 @@
         <v>0</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>0.2672</v>
+        <v>0.2646</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-0.931</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>4.2797</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="n">
-        <v>4.7848</v>
+        <v>5.0202</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.1985</v>
+        <v>0.1916</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -1615,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>0.2727</v>
+        <v>0.2014</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-0.952</v>
+        <v>-0.96</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>4.8808</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14"/>
@@ -1629,7 +1629,7 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2026-12-18 (56 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2026-12-18 (55 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -1722,13 +1722,13 @@
     </row>
     <row r="18">
       <c r="B18" s="22" t="n">
-        <v>2.196</v>
+        <v>2.9639</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>1</v>
+        <v>0.962</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0</v>
+        <v>7.8431</v>
       </c>
       <c r="E18" s="24" t="n">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="26" t="n">
         <v>0.5</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="M18" s="16" t="n">
         <v>0</v>
@@ -1764,24 +1764,24 @@
         <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>7.4409</v>
+        <v>4.4139</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.503</v>
+        <v>-0.758</v>
       </c>
       <c r="R18" s="17" t="n">
-        <v>1.2372</v>
+        <v>5.7863</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="n">
-        <v>2.262</v>
+        <v>3.1571</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.422</v>
+        <v>0.533</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.7832</v>
+        <v>0.6251</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="J19" s="26" t="n">
         <v>1</v>
@@ -1805,7 +1805,7 @@
         <v>0.1</v>
       </c>
       <c r="L19" s="27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="M19" s="27" t="n">
         <v>0</v>
@@ -1820,15 +1820,15 @@
         <v>0</v>
       </c>
       <c r="Q19" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.869</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>2.5742</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="n">
-        <v>2.4646</v>
+        <v>2.1699</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J20" s="26" t="n">
         <v>1.5</v>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.869</v>
       </c>
       <c r="R20" s="30" t="n">
         <v>1.2</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="21">
       <c r="B21" s="17" t="n">
-        <v>2.3523</v>
+        <v>2.4935</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>2</v>
       </c>
       <c r="K21" s="27" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M21" s="27" t="n">
         <v>0</v>
@@ -1926,15 +1926,15 @@
         <v>0</v>
       </c>
       <c r="Q21" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.869</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>1.4542</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="n">
-        <v>4.4321</v>
+        <v>8.449</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>0</v>
@@ -1955,13 +1955,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="J22" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K22" s="27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>2.65</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.869</v>
       </c>
       <c r="R22" s="30" t="n">
         <v>1.2</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="J23" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K23" s="27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L23" s="27" t="n">
         <v>5.2</v>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="29" t="n">
-        <v>-0.862</v>
+        <v>-0.869</v>
       </c>
       <c r="R23" s="30" t="n">
         <v>1.2</v>
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.0373</v>
+        <v>0.1005</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>-0.864</v>
+        <v>-0.873</v>
       </c>
       <c r="R24" s="30" t="n">
         <v>1.2</v>
@@ -2096,7 +2096,7 @@
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-01-15 (84 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-01-15 (83 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2189,19 +2189,19 @@
     </row>
     <row r="29">
       <c r="B29" s="22" t="n">
-        <v>1.008</v>
+        <v>1.0405</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.731</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>1.0078</v>
+        <v>1.133</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>10064</v>
+        <v>10063</v>
       </c>
       <c r="G29" s="25" t="n">
         <v>0.15</v>
@@ -2210,7 +2210,7 @@
         <v>0.05</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J29" s="26" t="n">
         <v>0.5</v>
@@ -2219,7 +2219,7 @@
         <v>0.05</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>0.1</v>
@@ -2228,39 +2228,39 @@
         <v>2093</v>
       </c>
       <c r="O29" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>1.0258</v>
+        <v>1.1545</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>-0.297</v>
+        <v>-0.339</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>2.4491</v>
+        <v>1.7702</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="n">
-        <v>1.7796</v>
+        <v>1.4341</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.395</v>
+        <v>0.368</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.8854</v>
+        <v>0.9099</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>7001</v>
+        <v>7012</v>
       </c>
       <c r="G30" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>0.15</v>
@@ -2284,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.9176</v>
+        <v>0.9456</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.64</v>
+        <v>-0.667</v>
       </c>
       <c r="R30" s="30" t="n">
-        <v>1.6327</v>
+        <v>1.3418</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="n">
-        <v>1.7616</v>
+        <v>1.8895</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>0.285</v>
+        <v>0.267</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6854</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0.7</v>
       </c>
       <c r="L31" s="27" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="M31" s="27" t="n">
         <v>0.97</v>
@@ -2337,24 +2337,24 @@
         <v>0</v>
       </c>
       <c r="P31" s="29" t="n">
-        <v>0.712</v>
+        <v>0.7301</v>
       </c>
       <c r="Q31" s="29" t="n">
-        <v>-0.754</v>
+        <v>-0.773</v>
       </c>
       <c r="R31" s="30" t="n">
-        <v>2.8479</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="n">
-        <v>3.0389</v>
+        <v>4.2236</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0.233</v>
+        <v>0.218</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.551</v>
+        <v>0.5613</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
@@ -2369,16 +2369,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J32" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="L32" s="27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M32" s="27" t="n">
         <v>1.3</v>
@@ -2390,24 +2390,24 @@
         <v>0</v>
       </c>
       <c r="P32" s="29" t="n">
-        <v>0.6002</v>
+        <v>0.6182</v>
       </c>
       <c r="Q32" s="29" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.826</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>1.8448</v>
+        <v>1.5073</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="n">
-        <v>2.7974</v>
+        <v>2.9551</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.475</v>
+        <v>0.4837</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         <v>2.5</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="L33" s="27" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M33" s="27" t="n">
         <v>2</v>
@@ -2443,24 +2443,24 @@
         <v>0</v>
       </c>
       <c r="P33" s="29" t="n">
-        <v>0.5331</v>
+        <v>0.551</v>
       </c>
       <c r="Q33" s="29" t="n">
-        <v>-0.846</v>
+        <v>-0.859</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>2.0715</v>
+        <v>6.9688</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="17" t="n">
-        <v>4.1222</v>
+        <v>4.3253</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.312</v>
+        <v>0.3175</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>0</v>
@@ -2496,24 +2496,24 @@
         <v>0</v>
       </c>
       <c r="P34" s="29" t="n">
-        <v>0.4042</v>
+        <v>0.3856</v>
       </c>
       <c r="Q34" s="29" t="n">
-        <v>-0.927</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>3.4346</v>
+        <v>3.0457</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="n">
-        <v>4.4566</v>
+        <v>4.658</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.113</v>
+        <v>0.106</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.2508</v>
+        <v>0.2551</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>7.5</v>
       </c>
       <c r="K35" s="27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L35" s="27" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M35" s="27" t="n">
         <v>6.2</v>
@@ -2549,24 +2549,24 @@
         <v>0</v>
       </c>
       <c r="P35" s="29" t="n">
-        <v>0.4172</v>
+        <v>0.2551</v>
       </c>
       <c r="Q35" s="29" t="n">
         <v>-0.968</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>3.8528</v>
+        <v>7.8125</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="n">
-        <v>2.9761</v>
+        <v>3.0802</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.2171</v>
+        <v>0.2208</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>0</v>
@@ -2602,24 +2602,24 @@
         <v>0</v>
       </c>
       <c r="P36" s="29" t="n">
-        <v>0.1391</v>
+        <v>0.1638</v>
       </c>
       <c r="Q36" s="29" t="n">
-        <v>-0.989</v>
+        <v>-0.983</v>
       </c>
       <c r="R36" s="30" t="n">
-        <v>6.625</v>
+        <v>6.5313</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="n">
-        <v>3.1288</v>
+        <v>3.2333</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>0.091</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.1952</v>
+        <v>0.1984</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0</v>
@@ -2655,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="29" t="n">
-        <v>0</v>
+        <v>0.0997</v>
       </c>
       <c r="Q37" s="29" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="R37" s="30" t="n">
-        <v>8.2188</v>
+        <v>8.1875</v>
       </c>
     </row>
     <row r="38"/>
@@ -2669,7 +2669,7 @@
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-02-19 (119 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-02-19 (118 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -2762,19 +2762,19 @@
     </row>
     <row r="42">
       <c r="B42" s="22" t="n">
-        <v>1.688</v>
+        <v>2.5291</v>
       </c>
       <c r="C42" s="23" t="n">
-        <v>0.706</v>
+        <v>0.674</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>0.6702</v>
+        <v>0.7734</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="24" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="G42" s="25" t="n">
         <v>0.35</v>
@@ -2783,7 +2783,7 @@
         <v>0.15</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J42" s="26" t="n">
         <v>0.5</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M42" s="16" t="n">
         <v>0.11</v>
@@ -2804,30 +2804,30 @@
         <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0.6569</v>
+        <v>0.7619</v>
       </c>
       <c r="Q42" s="15" t="n">
-        <v>-0.276</v>
+        <v>-0.309</v>
       </c>
       <c r="R42" s="17" t="n">
-        <v>0.125</v>
+        <v>7.1869</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="17" t="n">
-        <v>1.9823</v>
+        <v>2.3884</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.421</v>
+        <v>0.394</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.748</v>
+        <v>0.7874</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>6484</v>
+        <v>6456</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>0.1</v>
@@ -2836,16 +2836,16 @@
         <v>0.05</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J43" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L43" s="27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="M43" s="27" t="n">
         <v>0.45</v>
@@ -2857,24 +2857,24 @@
         <v>0</v>
       </c>
       <c r="P43" s="29" t="n">
-        <v>0.7599</v>
+        <v>0.8044</v>
       </c>
       <c r="Q43" s="29" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.589</v>
       </c>
       <c r="R43" s="30" t="n">
-        <v>1.281</v>
+        <v>1.4878</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="17" t="n">
-        <v>1.7785</v>
+        <v>1.9094</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.308</v>
+        <v>0.288</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.614</v>
+        <v>0.6362</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0</v>
@@ -2910,24 +2910,24 @@
         <v>0</v>
       </c>
       <c r="P44" s="29" t="n">
-        <v>0.6444</v>
+        <v>0.6737</v>
       </c>
       <c r="Q44" s="29" t="n">
-        <v>-0.679</v>
+        <v>-0.7</v>
       </c>
       <c r="R44" s="30" t="n">
-        <v>1.7132</v>
+        <v>1.3628</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="17" t="n">
-        <v>3.2514</v>
+        <v>3.0416</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>0.251</v>
+        <v>0.236</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.5195</v>
+        <v>0.5363</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>0</v>
@@ -2942,16 +2942,16 @@
         <v>0</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="J45" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L45" s="27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M45" s="27" t="n">
         <v>1.35</v>
@@ -2963,24 +2963,24 @@
         <v>0</v>
       </c>
       <c r="P45" s="29" t="n">
-        <v>0.5647</v>
+        <v>0.5906</v>
       </c>
       <c r="Q45" s="29" t="n">
-        <v>-0.74</v>
+        <v>-0.758</v>
       </c>
       <c r="R45" s="30" t="n">
-        <v>0</v>
+        <v>6.8125</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="17" t="n">
-        <v>4.0779</v>
+        <v>4.3827</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>0.217</v>
+        <v>0.204</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.4552</v>
+        <v>0.4693</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         <v>2.5</v>
       </c>
       <c r="K46" s="27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="L46" s="27" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M46" s="27" t="n">
         <v>0</v>
@@ -3016,10 +3016,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="29" t="n">
-        <v>0.5139</v>
+        <v>0.5391</v>
       </c>
       <c r="Q46" s="29" t="n">
-        <v>-0.78</v>
+        <v>-0.796</v>
       </c>
       <c r="R46" s="30" t="n">
         <v>1.2</v>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="47">
       <c r="B47" s="17" t="n">
-        <v>3.1634</v>
+        <v>4.4084</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>0.144</v>
+        <v>0.136</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.3054</v>
+        <v>0.3143</v>
       </c>
       <c r="E47" s="14" t="n">
         <v>0</v>
@@ -3048,16 +3048,16 @@
         <v>0</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="L47" s="27" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="M47" s="27" t="n">
         <v>0</v>
@@ -3069,24 +3069,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="29" t="n">
-        <v>0.4295</v>
+        <v>0.4649</v>
       </c>
       <c r="Q47" s="29" t="n">
-        <v>-0.88</v>
+        <v>-0.894</v>
       </c>
       <c r="R47" s="30" t="n">
-        <v>2.5959</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="n">
-        <v>0.5</v>
+        <v>6.0172</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>0.117</v>
+        <v>0.11</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.2449</v>
+        <v>0.2518</v>
       </c>
       <c r="E48" s="14" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="J48" s="26" t="n">
         <v>7.5</v>
@@ -3122,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="29" t="n">
-        <v>0.4519</v>
+        <v>0.3802</v>
       </c>
       <c r="Q48" s="29" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.945</v>
       </c>
       <c r="R48" s="30" t="n">
-        <v>2.6359</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="49"/>
@@ -3136,7 +3136,7 @@
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EXPIRATION: 2027-05-21 (210 days) — Max Pain: $0.5</t>
+          <t>EXPIRATION: 2027-05-21 (209 days) — Max Pain: $0.5</t>
         </is>
       </c>
     </row>
@@ -3229,28 +3229,28 @@
     </row>
     <row r="53">
       <c r="B53" s="22" t="n">
-        <v>1.2002</v>
+        <v>3.4088</v>
       </c>
       <c r="C53" s="23" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.786</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>0.5236</v>
+        <v>0.613</v>
       </c>
       <c r="E53" s="24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F53" s="24" t="n">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="G53" s="25" t="n">
         <v>0.3</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J53" s="26" t="n">
         <v>0.5</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="M53" s="16" t="n">
         <v>0.2</v>
@@ -3271,45 +3271,45 @@
         <v>0</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>0.5399</v>
+        <v>0.6351</v>
       </c>
       <c r="Q53" s="15" t="n">
-        <v>-0.249</v>
+        <v>-0.277</v>
       </c>
       <c r="R53" s="17" t="n">
-        <v>1.8049</v>
+        <v>5.6279</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="17" t="n">
-        <v>1.3488</v>
+        <v>2.645</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>0.569</v>
+        <v>0.544</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.6869</v>
+        <v>0.7345</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H54" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="J54" s="26" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="27" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L54" s="27" t="n">
         <v>1.05</v>
@@ -3324,24 +3324,24 @@
         <v>0</v>
       </c>
       <c r="P54" s="29" t="n">
-        <v>0.7352</v>
+        <v>0.793</v>
       </c>
       <c r="Q54" s="29" t="n">
-        <v>-0.506</v>
+        <v>-0.533</v>
       </c>
       <c r="R54" s="30" t="n">
-        <v>1.5644</v>
+        <v>1.2837</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="17" t="n">
-        <v>2.2312</v>
+        <v>1.3337</v>
       </c>
       <c r="C55" s="15" t="n">
-        <v>0.464</v>
+        <v>0.446</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>0.6194</v>
+        <v>0.6534</v>
       </c>
       <c r="E55" s="14" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="J55" s="26" t="n">
         <v>1.5</v>
@@ -3377,24 +3377,24 @@
         <v>0</v>
       </c>
       <c r="P55" s="29" t="n">
-        <v>0.6871</v>
+        <v>0.7339</v>
       </c>
       <c r="Q55" s="29" t="n">
-        <v>-0.62</v>
+        <v>-0.641</v>
       </c>
       <c r="R55" s="30" t="n">
-        <v>1.776</v>
+        <v>1.6272</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="17" t="n">
-        <v>4.4153</v>
+        <v>5.1383</v>
       </c>
       <c r="C56" s="15" t="n">
-        <v>0.408</v>
+        <v>0.393</v>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.5609</v>
+        <v>0.59</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="L56" s="27" t="n">
         <v>2</v>
@@ -3430,24 +3430,24 @@
         <v>0</v>
       </c>
       <c r="P56" s="29" t="n">
-        <v>0.646</v>
+        <v>0.6896</v>
       </c>
       <c r="Q56" s="29" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.703</v>
       </c>
       <c r="R56" s="30" t="n">
-        <v>1.7061</v>
+        <v>1.6788</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="17" t="n">
-        <v>0.5</v>
+        <v>3.6481</v>
       </c>
       <c r="C57" s="15" t="n">
-        <v>0.372</v>
+        <v>0.357</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>0.5173</v>
+        <v>0.5436</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>0</v>
@@ -3462,16 +3462,16 @@
         <v>0</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>2.95</v>
+        <v>0.75</v>
       </c>
       <c r="J57" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="K57" s="27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L57" s="27" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="M57" s="27" t="n">
         <v>2</v>
@@ -3483,24 +3483,24 @@
         <v>0</v>
       </c>
       <c r="P57" s="29" t="n">
-        <v>0.6214</v>
+        <v>0.6641</v>
       </c>
       <c r="Q57" s="29" t="n">
-        <v>-0.729</v>
+        <v>-0.747</v>
       </c>
       <c r="R57" s="30" t="n">
-        <v>3.8332</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="n">
-        <v>1.5376</v>
+        <v>4.0241</v>
       </c>
       <c r="C58" s="15" t="n">
-        <v>0.283</v>
+        <v>0.272</v>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.4016</v>
+        <v>0.4211</v>
       </c>
       <c r="E58" s="14" t="n">
         <v>0</v>
@@ -3515,16 +3515,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="J58" s="26" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L58" s="27" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M58" s="27" t="n">
         <v>0</v>
@@ -3536,24 +3536,24 @@
         <v>0</v>
       </c>
       <c r="P58" s="29" t="n">
-        <v>0.5831</v>
+        <v>0.634</v>
       </c>
       <c r="Q58" s="29" t="n">
-        <v>-0.857</v>
+        <v>-0.876</v>
       </c>
       <c r="R58" s="30" t="n">
-        <v>2.7212</v>
+        <v>2.5536</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="17" t="n">
-        <v>1.9763</v>
+        <v>2.0524</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.242</v>
+        <v>0.232</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.3467</v>
+        <v>0.3631</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="29" t="n">
-        <v>0.588</v>
+        <v>0.4432</v>
       </c>
       <c r="Q59" s="29" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="R59" s="30" t="n">
-        <v>2.3012</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3714,26 +3714,26 @@
     <row r="6">
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.519</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>52908</v>
+        <v>52917</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>5174</v>
@@ -3745,10 +3745,10 @@
         <v>0.5</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1942369</v>
+        <v>1783512</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>2.1654</v>
+        <v>2.7517</v>
       </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
@@ -3759,29 +3759,29 @@
     <row r="7">
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C7" s="35" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>479</v>
+        <v>92</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>472</v>
+        <v>90</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>52837</v>
+        <v>52908</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>0.098</v>
@@ -3790,10 +3790,10 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1964829</v>
+        <v>1942369</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>2.5511</v>
+        <v>2.1654</v>
       </c>
       <c r="N7" s="34" t="inlineStr">
         <is>
@@ -3804,29 +3804,29 @@
     <row r="8">
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>0.52</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>351</v>
+        <v>479</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>350</v>
+        <v>472</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>52615</v>
+        <v>52837</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.098</v>
@@ -3835,10 +3835,10 @@
         <v>0.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1848028</v>
+        <v>1964829</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>1.9397</v>
+        <v>2.5511</v>
       </c>
       <c r="N8" s="31" t="inlineStr">
         <is>
@@ -3849,41 +3849,41 @@
     <row r="9">
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C9" s="35" t="n">
-        <v>0.493</v>
+        <v>0.52</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>245</v>
+        <v>351</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>52420</v>
+        <v>52615</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>5168</v>
+        <v>5172</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K9" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>1783238</v>
+        <v>1848028</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>2.1247</v>
+        <v>1.9397</v>
       </c>
       <c r="N9" s="34" t="inlineStr">
         <is>
@@ -3894,41 +3894,41 @@
     <row r="10">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>0.488</v>
+        <v>0.493</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1068</v>
+        <v>245</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1068</v>
+        <v>240</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>52426</v>
+        <v>52420</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5148</v>
+        <v>5168</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1713337</v>
+        <v>1783238</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>2.3701</v>
+        <v>2.1247</v>
       </c>
       <c r="N10" s="31" t="inlineStr">
         <is>
@@ -3939,17 +3939,17 @@
     <row r="11">
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C11" s="35" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>21</v>
+        <v>1068</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>0</v>
@@ -3958,10 +3958,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>52809</v>
+        <v>52426</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>5156</v>
+        <v>5148</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.098</v>
@@ -3970,10 +3970,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>1758474</v>
+        <v>1713337</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>2.3822</v>
+        <v>2.3701</v>
       </c>
       <c r="N11" s="34" t="inlineStr">
         <is>
@@ -3984,29 +3984,29 @@
     <row r="12">
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>52606</v>
+        <v>52809</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5168</v>
+        <v>5156</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.098</v>
@@ -4015,10 +4015,10 @@
         <v>0.5</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1656075</v>
+        <v>1758474</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>1.2617</v>
+        <v>2.3822</v>
       </c>
       <c r="N12" s="31" t="inlineStr">
         <is>
@@ -4029,29 +4029,29 @@
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C13" s="35" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>160</v>
+        <v>579</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.098</v>
@@ -4060,10 +4060,10 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>1944243</v>
+        <v>1656075</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1.8127</v>
+        <v>1.2617</v>
       </c>
       <c r="N13" s="34" t="inlineStr">
         <is>
@@ -4074,29 +4074,29 @@
     <row r="14">
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>52582</v>
+        <v>52600</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.098</v>
@@ -4105,10 +4105,10 @@
         <v>0.5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2035091</v>
+        <v>1944243</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>2.1738</v>
+        <v>1.8127</v>
       </c>
       <c r="N14" s="31" t="inlineStr">
         <is>
@@ -4119,29 +4119,29 @@
     <row r="15">
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C15" s="35" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>52437</v>
+        <v>52582</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>5157</v>
+        <v>5162</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0.098</v>
@@ -4150,10 +4150,10 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>2109261</v>
+        <v>2035091</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>1.7667</v>
+        <v>2.1738</v>
       </c>
       <c r="N15" s="34" t="inlineStr">
         <is>
@@ -4164,26 +4164,26 @@
     <row r="16">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>52411</v>
+        <v>52437</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>5157</v>
@@ -4195,10 +4195,10 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2123587</v>
+        <v>2109261</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.6438</v>
+        <v>1.7667</v>
       </c>
       <c r="N16" s="31" t="inlineStr">
         <is>
@@ -4209,41 +4209,41 @@
     <row r="17">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
-        <v>0.59</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>52350</v>
+        <v>52411</v>
       </c>
       <c r="I17" s="14" t="n">
         <v>5157</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>2053723</v>
+        <v>2123587</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>1.5704</v>
+        <v>1.6438</v>
       </c>
       <c r="N17" s="34" t="inlineStr">
         <is>
@@ -4254,29 +4254,29 @@
     <row r="18">
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>0.572</v>
+        <v>0.59</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>753</v>
+        <v>97</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>752</v>
+        <v>97</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>52240</v>
+        <v>52350</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.099</v>
@@ -4285,10 +4285,10 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1990459</v>
+        <v>2053723</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.565</v>
+        <v>1.5704</v>
       </c>
       <c r="N18" s="31" t="inlineStr">
         <is>
@@ -4299,29 +4299,29 @@
     <row r="19">
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C19" s="35" t="n">
-        <v>0.596</v>
+        <v>0.572</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>54</v>
+        <v>753</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>52</v>
+        <v>752</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.038</v>
+        <v>0.001</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>52224</v>
+        <v>52240</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>0.099</v>
@@ -4330,10 +4330,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>2043757</v>
+        <v>1990459</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>1.7067</v>
+        <v>1.565</v>
       </c>
       <c r="N19" s="34" t="inlineStr">
         <is>
@@ -4344,26 +4344,26 @@
     <row r="20">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>52215</v>
+        <v>52224</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>5161</v>
@@ -4375,10 +4375,10 @@
         <v>0.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2089489</v>
+        <v>2043757</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>1.5299</v>
+        <v>1.7067</v>
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
@@ -4389,17 +4389,17 @@
     <row r="21">
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C21" s="35" t="n">
-        <v>0.575</v>
+        <v>0.593</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F21" s="14" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>52120</v>
+        <v>52215</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>5161</v>
@@ -4420,10 +4420,10 @@
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>2045464</v>
+        <v>2089489</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1.3543</v>
+        <v>1.5299</v>
       </c>
       <c r="N21" s="34" t="inlineStr">
         <is>
@@ -4434,29 +4434,29 @@
     <row r="22">
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52113</v>
+        <v>52120</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="J22" s="9" t="n">
         <v>0.099</v>
@@ -4465,10 +4465,10 @@
         <v>0.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2073560</v>
+        <v>2045464</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>1.9768</v>
+        <v>1.3543</v>
       </c>
       <c r="N22" s="31" t="inlineStr">
         <is>
@@ -4479,41 +4479,41 @@
     <row r="23">
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>0.626</v>
+        <v>0.574</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>926</v>
+        <v>92</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>926</v>
+        <v>76</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>52476</v>
+        <v>52113</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>5159</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K23" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>2302405</v>
+        <v>2073560</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>1.4818</v>
+        <v>1.9768</v>
       </c>
       <c r="N23" s="34" t="inlineStr">
         <is>
@@ -4524,29 +4524,29 @@
     <row r="24">
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>185</v>
+        <v>926</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>183</v>
+        <v>926</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>52389</v>
+        <v>52476</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>0.098</v>
@@ -4555,10 +4555,10 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2187188</v>
+        <v>2302405</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>1.7835</v>
+        <v>1.4818</v>
       </c>
       <c r="N24" s="31" t="inlineStr">
         <is>
@@ -4569,29 +4569,29 @@
     <row r="25">
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C25" s="35" t="n">
-        <v>0.64</v>
+        <v>0.621</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>52366</v>
+        <v>52389</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>0.098</v>
@@ -4600,10 +4600,10 @@
         <v>0.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2331050</v>
+        <v>2187188</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>1.8306</v>
+        <v>1.7835</v>
       </c>
       <c r="N25" s="34" t="inlineStr">
         <is>
@@ -4614,26 +4614,26 @@
     <row r="26">
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>52361</v>
+        <v>52366</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>5156</v>
@@ -4645,10 +4645,10 @@
         <v>0.5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2322466</v>
+        <v>2331050</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1.8394</v>
+        <v>1.8306</v>
       </c>
       <c r="N26" s="31" t="inlineStr">
         <is>
@@ -4659,41 +4659,41 @@
     <row r="27">
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C27" s="35" t="n">
-        <v>0.662</v>
+        <v>0.656</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>52329</v>
+        <v>52361</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>2291254</v>
+        <v>2322466</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>1.7796</v>
+        <v>1.8394</v>
       </c>
       <c r="N27" s="34" t="inlineStr">
         <is>
@@ -4704,41 +4704,41 @@
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>0.6962</v>
+        <v>0.662</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>3</v>
+        <v>0.034</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>52308</v>
+        <v>52329</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>4903</v>
+        <v>5155</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2387186</v>
+        <v>2291254</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>1.7491</v>
+        <v>1.7796</v>
       </c>
       <c r="N28" s="31" t="inlineStr">
         <is>
@@ -4749,41 +4749,41 @@
     <row r="29">
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C29" s="35" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6962</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.173</v>
+        <v>3</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>52206</v>
+        <v>52308</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>4868</v>
+        <v>4903</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K29" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>2418880</v>
+        <v>2387186</v>
       </c>
       <c r="M29" s="17" t="n">
-        <v>1.9942</v>
+        <v>1.7491</v>
       </c>
       <c r="N29" s="34" t="inlineStr">
         <is>
@@ -4794,29 +4794,29 @@
     <row r="30">
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>0.653</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.075</v>
+        <v>0.173</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>52119</v>
+        <v>52206</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>4863</v>
+        <v>4868</v>
       </c>
       <c r="J30" s="9" t="n">
         <v>0.093</v>
@@ -4825,10 +4825,10 @@
         <v>0.5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2361798</v>
+        <v>2418880</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>1.8962</v>
+        <v>1.9942</v>
       </c>
       <c r="N30" s="31" t="inlineStr">
         <is>
@@ -4839,73 +4839,77 @@
     <row r="31">
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
-        <v>1.39</v>
+        <v>0.653</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>3394</v>
+        <v>171</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>3244</v>
+        <v>159</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>45759</v>
+        <v>52119</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>7845</v>
+        <v>4863</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K31" s="16" t="n"/>
+        <v>0.093</v>
+      </c>
+      <c r="K31" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L31" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="17" t="n"/>
+        <v>2361798</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>1.8962</v>
+      </c>
       <c r="N31" s="34" t="inlineStr">
         <is>
-          <t>NO DATA</t>
+          <t>Heavy call skew 🟢🟢</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>4661</v>
+        <v>3394</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>3922</v>
+        <v>3244</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>739</v>
+        <v>150</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.188</v>
+        <v>0.046</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>44316</v>
+        <v>45759</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>7547</v>
+        <v>7845</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="12" t="n">
@@ -4921,32 +4925,32 @@
     <row r="33">
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>2373</v>
+        <v>4661</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1490</v>
+        <v>3922</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>883</v>
+        <v>739</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.593</v>
+        <v>0.188</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>43736</v>
+        <v>44316</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>7194</v>
+        <v>7547</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="K33" s="16" t="n"/>
       <c r="L33" s="18" t="n">
@@ -4962,31 +4966,33 @@
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7609</v>
+        <v>2373</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6020</v>
+        <v>1490</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1589</v>
+        <v>883</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.264</v>
+        <v>0.593</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>43736</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9" t="n"/>
+        <v>7194</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.164</v>
+      </c>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -5001,23 +5007,23 @@
     <row r="35">
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>6065</v>
+        <v>7609</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>4568</v>
+        <v>6020</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1497</v>
+        <v>1589</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>0.328</v>
+        <v>0.264</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>0</v>
@@ -5040,33 +5046,31 @@
     <row r="36">
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>7670</v>
+        <v>6065</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6615</v>
+        <v>4568</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1055</v>
+        <v>1497</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.159</v>
+        <v>0.328</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>39061</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6136</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0.157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="12" t="n">
         <v>0</v>
@@ -5081,31 +5085,33 @@
     <row r="37">
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>11817</v>
+        <v>7670</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>11355</v>
+        <v>6615</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>462</v>
+        <v>1055</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>0.041</v>
+        <v>0.159</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>39061</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="15" t="n"/>
+        <v>6136</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>0.157</v>
+      </c>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="18" t="n">
         <v>0</v>
@@ -5120,23 +5126,23 @@
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
         <v>1.69</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>12436</v>
+        <v>11817</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>11777</v>
+        <v>11355</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>659</v>
+        <v>462</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
@@ -5159,33 +5165,31 @@
     <row r="39">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>5645</v>
+        <v>12436</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>5096</v>
+        <v>11777</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>0.108</v>
+        <v>0.056</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>32341</v>
+        <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>5834</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>0.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J39" s="15" t="n"/>
       <c r="K39" s="16" t="n"/>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -5200,31 +5204,33 @@
     <row r="40">
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>4451</v>
+        <v>5645</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>2661</v>
+        <v>5096</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>1790</v>
+        <v>549</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.673</v>
+        <v>0.108</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>32341</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="n"/>
+        <v>5834</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.18</v>
+      </c>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="12" t="n">
         <v>0</v>
@@ -5239,33 +5245,31 @@
     <row r="41">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>7705</v>
+        <v>4451</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>5069</v>
+        <v>2661</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>2636</v>
+        <v>1790</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>0.52</v>
+        <v>0.673</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>29371</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>4272</v>
-      </c>
-      <c r="J41" s="15" t="n">
-        <v>0.145</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J41" s="15" t="n"/>
       <c r="K41" s="16" t="n"/>
       <c r="L41" s="18" t="n">
         <v>0</v>
@@ -5280,31 +5284,33 @@
     <row r="42">
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2568</v>
+        <v>7705</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>2022</v>
+        <v>5069</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>546</v>
+        <v>2636</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>29371</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9" t="n"/>
+        <v>4272</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.145</v>
+      </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="12" t="n">
         <v>0</v>
@@ -5319,11 +5325,11 @@
     <row r="43">
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C43" s="35" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>2568</v>
@@ -5338,14 +5344,12 @@
         <v>0.27</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>27287</v>
+        <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J43" s="15" t="n">
-        <v>0.152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J43" s="15" t="n"/>
       <c r="K43" s="16" t="n"/>
       <c r="L43" s="18" t="n">
         <v>0</v>
@@ -5360,11 +5364,11 @@
     <row r="44">
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2568</v>
@@ -5379,12 +5383,14 @@
         <v>0.27</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>27287</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="9" t="n"/>
+        <v>4145</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.152</v>
+      </c>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="12" t="n">
         <v>0</v>
@@ -5399,11 +5405,11 @@
     <row r="45">
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C45" s="35" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>2568</v>
@@ -5418,14 +5424,12 @@
         <v>0.27</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>4059</v>
-      </c>
-      <c r="J45" s="15" t="n">
-        <v>0.159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J45" s="15" t="n"/>
       <c r="K45" s="16" t="n"/>
       <c r="L45" s="18" t="n">
         <v>0</v>
@@ -5440,29 +5444,33 @@
     <row r="46">
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="9" t="n"/>
+        <v>546</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="H46" s="8" t="n">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="9" t="n"/>
+        <v>4059</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.159</v>
+      </c>
       <c r="K46" s="10" t="n"/>
       <c r="L46" s="12" t="n">
         <v>0</v>
@@ -5477,11 +5485,11 @@
     <row r="47">
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C47" s="35" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
@@ -5514,11 +5522,11 @@
     <row r="48">
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>0</v>
@@ -5551,11 +5559,11 @@
     <row r="49">
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C49" s="35" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>0</v>
@@ -5588,11 +5596,11 @@
     <row r="50">
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>0</v>
@@ -5625,11 +5633,11 @@
     <row r="51">
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C51" s="35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>0</v>
@@ -5662,7 +5670,7 @@
     <row r="52">
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C52" s="32" t="n">
@@ -5699,7 +5707,7 @@
     <row r="53">
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C53" s="35" t="n">
@@ -5736,7 +5744,7 @@
     <row r="54">
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C54" s="32" t="n">
@@ -5765,6 +5773,43 @@
       </c>
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="31" t="inlineStr">
+        <is>
+          <t>NO DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="17" t="n"/>
+      <c r="N55" s="34" t="inlineStr">
         <is>
           <t>NO DATA</t>
         </is>
@@ -5885,19 +5930,19 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>1755</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
@@ -5931,7 +5976,7 @@
         <v>876</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>876</v>
@@ -5971,7 +6016,7 @@
         <v>1631</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0</v>
+        <v>1631</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>1631</v>
@@ -6011,7 +6056,7 @@
         <v>358</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>358</v>
@@ -6051,7 +6096,7 @@
         <v>2128</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>2128</v>
@@ -6091,7 +6136,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>150</v>
@@ -6131,7 +6176,7 @@
         <v>1358</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>1358</v>
@@ -7005,19 +7050,19 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>10064</v>
+        <v>10063</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10064</v>
+        <v>10063</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>10063</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>10064</v>
+        <v>10063</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>10064</v>
+        <v>10063</v>
       </c>
       <c r="K34" s="31" t="inlineStr">
         <is>
@@ -7051,7 +7096,7 @@
         <v>2093</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="I35" s="14" t="n">
         <v>2093</v>
@@ -7085,19 +7130,19 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>7001</v>
+        <v>7012</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>7001</v>
+        <v>7012</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>7012</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>7001</v>
+        <v>7012</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>7001</v>
+        <v>7012</v>
       </c>
       <c r="K36" s="31" t="inlineStr">
         <is>
@@ -7131,7 +7176,7 @@
         <v>641</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="I37" s="14" t="n">
         <v>641</v>
@@ -7171,7 +7216,7 @@
         <v>1986</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="I38" s="8" t="n">
         <v>1986</v>
@@ -7211,7 +7256,7 @@
         <v>455</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="I39" s="14" t="n">
         <v>455</v>
@@ -7251,7 +7296,7 @@
         <v>2821</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>2821</v>
       </c>
       <c r="I40" s="8" t="n">
         <v>2821</v>
@@ -7291,7 +7336,7 @@
         <v>12</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>12</v>
@@ -7331,7 +7376,7 @@
         <v>3053</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>3053</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>3053</v>
@@ -7371,7 +7416,7 @@
         <v>153</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="I43" s="14" t="n">
         <v>153</v>
@@ -7411,7 +7456,7 @@
         <v>1989</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>1989</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>1989</v>
@@ -7491,7 +7536,7 @@
         <v>252</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>252</v>
@@ -7571,7 +7616,7 @@
         <v>55</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I48" s="8" t="n">
         <v>55</v>
@@ -7725,19 +7770,19 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="K52" s="31" t="inlineStr">
         <is>
@@ -7805,19 +7850,19 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>6484</v>
+        <v>6456</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>6484</v>
+        <v>6456</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0</v>
+        <v>6456</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>6484</v>
+        <v>6456</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>6484</v>
+        <v>6456</v>
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
@@ -7851,7 +7896,7 @@
         <v>151</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>151</v>
@@ -7891,7 +7936,7 @@
         <v>5594</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0</v>
+        <v>5594</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>5594</v>
@@ -7931,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>1</v>
@@ -7971,7 +8016,7 @@
         <v>1074</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0</v>
+        <v>1074</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>1074</v>
@@ -8011,7 +8056,7 @@
         <v>41</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>41</v>
@@ -8051,7 +8096,7 @@
         <v>838</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>838</v>
@@ -8285,19 +8330,19 @@
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="I66" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="K66" s="31" t="inlineStr">
         <is>
@@ -8331,7 +8376,7 @@
         <v>5</v>
       </c>
       <c r="H67" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" s="14" t="n">
         <v>0</v>
@@ -8365,19 +8410,19 @@
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="I68" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K68" s="31" t="inlineStr">
         <is>
@@ -8411,7 +8456,7 @@
         <v>3</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" s="14" t="n">
         <v>0</v>
@@ -8451,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="8" t="n">
         <v>0</v>
@@ -8531,7 +8576,7 @@
         <v>152</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="I72" s="8" t="n">
         <v>0</v>
@@ -8611,7 +8656,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="8" t="n">
         <v>0</v>
@@ -8691,7 +8736,7 @@
         <v>30</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -8771,7 +8816,7 @@
         <v>36</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I78" s="8" t="n">
         <v>0</v>
